--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="583">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -491,6 +491,9 @@
     <t>Four ADRs marked Accepted with a name and date</t>
   </si>
   <si>
+    <t>✅ Done — D1/D5/D11/D14 marked Accepted, name+date in 05-kickoff-pack §2</t>
+  </si>
+  <si>
     <t>W00-03</t>
   </si>
   <si>
@@ -501,6 +504,9 @@
   </si>
   <si>
     <t>Fourteen of fourteen Accepted</t>
+  </si>
+  <si>
+    <t>✅ Done — 14/14 ADRs marked Accepted, name+date in 05-kickoff-pack §2</t>
   </si>
   <si>
     <t>W00-04</t>
@@ -3207,12 +3213,12 @@
         <v>155</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" s="11" t="s">
         <v>51</v>
@@ -3224,10 +3230,10 @@
         <v>146</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G7" s="12">
         <v>0.25</v>
@@ -3239,15 +3245,15 @@
         <v>152</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>51</v>
@@ -3256,13 +3262,13 @@
         <v>145</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G8" s="12">
         <v>0.5</v>
@@ -3274,7 +3280,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>151</v>
@@ -3282,7 +3288,7 @@
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>51</v>
@@ -3291,25 +3297,25 @@
         <v>145</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G9" s="12">
         <v>0.25</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>151</v>
@@ -3317,7 +3323,7 @@
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>51</v>
@@ -3326,13 +3332,13 @@
         <v>145</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G10" s="12">
         <v>0.25</v>
@@ -3344,7 +3350,7 @@
         <v>61</v>
       </c>
       <c r="J10" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>151</v>
@@ -3352,7 +3358,7 @@
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>51</v>
@@ -3361,13 +3367,13 @@
         <v>145</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G11" s="12">
         <v>0.5</v>
@@ -3379,7 +3385,7 @@
         <v>61</v>
       </c>
       <c r="J11" s="11" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>151</v>
@@ -3387,7 +3393,7 @@
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>51</v>
@@ -3396,13 +3402,13 @@
         <v>145</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="G12" s="12">
         <v>0.25</v>
@@ -3411,10 +3417,10 @@
         <v>149</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>151</v>
@@ -3422,7 +3428,7 @@
     </row>
     <row r="13" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B13" s="11" t="s">
         <v>51</v>
@@ -3431,13 +3437,13 @@
         <v>145</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G13" s="12">
         <v>0.25</v>
@@ -3446,10 +3452,10 @@
         <v>149</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J13" s="11" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>151</v>
@@ -3457,7 +3463,7 @@
     </row>
     <row r="14" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>51</v>
@@ -3466,13 +3472,13 @@
         <v>145</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G14" s="12">
         <v>0.5</v>
@@ -3484,7 +3490,7 @@
         <v>61</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>151</v>
@@ -3492,22 +3498,22 @@
     </row>
     <row r="15" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B15" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G15" s="12">
         <v>0.5</v>
@@ -3519,7 +3525,7 @@
         <v>61</v>
       </c>
       <c r="J15" s="11" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>151</v>
@@ -3527,22 +3533,22 @@
     </row>
     <row r="16" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="G16" s="12">
         <v>0.75</v>
@@ -3551,10 +3557,10 @@
         <v>149</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>151</v>
@@ -3562,22 +3568,22 @@
     </row>
     <row r="17" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G17" s="12">
         <v>0.75</v>
@@ -3586,10 +3592,10 @@
         <v>149</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>151</v>
@@ -3597,22 +3603,22 @@
     </row>
     <row r="18" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G18" s="12">
         <v>0.5</v>
@@ -3621,10 +3627,10 @@
         <v>149</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>151</v>
@@ -3632,22 +3638,22 @@
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G19" s="12">
         <v>0.5</v>
@@ -3659,15 +3665,15 @@
         <v>61</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>51</v>
@@ -3676,13 +3682,13 @@
         <v>145</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G20" s="12">
         <v>0.25</v>
@@ -3691,10 +3697,10 @@
         <v>149</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>151</v>
@@ -3702,22 +3708,22 @@
     </row>
     <row r="21" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="G21" s="12">
         <v>0.5</v>
@@ -3726,10 +3732,10 @@
         <v>149</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>151</v>
@@ -3737,7 +3743,7 @@
     </row>
     <row r="22" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>51</v>
@@ -3746,13 +3752,13 @@
         <v>145</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G22" s="12">
         <v>0.25</v>
@@ -3764,7 +3770,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>151</v>
@@ -3772,22 +3778,22 @@
     </row>
     <row r="23" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>107</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G23" s="12">
         <v>0.5</v>
@@ -3799,30 +3805,30 @@
         <v>61</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G24" s="12">
         <v>0.25</v>
@@ -3831,10 +3837,10 @@
         <v>149</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>151</v>
@@ -3842,22 +3848,22 @@
     </row>
     <row r="25" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>57</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G25" s="12">
         <v>3</v>
@@ -3869,7 +3875,7 @@
         <v>144</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>151</v>
@@ -3877,22 +3883,22 @@
     </row>
     <row r="26" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>57</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G26" s="12">
         <v>2</v>
@@ -3901,10 +3907,10 @@
         <v>149</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>151</v>
@@ -3912,22 +3918,22 @@
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>57</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="G27" s="12">
         <v>0.75</v>
@@ -3936,10 +3942,10 @@
         <v>149</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>151</v>
@@ -3947,22 +3953,22 @@
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G28" s="12">
         <v>2</v>
@@ -3971,10 +3977,10 @@
         <v>149</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>151</v>
@@ -3982,22 +3988,22 @@
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -4006,10 +4012,10 @@
         <v>149</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>151</v>
@@ -4017,22 +4023,22 @@
     </row>
     <row r="30" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -4041,10 +4047,10 @@
         <v>149</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>151</v>
@@ -4052,22 +4058,22 @@
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
@@ -4076,10 +4082,10 @@
         <v>149</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>151</v>
@@ -4087,22 +4093,22 @@
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>63</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G32" s="12">
         <v>0.5</v>
@@ -4111,10 +4117,10 @@
         <v>149</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>151</v>
@@ -4122,22 +4128,22 @@
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G33" s="12">
         <v>2</v>
@@ -4146,10 +4152,10 @@
         <v>149</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>151</v>
@@ -4157,22 +4163,22 @@
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4181,10 +4187,10 @@
         <v>149</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>151</v>
@@ -4192,22 +4198,22 @@
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4216,10 +4222,10 @@
         <v>149</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4227,22 +4233,22 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4251,10 +4257,10 @@
         <v>149</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>151</v>
@@ -4262,22 +4268,22 @@
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4286,10 +4292,10 @@
         <v>149</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4297,22 +4303,22 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4321,10 +4327,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4332,22 +4338,22 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4356,10 +4362,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4367,22 +4373,22 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4391,10 +4397,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4402,22 +4408,22 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4426,10 +4432,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4437,22 +4443,22 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4461,10 +4467,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4472,22 +4478,22 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4496,10 +4502,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4507,22 +4513,22 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4531,10 +4537,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4542,34 +4548,34 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4577,22 +4583,22 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4601,10 +4607,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4612,22 +4618,22 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4636,10 +4642,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4647,22 +4653,22 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4671,10 +4677,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4682,22 +4688,22 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4706,10 +4712,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4717,22 +4723,22 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4741,10 +4747,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4752,22 +4758,22 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4776,10 +4782,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4787,22 +4793,22 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4811,10 +4817,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4822,22 +4828,22 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4846,10 +4852,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4857,22 +4863,22 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4881,10 +4887,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4892,22 +4898,22 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C55" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4916,10 +4922,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4927,22 +4933,22 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4951,10 +4957,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4962,22 +4968,22 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -4986,10 +4992,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -4997,22 +5003,22 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5021,10 +5027,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5032,22 +5038,22 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5056,10 +5062,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5067,22 +5073,22 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5091,10 +5097,10 @@
         <v>149</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5102,22 +5108,22 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5126,10 +5132,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5137,22 +5143,22 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5161,10 +5167,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5172,22 +5178,22 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5196,10 +5202,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5207,22 +5213,22 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5231,10 +5237,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5242,22 +5248,22 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5266,10 +5272,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5277,22 +5283,22 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5301,10 +5307,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5312,22 +5318,22 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5336,10 +5342,10 @@
         <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5347,22 +5353,22 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5371,10 +5377,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5382,34 +5388,34 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5417,34 +5423,34 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5452,22 +5458,22 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5476,10 +5482,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5487,7 +5493,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5496,13 +5502,13 @@
         <v>145</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5511,10 +5517,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5522,22 +5528,22 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5546,10 +5552,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5557,7 +5563,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5566,13 +5572,13 @@
         <v>145</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5581,10 +5587,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5592,22 +5598,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C75" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5616,10 +5622,10 @@
         <v>149</v>
       </c>
       <c r="I75" s="23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5627,22 +5633,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C76" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5651,10 +5657,10 @@
         <v>149</v>
       </c>
       <c r="I76" s="23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5662,22 +5668,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5686,10 +5692,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5697,22 +5703,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C78" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5721,10 +5727,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5732,22 +5738,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C79" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5756,10 +5762,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5767,22 +5773,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C80" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5791,10 +5797,10 @@
         <v>149</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5802,22 +5808,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C81" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5826,10 +5832,10 @@
         <v>149</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5837,34 +5843,34 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C82" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5872,34 +5878,34 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C83" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5907,34 +5913,34 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C84" s="20" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D84" s="26" t="s">
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -5974,12 +5980,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5993,19 +5999,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6028,10 +6034,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6054,10 +6060,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6080,10 +6086,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6106,7 +6112,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6130,7 +6136,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6154,10 +6160,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6180,7 +6186,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6204,7 +6210,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6228,10 +6234,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6254,7 +6260,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6278,7 +6284,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6302,7 +6308,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6326,7 +6332,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6350,15 +6356,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6366,7 +6372,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6374,7 +6380,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6403,7 +6409,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6420,10 +6426,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6431,7 +6437,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6440,10 +6446,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6451,7 +6457,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6463,7 +6469,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6471,7 +6477,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6480,10 +6486,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6491,7 +6497,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6500,10 +6506,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6517,18 +6523,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6537,53 +6543,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>
@@ -6608,26 +6614,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6635,13 +6641,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6649,13 +6655,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6663,13 +6669,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6677,13 +6683,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6691,13 +6697,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6705,13 +6711,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6719,13 +6725,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6733,13 +6739,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6747,13 +6753,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6761,13 +6767,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6775,21 +6781,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6825,7 +6831,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6833,7 +6839,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6845,167 +6851,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
   </sheetData>
@@ -7037,7 +7043,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7057,47 +7063,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7108,16 +7114,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7125,19 +7131,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7145,19 +7151,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7165,19 +7171,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="584">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -618,6 +618,9 @@
   </si>
   <si>
     <t>A direct push to main is rejected</t>
+  </si>
+  <si>
+    <t>✅ Done (e8f134b)</t>
   </si>
   <si>
     <t>W00-12</t>
@@ -3528,12 +3531,12 @@
         <v>198</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>151</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>51</v>
@@ -3545,10 +3548,10 @@
         <v>146</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G16" s="12">
         <v>0.75</v>
@@ -3560,7 +3563,7 @@
         <v>194</v>
       </c>
       <c r="J16" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>151</v>
@@ -3568,7 +3571,7 @@
     </row>
     <row r="17" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>51</v>
@@ -3580,10 +3583,10 @@
         <v>146</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G17" s="12">
         <v>0.75</v>
@@ -3592,10 +3595,10 @@
         <v>149</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>151</v>
@@ -3603,7 +3606,7 @@
     </row>
     <row r="18" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>51</v>
@@ -3615,10 +3618,10 @@
         <v>146</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G18" s="12">
         <v>0.5</v>
@@ -3627,10 +3630,10 @@
         <v>149</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>151</v>
@@ -3638,7 +3641,7 @@
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>51</v>
@@ -3647,13 +3650,13 @@
         <v>195</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G19" s="12">
         <v>0.5</v>
@@ -3665,15 +3668,15 @@
         <v>61</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>51</v>
@@ -3685,10 +3688,10 @@
         <v>190</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G20" s="12">
         <v>0.25</v>
@@ -3700,7 +3703,7 @@
         <v>189</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>151</v>
@@ -3708,7 +3711,7 @@
     </row>
     <row r="21" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>51</v>
@@ -3720,10 +3723,10 @@
         <v>70</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G21" s="12">
         <v>0.5</v>
@@ -3732,10 +3735,10 @@
         <v>149</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>151</v>
@@ -3743,7 +3746,7 @@
     </row>
     <row r="22" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>51</v>
@@ -3755,10 +3758,10 @@
         <v>177</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G22" s="12">
         <v>0.25</v>
@@ -3770,7 +3773,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>151</v>
@@ -3778,7 +3781,7 @@
     </row>
     <row r="23" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>51</v>
@@ -3790,10 +3793,10 @@
         <v>107</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G23" s="12">
         <v>0.5</v>
@@ -3805,30 +3808,30 @@
         <v>61</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G24" s="12">
         <v>0.25</v>
@@ -3837,10 +3840,10 @@
         <v>149</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>151</v>
@@ -3848,7 +3851,7 @@
     </row>
     <row r="25" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>57</v>
@@ -3860,10 +3863,10 @@
         <v>146</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G25" s="12">
         <v>3</v>
@@ -3875,7 +3878,7 @@
         <v>144</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>151</v>
@@ -3883,7 +3886,7 @@
     </row>
     <row r="26" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>57</v>
@@ -3895,10 +3898,10 @@
         <v>146</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G26" s="12">
         <v>2</v>
@@ -3907,10 +3910,10 @@
         <v>149</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>151</v>
@@ -3918,7 +3921,7 @@
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>57</v>
@@ -3930,10 +3933,10 @@
         <v>146</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G27" s="12">
         <v>0.75</v>
@@ -3942,10 +3945,10 @@
         <v>149</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>151</v>
@@ -3953,7 +3956,7 @@
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>63</v>
@@ -3965,10 +3968,10 @@
         <v>146</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G28" s="12">
         <v>2</v>
@@ -3977,10 +3980,10 @@
         <v>149</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>151</v>
@@ -3988,7 +3991,7 @@
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>63</v>
@@ -4000,10 +4003,10 @@
         <v>146</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -4012,10 +4015,10 @@
         <v>149</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>151</v>
@@ -4023,7 +4026,7 @@
     </row>
     <row r="30" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>63</v>
@@ -4035,10 +4038,10 @@
         <v>146</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -4047,10 +4050,10 @@
         <v>149</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>151</v>
@@ -4058,7 +4061,7 @@
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>63</v>
@@ -4070,10 +4073,10 @@
         <v>146</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
@@ -4082,10 +4085,10 @@
         <v>149</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>151</v>
@@ -4093,7 +4096,7 @@
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>63</v>
@@ -4105,10 +4108,10 @@
         <v>70</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G32" s="12">
         <v>0.5</v>
@@ -4117,10 +4120,10 @@
         <v>149</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>151</v>
@@ -4128,7 +4131,7 @@
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>68</v>
@@ -4140,10 +4143,10 @@
         <v>70</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G33" s="12">
         <v>2</v>
@@ -4152,10 +4155,10 @@
         <v>149</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>151</v>
@@ -4163,7 +4166,7 @@
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
@@ -4175,10 +4178,10 @@
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4187,10 +4190,10 @@
         <v>149</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>151</v>
@@ -4198,7 +4201,7 @@
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4210,10 +4213,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4222,10 +4225,10 @@
         <v>149</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4233,7 +4236,7 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4245,10 +4248,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4257,10 +4260,10 @@
         <v>149</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>151</v>
@@ -4268,7 +4271,7 @@
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4277,13 +4280,13 @@
         <v>195</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4292,10 +4295,10 @@
         <v>149</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4303,7 +4306,7 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4312,13 +4315,13 @@
         <v>195</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4327,10 +4330,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4338,7 +4341,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4347,13 +4350,13 @@
         <v>195</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4362,10 +4365,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4373,7 +4376,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4382,13 +4385,13 @@
         <v>195</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4397,10 +4400,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4408,7 +4411,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4417,13 +4420,13 @@
         <v>195</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4432,10 +4435,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4443,7 +4446,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4452,13 +4455,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4467,10 +4470,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4478,7 +4481,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4487,13 +4490,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4502,10 +4505,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4513,7 +4516,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4522,13 +4525,13 @@
         <v>195</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4537,10 +4540,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4548,7 +4551,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4557,13 +4560,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4572,10 +4575,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4583,7 +4586,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4592,13 +4595,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4607,10 +4610,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4618,7 +4621,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4627,13 +4630,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4642,10 +4645,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4653,7 +4656,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4662,13 +4665,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4677,10 +4680,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4688,7 +4691,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4697,13 +4700,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4712,10 +4715,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4723,7 +4726,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4732,13 +4735,13 @@
         <v>195</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4747,10 +4750,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4758,7 +4761,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4767,13 +4770,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4782,10 +4785,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4793,7 +4796,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4802,13 +4805,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4817,10 +4820,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4828,7 +4831,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4837,13 +4840,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4852,10 +4855,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4863,7 +4866,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4872,13 +4875,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4887,10 +4890,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4898,7 +4901,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4907,13 +4910,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4922,10 +4925,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4933,7 +4936,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4942,13 +4945,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4957,10 +4960,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4968,7 +4971,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -4977,13 +4980,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -4992,10 +4995,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5003,7 +5006,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5012,13 +5015,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5027,10 +5030,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5038,7 +5041,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5047,13 +5050,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5062,10 +5065,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5073,7 +5076,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5085,10 +5088,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5097,10 +5100,10 @@
         <v>149</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5108,7 +5111,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5120,10 +5123,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5132,10 +5135,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5143,7 +5146,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5155,10 +5158,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5167,10 +5170,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5178,7 +5181,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5187,13 +5190,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5202,10 +5205,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5213,7 +5216,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5222,13 +5225,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5237,10 +5240,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5248,7 +5251,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5257,13 +5260,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5272,10 +5275,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5283,7 +5286,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5292,13 +5295,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5307,10 +5310,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5318,7 +5321,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5327,13 +5330,13 @@
         <v>195</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5342,10 +5345,10 @@
         <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5353,7 +5356,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5362,13 +5365,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5377,10 +5380,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5388,7 +5391,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5397,13 +5400,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5412,10 +5415,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5423,7 +5426,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5432,13 +5435,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5447,10 +5450,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5458,22 +5461,22 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5482,10 +5485,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5493,7 +5496,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5505,10 +5508,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5517,10 +5520,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5528,22 +5531,22 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5552,10 +5555,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5563,7 +5566,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5575,10 +5578,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5587,10 +5590,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5598,22 +5601,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5625,7 +5628,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5633,22 +5636,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5660,7 +5663,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5668,22 +5671,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5692,10 +5695,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5703,22 +5706,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5727,10 +5730,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5738,22 +5741,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5762,10 +5765,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5773,22 +5776,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5800,7 +5803,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5808,22 +5811,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5835,7 +5838,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5843,22 +5846,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5867,10 +5870,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5878,22 +5881,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5902,10 +5905,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5913,10 +5916,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5925,10 +5928,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5937,10 +5940,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -5980,12 +5983,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -5999,19 +6002,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6034,10 +6037,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6060,10 +6063,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6086,10 +6089,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>497</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6112,7 +6115,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6136,7 +6139,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6160,10 +6163,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>497</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6186,7 +6189,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6210,7 +6213,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6234,10 +6237,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>498</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>497</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6260,7 +6263,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6284,7 +6287,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6308,7 +6311,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6332,7 +6335,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6356,15 +6359,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6372,7 +6375,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6380,7 +6383,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6409,7 +6412,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6426,10 +6429,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6437,7 +6440,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6446,10 +6449,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6457,7 +6460,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6469,7 +6472,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,7 +6480,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6486,10 +6489,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6497,7 +6500,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6506,10 +6509,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6523,18 +6526,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6543,53 +6546,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
   </sheetData>
@@ -6614,26 +6617,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6641,13 +6644,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6655,13 +6658,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6669,13 +6672,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6683,13 +6686,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6697,13 +6700,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6711,13 +6714,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6725,13 +6728,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6739,13 +6742,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6753,13 +6756,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6767,13 +6770,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6781,21 +6784,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6831,7 +6834,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6839,7 +6842,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6851,167 +6854,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
   </sheetData>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7063,47 +7066,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7114,16 +7117,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7131,19 +7134,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7151,19 +7154,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7171,19 +7174,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="585">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -633,6 +633,9 @@
   </si>
   <si>
     <t>A PR produces a preview URL and a green check</t>
+  </si>
+  <si>
+    <t>✅ Done (a469d5e)</t>
   </si>
   <si>
     <t>W00-13</t>
@@ -3566,12 +3569,12 @@
         <v>203</v>
       </c>
       <c r="K16" s="11" t="s">
-        <v>151</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B17" s="11" t="s">
         <v>51</v>
@@ -3583,10 +3586,10 @@
         <v>146</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G17" s="12">
         <v>0.75</v>
@@ -3598,7 +3601,7 @@
         <v>200</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>151</v>
@@ -3606,7 +3609,7 @@
     </row>
     <row r="18" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>51</v>
@@ -3618,10 +3621,10 @@
         <v>146</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G18" s="12">
         <v>0.5</v>
@@ -3630,10 +3633,10 @@
         <v>149</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>151</v>
@@ -3641,7 +3644,7 @@
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>51</v>
@@ -3650,13 +3653,13 @@
         <v>195</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G19" s="12">
         <v>0.5</v>
@@ -3668,15 +3671,15 @@
         <v>61</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>51</v>
@@ -3688,10 +3691,10 @@
         <v>190</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G20" s="12">
         <v>0.25</v>
@@ -3703,7 +3706,7 @@
         <v>189</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>151</v>
@@ -3711,7 +3714,7 @@
     </row>
     <row r="21" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>51</v>
@@ -3723,10 +3726,10 @@
         <v>70</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G21" s="12">
         <v>0.5</v>
@@ -3735,10 +3738,10 @@
         <v>149</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>151</v>
@@ -3746,7 +3749,7 @@
     </row>
     <row r="22" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>51</v>
@@ -3758,10 +3761,10 @@
         <v>177</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G22" s="12">
         <v>0.25</v>
@@ -3773,7 +3776,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>151</v>
@@ -3781,7 +3784,7 @@
     </row>
     <row r="23" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>51</v>
@@ -3793,10 +3796,10 @@
         <v>107</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G23" s="12">
         <v>0.5</v>
@@ -3808,30 +3811,30 @@
         <v>61</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G24" s="12">
         <v>0.25</v>
@@ -3840,10 +3843,10 @@
         <v>149</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>151</v>
@@ -3851,7 +3854,7 @@
     </row>
     <row r="25" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>57</v>
@@ -3863,10 +3866,10 @@
         <v>146</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G25" s="12">
         <v>3</v>
@@ -3878,7 +3881,7 @@
         <v>144</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>151</v>
@@ -3886,7 +3889,7 @@
     </row>
     <row r="26" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>57</v>
@@ -3898,10 +3901,10 @@
         <v>146</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G26" s="12">
         <v>2</v>
@@ -3910,10 +3913,10 @@
         <v>149</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>151</v>
@@ -3921,7 +3924,7 @@
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>57</v>
@@ -3933,10 +3936,10 @@
         <v>146</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G27" s="12">
         <v>0.75</v>
@@ -3945,10 +3948,10 @@
         <v>149</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>151</v>
@@ -3956,7 +3959,7 @@
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>63</v>
@@ -3968,10 +3971,10 @@
         <v>146</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G28" s="12">
         <v>2</v>
@@ -3980,10 +3983,10 @@
         <v>149</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>151</v>
@@ -3991,7 +3994,7 @@
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>63</v>
@@ -4003,10 +4006,10 @@
         <v>146</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -4015,10 +4018,10 @@
         <v>149</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>151</v>
@@ -4026,7 +4029,7 @@
     </row>
     <row r="30" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>63</v>
@@ -4038,10 +4041,10 @@
         <v>146</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -4050,10 +4053,10 @@
         <v>149</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>151</v>
@@ -4061,7 +4064,7 @@
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>63</v>
@@ -4073,10 +4076,10 @@
         <v>146</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
@@ -4085,10 +4088,10 @@
         <v>149</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>151</v>
@@ -4096,7 +4099,7 @@
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>63</v>
@@ -4108,10 +4111,10 @@
         <v>70</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G32" s="12">
         <v>0.5</v>
@@ -4120,10 +4123,10 @@
         <v>149</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>151</v>
@@ -4131,7 +4134,7 @@
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>68</v>
@@ -4143,10 +4146,10 @@
         <v>70</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G33" s="12">
         <v>2</v>
@@ -4155,10 +4158,10 @@
         <v>149</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>151</v>
@@ -4166,7 +4169,7 @@
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
@@ -4178,10 +4181,10 @@
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4190,10 +4193,10 @@
         <v>149</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>151</v>
@@ -4201,7 +4204,7 @@
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4213,10 +4216,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4225,10 +4228,10 @@
         <v>149</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4236,7 +4239,7 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4248,10 +4251,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4260,10 +4263,10 @@
         <v>149</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>151</v>
@@ -4271,7 +4274,7 @@
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4280,13 +4283,13 @@
         <v>195</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4295,10 +4298,10 @@
         <v>149</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4306,7 +4309,7 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4315,13 +4318,13 @@
         <v>195</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4330,10 +4333,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4341,7 +4344,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4350,13 +4353,13 @@
         <v>195</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4365,10 +4368,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4376,7 +4379,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4385,13 +4388,13 @@
         <v>195</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4400,10 +4403,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4411,7 +4414,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4420,13 +4423,13 @@
         <v>195</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4435,10 +4438,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4446,7 +4449,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4455,13 +4458,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4470,10 +4473,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4481,7 +4484,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4490,13 +4493,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4505,10 +4508,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4516,7 +4519,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4525,13 +4528,13 @@
         <v>195</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4540,10 +4543,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4551,7 +4554,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4560,13 +4563,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4575,10 +4578,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4586,7 +4589,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4595,13 +4598,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4610,10 +4613,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4621,7 +4624,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4630,13 +4633,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4645,10 +4648,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4656,7 +4659,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4665,13 +4668,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4680,10 +4683,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4691,7 +4694,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4700,13 +4703,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4715,10 +4718,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4726,7 +4729,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4735,13 +4738,13 @@
         <v>195</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4750,10 +4753,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4761,7 +4764,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4770,13 +4773,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4785,10 +4788,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4796,7 +4799,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4805,13 +4808,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4820,10 +4823,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4831,7 +4834,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4840,13 +4843,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4855,10 +4858,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4866,7 +4869,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4875,13 +4878,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4890,10 +4893,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4901,7 +4904,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4910,13 +4913,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4925,10 +4928,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4936,7 +4939,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4945,13 +4948,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4960,10 +4963,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4971,7 +4974,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -4980,13 +4983,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -4995,10 +4998,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5006,7 +5009,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5015,13 +5018,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5030,10 +5033,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5041,7 +5044,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5050,13 +5053,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5065,10 +5068,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5076,7 +5079,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5088,10 +5091,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5100,10 +5103,10 @@
         <v>149</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5111,7 +5114,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5123,10 +5126,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5135,10 +5138,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5146,7 +5149,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5158,10 +5161,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5170,10 +5173,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5181,7 +5184,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5190,13 +5193,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5205,10 +5208,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5216,7 +5219,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5225,13 +5228,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5240,10 +5243,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5251,7 +5254,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5260,13 +5263,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5275,10 +5278,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5286,7 +5289,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5295,13 +5298,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5310,10 +5313,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5321,7 +5324,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5330,13 +5333,13 @@
         <v>195</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5345,10 +5348,10 @@
         <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5356,7 +5359,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5365,13 +5368,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5380,10 +5383,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5391,7 +5394,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5400,13 +5403,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5415,10 +5418,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5426,7 +5429,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5435,13 +5438,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5450,10 +5453,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5461,22 +5464,22 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5485,10 +5488,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5496,7 +5499,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5508,10 +5511,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5520,10 +5523,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5531,22 +5534,22 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5555,10 +5558,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5566,7 +5569,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5578,10 +5581,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5590,10 +5593,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5601,22 +5604,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5628,7 +5631,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5636,22 +5639,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5663,7 +5666,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5671,22 +5674,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5695,10 +5698,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5706,22 +5709,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5730,10 +5733,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5741,22 +5744,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5765,10 +5768,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5776,22 +5779,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5803,7 +5806,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5811,22 +5814,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5838,7 +5841,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5846,22 +5849,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5870,10 +5873,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5881,22 +5884,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5905,10 +5908,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5916,10 +5919,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5928,10 +5931,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5940,10 +5943,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -5983,12 +5986,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6002,19 +6005,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6037,10 +6040,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6063,10 +6066,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6089,10 +6092,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>499</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>498</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6115,7 +6118,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6139,7 +6142,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6163,10 +6166,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>499</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>498</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6189,7 +6192,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6213,7 +6216,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6237,10 +6240,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>499</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>498</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6263,7 +6266,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6287,7 +6290,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6311,7 +6314,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6335,7 +6338,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6359,15 +6362,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6375,7 +6378,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6383,7 +6386,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6412,7 +6415,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6429,10 +6432,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6440,7 +6443,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6449,10 +6452,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6460,7 +6463,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6472,7 +6475,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6480,7 +6483,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6489,10 +6492,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6500,7 +6503,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6509,10 +6512,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6526,18 +6529,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6546,53 +6549,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>
@@ -6617,26 +6620,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6644,13 +6647,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6658,13 +6661,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6672,13 +6675,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6686,13 +6689,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6700,13 +6703,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6714,13 +6717,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6728,13 +6731,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6742,13 +6745,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6756,13 +6759,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6770,13 +6773,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6784,21 +6787,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6834,7 +6837,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6842,7 +6845,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6854,167 +6857,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -7046,7 +7049,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7066,47 +7069,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7117,16 +7120,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7134,19 +7137,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7154,19 +7157,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7174,19 +7177,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="588">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -761,6 +761,9 @@
     <t>Runs clean from an empty database; ERD committed</t>
   </si>
   <si>
+    <t>Done (PR #5 — 25/25 db incl. clean-from-empty on scratch; 4 review rounds)</t>
+  </si>
+  <si>
     <t>S01-02</t>
   </si>
   <si>
@@ -773,6 +776,9 @@
     <t>A query without tenant context returns zero rows</t>
   </si>
   <si>
+    <t>Done (PR #5 — zero-row AC asserted on all 21 tenant tables + withTenant guard)</t>
+  </si>
+  <si>
     <t>S01-03</t>
   </si>
   <si>
@@ -783,6 +789,9 @@
   </si>
   <si>
     <t>Suite runs in CI and fails the build on a leak</t>
+  </si>
+  <si>
+    <t>Done (PR #5 — policy-derived enumeration + leak sweep + ci db-test job, 5 review rounds)</t>
   </si>
   <si>
     <t>S02-01</t>
@@ -3884,12 +3893,12 @@
         <v>245</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>151</v>
+        <v>246</v>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>57</v>
@@ -3901,10 +3910,10 @@
         <v>146</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G26" s="12">
         <v>2</v>
@@ -3916,15 +3925,15 @@
         <v>242</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>57</v>
@@ -3936,10 +3945,10 @@
         <v>146</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G27" s="12">
         <v>0.75</v>
@@ -3948,18 +3957,18 @@
         <v>149</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>63</v>
@@ -3971,10 +3980,10 @@
         <v>146</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="G28" s="12">
         <v>2</v>
@@ -3986,7 +3995,7 @@
         <v>242</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>151</v>
@@ -3994,7 +4003,7 @@
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>63</v>
@@ -4006,10 +4015,10 @@
         <v>146</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -4018,10 +4027,10 @@
         <v>149</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>151</v>
@@ -4029,7 +4038,7 @@
     </row>
     <row r="30" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>63</v>
@@ -4041,10 +4050,10 @@
         <v>146</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -4056,7 +4065,7 @@
         <v>242</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>151</v>
@@ -4064,7 +4073,7 @@
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>63</v>
@@ -4076,10 +4085,10 @@
         <v>146</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
@@ -4091,7 +4100,7 @@
         <v>242</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>151</v>
@@ -4099,7 +4108,7 @@
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>63</v>
@@ -4111,10 +4120,10 @@
         <v>70</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G32" s="12">
         <v>0.5</v>
@@ -4123,10 +4132,10 @@
         <v>149</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>151</v>
@@ -4134,7 +4143,7 @@
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>68</v>
@@ -4146,10 +4155,10 @@
         <v>70</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G33" s="12">
         <v>2</v>
@@ -4161,7 +4170,7 @@
         <v>242</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>151</v>
@@ -4169,7 +4178,7 @@
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
@@ -4181,10 +4190,10 @@
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4193,10 +4202,10 @@
         <v>149</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>151</v>
@@ -4204,7 +4213,7 @@
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4216,10 +4225,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4228,10 +4237,10 @@
         <v>149</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4239,7 +4248,7 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4251,10 +4260,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4263,10 +4272,10 @@
         <v>149</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>151</v>
@@ -4274,7 +4283,7 @@
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4286,10 +4295,10 @@
         <v>214</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4298,10 +4307,10 @@
         <v>149</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4309,7 +4318,7 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4321,10 +4330,10 @@
         <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4333,10 +4342,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4344,7 +4353,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4356,10 +4365,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4368,10 +4377,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4379,7 +4388,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4391,10 +4400,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4403,10 +4412,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4414,7 +4423,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4426,10 +4435,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4438,10 +4447,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4449,7 +4458,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4458,13 +4467,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4473,10 +4482,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4484,7 +4493,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4493,13 +4502,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4508,10 +4517,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4519,7 +4528,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4531,10 +4540,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4543,10 +4552,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4554,7 +4563,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4563,13 +4572,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4578,10 +4587,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4589,7 +4598,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4598,13 +4607,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4613,10 +4622,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4624,7 +4633,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4633,13 +4642,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4648,10 +4657,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4659,7 +4668,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4668,13 +4677,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4683,10 +4692,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4694,7 +4703,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4703,13 +4712,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4718,10 +4727,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4729,7 +4738,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4741,10 +4750,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4753,10 +4762,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4764,7 +4773,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4773,13 +4782,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4788,10 +4797,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4799,7 +4808,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4808,13 +4817,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4823,10 +4832,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4834,7 +4843,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4843,13 +4852,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4858,10 +4867,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4869,7 +4878,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4878,13 +4887,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4893,10 +4902,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4904,7 +4913,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4913,13 +4922,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4928,10 +4937,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4939,7 +4948,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4948,13 +4957,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4963,10 +4972,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4974,7 +4983,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -4983,13 +4992,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -4998,10 +5007,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5009,7 +5018,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5018,13 +5027,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5033,10 +5042,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5044,7 +5053,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5053,13 +5062,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5068,10 +5077,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5079,7 +5088,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5091,10 +5100,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5106,7 +5115,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5114,7 +5123,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5126,10 +5135,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5138,10 +5147,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5149,7 +5158,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5161,10 +5170,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5173,10 +5182,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5184,7 +5193,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5193,13 +5202,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5208,10 +5217,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5219,7 +5228,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5228,13 +5237,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5243,10 +5252,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5254,7 +5263,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5263,13 +5272,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5278,10 +5287,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5289,7 +5298,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5298,13 +5307,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5313,10 +5322,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5324,7 +5333,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5336,10 +5345,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5348,10 +5357,10 @@
         <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5359,7 +5368,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5368,13 +5377,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5383,10 +5392,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5394,7 +5403,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5403,13 +5412,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5418,10 +5427,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5429,7 +5438,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5438,13 +5447,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5453,10 +5462,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5464,7 +5473,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5476,10 +5485,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5488,10 +5497,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5499,7 +5508,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5511,10 +5520,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5523,10 +5532,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5534,7 +5543,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5546,10 +5555,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5558,10 +5567,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5569,7 +5578,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5581,10 +5590,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5593,10 +5602,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5604,22 +5613,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5631,7 +5640,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5639,22 +5648,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5666,7 +5675,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5674,22 +5683,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5698,10 +5707,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5709,22 +5718,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5733,10 +5742,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5744,22 +5753,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5768,10 +5777,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5779,22 +5788,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5806,7 +5815,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5814,22 +5823,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5841,7 +5850,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5849,22 +5858,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5873,10 +5882,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5884,22 +5893,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5908,10 +5917,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5919,10 +5928,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5931,10 +5940,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5943,10 +5952,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -5986,12 +5995,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6005,19 +6014,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6040,10 +6049,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6066,10 +6075,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6092,10 +6101,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6118,7 +6127,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6142,7 +6151,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6166,10 +6175,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6192,7 +6201,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6216,7 +6225,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6240,10 +6249,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6266,7 +6275,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6290,7 +6299,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6314,7 +6323,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6338,7 +6347,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6362,15 +6371,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6378,7 +6387,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6386,7 +6395,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6415,7 +6424,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6432,10 +6441,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6443,7 +6452,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6452,10 +6461,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6463,7 +6472,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6475,7 +6484,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6483,7 +6492,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6492,10 +6501,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6503,7 +6512,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6512,10 +6521,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6529,18 +6538,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6549,53 +6558,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -6620,26 +6629,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6647,13 +6656,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6661,13 +6670,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6675,13 +6684,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6689,13 +6698,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6703,13 +6712,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6717,13 +6726,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6731,13 +6740,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6745,13 +6754,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6759,13 +6768,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6773,13 +6782,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6787,21 +6796,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6837,7 +6846,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6845,7 +6854,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6857,167 +6866,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -7049,7 +7058,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7069,47 +7078,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7120,16 +7129,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7137,19 +7146,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7157,19 +7166,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,19 +7186,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="589">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -816,6 +816,9 @@
   </si>
   <si>
     <t>AI policy layer reads settings, does not hardcode</t>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
   <si>
     <t>S02-03</t>
@@ -4033,12 +4036,12 @@
         <v>264</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>151</v>
+        <v>265</v>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>63</v>
@@ -4050,10 +4053,10 @@
         <v>146</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -4065,7 +4068,7 @@
         <v>242</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>151</v>
@@ -4073,7 +4076,7 @@
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>63</v>
@@ -4085,10 +4088,10 @@
         <v>146</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
@@ -4100,7 +4103,7 @@
         <v>242</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>151</v>
@@ -4108,7 +4111,7 @@
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>63</v>
@@ -4120,10 +4123,10 @@
         <v>70</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G32" s="12">
         <v>0.5</v>
@@ -4132,10 +4135,10 @@
         <v>149</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>151</v>
@@ -4143,7 +4146,7 @@
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>68</v>
@@ -4155,10 +4158,10 @@
         <v>70</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G33" s="12">
         <v>2</v>
@@ -4170,7 +4173,7 @@
         <v>242</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>151</v>
@@ -4178,7 +4181,7 @@
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
@@ -4190,10 +4193,10 @@
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4202,10 +4205,10 @@
         <v>149</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>151</v>
@@ -4213,7 +4216,7 @@
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4225,10 +4228,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4237,10 +4240,10 @@
         <v>149</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4248,7 +4251,7 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4260,10 +4263,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4272,10 +4275,10 @@
         <v>149</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>151</v>
@@ -4283,7 +4286,7 @@
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4295,10 +4298,10 @@
         <v>214</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4307,10 +4310,10 @@
         <v>149</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4318,7 +4321,7 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4330,10 +4333,10 @@
         <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4342,10 +4345,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4353,7 +4356,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4365,10 +4368,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4377,10 +4380,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4388,7 +4391,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4400,10 +4403,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4412,10 +4415,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4423,7 +4426,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4435,10 +4438,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4447,10 +4450,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4458,7 +4461,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4467,13 +4470,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4482,10 +4485,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4493,7 +4496,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4502,13 +4505,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4517,10 +4520,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4528,7 +4531,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4540,10 +4543,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4552,10 +4555,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4563,7 +4566,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4572,13 +4575,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4587,10 +4590,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4598,7 +4601,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4607,13 +4610,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4622,10 +4625,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4633,7 +4636,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4642,13 +4645,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4657,10 +4660,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4668,7 +4671,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4677,13 +4680,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4692,10 +4695,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4703,7 +4706,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4712,13 +4715,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4727,10 +4730,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4738,7 +4741,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4750,10 +4753,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4762,10 +4765,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4773,7 +4776,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4782,13 +4785,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4797,10 +4800,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4808,7 +4811,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4817,13 +4820,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4832,10 +4835,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4843,7 +4846,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4852,13 +4855,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4867,10 +4870,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4878,7 +4881,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4887,13 +4890,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4902,10 +4905,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4913,7 +4916,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4922,13 +4925,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4937,10 +4940,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4948,7 +4951,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4957,13 +4960,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4972,10 +4975,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4983,7 +4986,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -4992,13 +4995,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5007,10 +5010,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5018,7 +5021,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5027,13 +5030,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5042,10 +5045,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5053,7 +5056,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5062,13 +5065,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5077,10 +5080,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5088,7 +5091,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5100,10 +5103,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5115,7 +5118,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5123,7 +5126,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5135,10 +5138,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5147,10 +5150,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5158,7 +5161,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5170,10 +5173,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5182,10 +5185,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5193,7 +5196,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5202,13 +5205,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5217,10 +5220,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5228,7 +5231,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5237,13 +5240,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5252,10 +5255,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5263,7 +5266,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5272,13 +5275,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5287,10 +5290,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5298,7 +5301,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5307,13 +5310,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5322,10 +5325,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5333,7 +5336,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5345,10 +5348,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5357,10 +5360,10 @@
         <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5368,7 +5371,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5377,13 +5380,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5392,10 +5395,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5403,7 +5406,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5412,13 +5415,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5427,10 +5430,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5438,7 +5441,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5447,13 +5450,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5462,10 +5465,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5473,7 +5476,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5485,10 +5488,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5497,10 +5500,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5508,7 +5511,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5520,10 +5523,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5532,10 +5535,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5555,10 +5558,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5567,10 +5570,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5578,7 +5581,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5590,10 +5593,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5602,10 +5605,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5613,22 +5616,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5640,7 +5643,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5648,22 +5651,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5675,7 +5678,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5683,22 +5686,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5707,10 +5710,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5718,22 +5721,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5742,10 +5745,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5753,22 +5756,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5777,10 +5780,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5788,22 +5791,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5815,7 +5818,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5823,22 +5826,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5850,7 +5853,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5858,22 +5861,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5882,10 +5885,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5893,22 +5896,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5917,10 +5920,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5928,10 +5931,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5940,10 +5943,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5952,10 +5955,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -5995,12 +5998,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6014,19 +6017,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6049,10 +6052,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6075,10 +6078,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6101,10 +6104,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>502</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6127,7 +6130,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6151,7 +6154,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6175,10 +6178,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>502</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6201,7 +6204,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6225,7 +6228,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6249,10 +6252,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>503</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>502</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6275,7 +6278,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6299,7 +6302,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6323,7 +6326,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6347,7 +6350,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6371,15 +6374,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6387,7 +6390,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6395,7 +6398,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6424,7 +6427,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6441,10 +6444,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6452,7 +6455,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6461,10 +6464,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6472,7 +6475,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6484,7 +6487,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6492,7 +6495,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6501,10 +6504,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6512,7 +6515,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6521,10 +6524,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6538,18 +6541,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6558,53 +6561,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
   </sheetData>
@@ -6629,26 +6632,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6656,13 +6659,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6670,13 +6673,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6684,13 +6687,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6698,13 +6701,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6712,13 +6715,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6726,13 +6729,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6740,13 +6743,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6754,13 +6757,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6768,13 +6771,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6782,13 +6785,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6796,21 +6799,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6846,7 +6849,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6854,7 +6857,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6866,167 +6869,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -7058,7 +7061,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7078,47 +7081,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7129,16 +7132,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7146,19 +7149,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7166,19 +7169,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7186,19 +7189,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -4071,7 +4071,7 @@
         <v>269</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>151</v>
+        <v>265</v>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -4106,7 +4106,7 @@
         <v>273</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>151</v>
+        <v>265</v>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -4141,7 +4141,7 @@
         <v>277</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>151</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="590">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -867,6 +867,9 @@
   </si>
   <si>
     <t>Editing never alters a historical version</t>
+  </si>
+  <si>
+    <t>Done (2026-10-24) - article create/edit/list/version services; 95 db / 120 unit</t>
   </si>
   <si>
     <t>S03-02</t>
@@ -4176,12 +4179,12 @@
         <v>281</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>151</v>
+        <v>282</v>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
@@ -4193,10 +4196,10 @@
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4208,7 +4211,7 @@
         <v>278</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>151</v>
@@ -4216,7 +4219,7 @@
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4228,10 +4231,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4243,7 +4246,7 @@
         <v>278</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4251,7 +4254,7 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4263,10 +4266,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4278,7 +4281,7 @@
         <v>278</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>151</v>
@@ -4286,7 +4289,7 @@
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4298,10 +4301,10 @@
         <v>214</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4313,7 +4316,7 @@
         <v>278</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4321,7 +4324,7 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4333,10 +4336,10 @@
         <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4345,10 +4348,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4356,7 +4359,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4368,10 +4371,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4380,10 +4383,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4391,7 +4394,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4403,10 +4406,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4415,10 +4418,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4426,7 +4429,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4438,10 +4441,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4450,10 +4453,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4461,7 +4464,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4470,13 +4473,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4485,10 +4488,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4496,7 +4499,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4505,13 +4508,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4520,10 +4523,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4531,7 +4534,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4543,10 +4546,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4555,10 +4558,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4566,7 +4569,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4575,13 +4578,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4590,10 +4593,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4601,7 +4604,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4610,13 +4613,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4625,10 +4628,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4636,7 +4639,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4645,13 +4648,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4660,10 +4663,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4671,7 +4674,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4680,13 +4683,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4695,10 +4698,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4706,7 +4709,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4715,13 +4718,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4730,10 +4733,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4741,7 +4744,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4753,10 +4756,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4765,10 +4768,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4776,7 +4779,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4785,13 +4788,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4800,10 +4803,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4811,7 +4814,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4820,13 +4823,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4835,10 +4838,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4846,7 +4849,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4855,13 +4858,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4870,10 +4873,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4881,7 +4884,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4890,13 +4893,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4905,10 +4908,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4916,7 +4919,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4925,13 +4928,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4940,10 +4943,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4951,7 +4954,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4960,13 +4963,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4975,10 +4978,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4986,7 +4989,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -4995,13 +4998,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5010,10 +5013,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5021,7 +5024,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5030,13 +5033,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5045,10 +5048,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5056,7 +5059,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5065,13 +5068,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5080,10 +5083,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5091,7 +5094,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5103,10 +5106,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5118,7 +5121,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5126,7 +5129,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5138,10 +5141,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5150,10 +5153,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5161,7 +5164,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5173,10 +5176,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5185,10 +5188,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5196,7 +5199,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5205,13 +5208,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5220,10 +5223,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5231,7 +5234,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5240,13 +5243,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5255,10 +5258,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5266,7 +5269,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5275,13 +5278,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5290,10 +5293,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5301,7 +5304,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5310,13 +5313,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5325,10 +5328,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5336,7 +5339,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5348,10 +5351,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5363,7 +5366,7 @@
         <v>274</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5371,7 +5374,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5380,13 +5383,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5395,10 +5398,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5406,7 +5409,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5415,13 +5418,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5430,10 +5433,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5441,7 +5444,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5450,13 +5453,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5465,10 +5468,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5476,7 +5479,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5488,10 +5491,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5500,10 +5503,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5511,7 +5514,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5523,10 +5526,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5535,10 +5538,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5546,7 +5549,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5558,10 +5561,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5570,10 +5573,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5581,7 +5584,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5593,10 +5596,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5605,10 +5608,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5616,22 +5619,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5643,7 +5646,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5651,22 +5654,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5678,7 +5681,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5686,22 +5689,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5710,10 +5713,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5721,22 +5724,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5745,10 +5748,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5756,22 +5759,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5780,10 +5783,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5791,22 +5794,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5818,7 +5821,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5826,22 +5829,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5853,7 +5856,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5861,22 +5864,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5885,10 +5888,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5896,22 +5899,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5920,10 +5923,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5931,10 +5934,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5943,10 +5946,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5955,10 +5958,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -5998,12 +6001,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6017,19 +6020,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6052,10 +6055,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6078,10 +6081,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6104,10 +6107,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>503</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6130,7 +6133,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6154,7 +6157,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6178,10 +6181,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>503</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6204,7 +6207,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6228,7 +6231,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6252,10 +6255,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>503</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6278,7 +6281,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6302,7 +6305,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6326,7 +6329,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6350,7 +6353,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6374,15 +6377,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6390,7 +6393,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6398,7 +6401,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6427,7 +6430,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6444,10 +6447,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6455,7 +6458,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6464,10 +6467,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6475,7 +6478,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6487,7 +6490,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6495,7 +6498,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6504,10 +6507,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,7 +6518,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6524,10 +6527,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6541,18 +6544,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6561,53 +6564,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -6632,26 +6635,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6659,13 +6662,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6673,13 +6676,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6687,13 +6690,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6701,13 +6704,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6715,13 +6718,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6729,13 +6732,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6743,13 +6746,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6757,13 +6760,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,13 +6774,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6785,13 +6788,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6799,21 +6802,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6849,7 +6852,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6857,7 +6860,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6869,167 +6872,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -7061,7 +7064,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7081,47 +7084,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7132,16 +7135,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7149,19 +7152,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7169,19 +7172,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7189,19 +7192,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="590">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="591">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -882,6 +882,9 @@
   </si>
   <si>
     <t>A 100-row CSV imports with a preview step and no silent failures</t>
+  </si>
+  <si>
+    <t>Done (2026-10-25) - RFC 4180 parser + pure preview, atomic commit; 107 db / 138 unit (PR #30)</t>
   </si>
   <si>
     <t>S03-03</t>
@@ -4214,12 +4217,12 @@
         <v>286</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>151</v>
+        <v>287</v>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4231,10 +4234,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4246,7 +4249,7 @@
         <v>278</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4254,7 +4257,7 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4266,10 +4269,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4281,7 +4284,7 @@
         <v>278</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>151</v>
@@ -4289,7 +4292,7 @@
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4301,10 +4304,10 @@
         <v>214</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4316,7 +4319,7 @@
         <v>278</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4324,7 +4327,7 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4336,10 +4339,10 @@
         <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4348,10 +4351,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4359,7 +4362,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4371,10 +4374,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4383,10 +4386,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4394,7 +4397,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4406,10 +4409,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4418,10 +4421,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4429,7 +4432,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4441,10 +4444,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4453,10 +4456,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4464,7 +4467,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4473,13 +4476,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4488,10 +4491,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4499,7 +4502,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4508,13 +4511,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4523,10 +4526,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4534,7 +4537,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4546,10 +4549,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4558,10 +4561,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4569,7 +4572,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4578,13 +4581,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4593,10 +4596,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4604,7 +4607,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4613,13 +4616,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4628,10 +4631,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4639,7 +4642,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4648,13 +4651,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4663,10 +4666,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4674,7 +4677,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4683,13 +4686,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4698,10 +4701,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4709,7 +4712,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4718,13 +4721,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4733,10 +4736,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4744,7 +4747,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4756,10 +4759,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4768,10 +4771,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4779,7 +4782,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4788,13 +4791,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4803,10 +4806,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4814,7 +4817,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4823,13 +4826,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4838,10 +4841,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4849,7 +4852,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4858,13 +4861,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4873,10 +4876,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4884,7 +4887,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4893,13 +4896,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4908,10 +4911,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4919,7 +4922,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4928,13 +4931,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4943,10 +4946,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4954,7 +4957,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4963,13 +4966,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4978,10 +4981,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4989,7 +4992,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -4998,13 +5001,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5013,10 +5016,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5024,7 +5027,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5033,13 +5036,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5048,10 +5051,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5059,7 +5062,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5068,13 +5071,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5083,10 +5086,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5094,7 +5097,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5106,10 +5109,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5121,7 +5124,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5129,7 +5132,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5141,10 +5144,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5153,10 +5156,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5164,7 +5167,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5176,10 +5179,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5188,10 +5191,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5199,7 +5202,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5208,13 +5211,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5223,10 +5226,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5234,7 +5237,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5243,13 +5246,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5258,10 +5261,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5269,7 +5272,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5278,13 +5281,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5293,10 +5296,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5304,7 +5307,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5313,13 +5316,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5328,10 +5331,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5339,7 +5342,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5351,10 +5354,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5366,7 +5369,7 @@
         <v>274</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5374,7 +5377,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5383,13 +5386,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5398,10 +5401,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5409,7 +5412,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5418,13 +5421,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5433,10 +5436,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5444,7 +5447,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5453,13 +5456,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5468,10 +5471,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5479,7 +5482,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5491,10 +5494,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5503,10 +5506,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5514,7 +5517,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5526,10 +5529,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5538,10 +5541,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5549,7 +5552,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5561,10 +5564,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5573,10 +5576,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5584,7 +5587,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5596,10 +5599,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5608,10 +5611,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5619,22 +5622,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5646,7 +5649,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5654,22 +5657,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5681,7 +5684,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5689,22 +5692,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5713,10 +5716,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5724,22 +5727,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5748,10 +5751,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5759,22 +5762,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5783,10 +5786,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5794,22 +5797,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5821,7 +5824,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5829,22 +5832,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5856,7 +5859,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5864,22 +5867,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5888,10 +5891,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5899,22 +5902,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5923,10 +5926,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5934,10 +5937,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5946,10 +5949,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5958,10 +5961,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6001,12 +6004,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6020,19 +6023,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6055,10 +6058,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6081,10 +6084,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6107,10 +6110,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>504</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6133,7 +6136,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6157,7 +6160,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6181,10 +6184,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>504</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6207,7 +6210,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6231,7 +6234,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6255,10 +6258,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>505</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>504</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6281,7 +6284,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6305,7 +6308,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6329,7 +6332,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6353,7 +6356,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6377,15 +6380,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6393,7 +6396,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6401,7 +6404,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6430,7 +6433,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6447,10 +6450,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6458,7 +6461,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6467,10 +6470,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6478,7 +6481,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6490,7 +6493,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6498,7 +6501,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6507,10 +6510,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6518,7 +6521,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6527,10 +6530,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6544,18 +6547,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6564,53 +6567,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -6635,26 +6638,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6662,13 +6665,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6676,13 +6679,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6690,13 +6693,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6704,13 +6707,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6718,13 +6721,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6732,13 +6735,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6746,13 +6749,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6760,13 +6763,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6774,13 +6777,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6788,13 +6791,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6802,21 +6805,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6852,7 +6855,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6860,7 +6863,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6872,167 +6875,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
@@ -7064,7 +7067,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7084,47 +7087,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7135,16 +7138,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7152,19 +7155,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7172,19 +7175,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7192,19 +7195,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="593">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -806,6 +806,9 @@
     <t>Each role can only reach its own surface</t>
   </si>
   <si>
+    <t>✅ Done (2026-10-25: requireRole is called by src/knowledge/review.ts on every review route; tests/db/role-denial.db.test.ts proves front_desk/observer 403 with zero writes — S02-06 / issue #14)</t>
+  </si>
+  <si>
     <t>S02-02</t>
   </si>
   <si>
@@ -909,6 +912,9 @@
   </si>
   <si>
     <t>A contradictory pair is blocked until a human resolves it</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-25: review queue + approve/reject + fact_resolutions, 10 denial DB tests, Next.js screen in web/; db:test 137, npm test 277)</t>
   </si>
   <si>
     <t>S04-02</t>
@@ -4007,12 +4013,12 @@
         <v>260</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>151</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>63</v>
@@ -4024,10 +4030,10 @@
         <v>146</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -4039,15 +4045,15 @@
         <v>257</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>63</v>
@@ -4059,10 +4065,10 @@
         <v>146</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -4074,15 +4080,15 @@
         <v>242</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>63</v>
@@ -4094,10 +4100,10 @@
         <v>146</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
@@ -4109,15 +4115,15 @@
         <v>242</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>63</v>
@@ -4129,10 +4135,10 @@
         <v>70</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G32" s="12">
         <v>0.5</v>
@@ -4141,18 +4147,18 @@
         <v>149</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>68</v>
@@ -4164,10 +4170,10 @@
         <v>70</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G33" s="12">
         <v>2</v>
@@ -4179,15 +4185,15 @@
         <v>242</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
@@ -4199,10 +4205,10 @@
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4211,18 +4217,18 @@
         <v>149</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4234,10 +4240,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4246,10 +4252,10 @@
         <v>149</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>151</v>
@@ -4257,7 +4263,7 @@
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4269,10 +4275,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4281,18 +4287,18 @@
         <v>149</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>151</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4304,10 +4310,10 @@
         <v>214</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4316,10 +4322,10 @@
         <v>149</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>151</v>
@@ -4327,7 +4333,7 @@
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4339,10 +4345,10 @@
         <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4351,10 +4357,10 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4362,7 +4368,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4374,10 +4380,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4386,10 +4392,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4397,7 +4403,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4409,10 +4415,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4421,10 +4427,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4432,7 +4438,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4444,10 +4450,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4456,10 +4462,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4467,7 +4473,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4476,13 +4482,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4491,10 +4497,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4502,7 +4508,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4511,13 +4517,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4526,10 +4532,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4537,7 +4543,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4549,10 +4555,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4561,10 +4567,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4572,7 +4578,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4581,13 +4587,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4596,10 +4602,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4607,7 +4613,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4616,13 +4622,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4631,10 +4637,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4642,7 +4648,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4651,13 +4657,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4666,10 +4672,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4677,7 +4683,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4686,13 +4692,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4701,10 +4707,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4712,7 +4718,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4721,13 +4727,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4736,10 +4742,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4747,7 +4753,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4759,10 +4765,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4771,10 +4777,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4782,7 +4788,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4791,13 +4797,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4806,10 +4812,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4817,7 +4823,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4826,13 +4832,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4841,10 +4847,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4852,7 +4858,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4861,13 +4867,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4876,10 +4882,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4887,7 +4893,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4896,13 +4902,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4911,10 +4917,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4922,7 +4928,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4931,13 +4937,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4946,10 +4952,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4957,7 +4963,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4966,13 +4972,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4981,10 +4987,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4992,7 +4998,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5001,13 +5007,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5016,10 +5022,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5027,7 +5033,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5036,13 +5042,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5051,10 +5057,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5062,7 +5068,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5071,13 +5077,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5086,10 +5092,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5097,7 +5103,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5109,10 +5115,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5124,7 +5130,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5132,7 +5138,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5144,10 +5150,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5156,10 +5162,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5167,7 +5173,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5179,10 +5185,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5191,10 +5197,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5202,7 +5208,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5211,13 +5217,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5226,10 +5232,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5237,7 +5243,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5246,13 +5252,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5261,10 +5267,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5272,7 +5278,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5281,13 +5287,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5296,10 +5302,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5307,7 +5313,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5316,13 +5322,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5331,10 +5337,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5342,7 +5348,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5354,10 +5360,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5366,10 +5372,10 @@
         <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5377,7 +5383,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5386,13 +5392,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5401,10 +5407,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5412,7 +5418,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5421,13 +5427,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5436,10 +5442,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5447,7 +5453,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5456,13 +5462,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5471,10 +5477,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5482,7 +5488,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5494,10 +5500,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5506,10 +5512,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5517,7 +5523,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5529,10 +5535,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5541,10 +5547,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5552,7 +5558,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5564,10 +5570,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5576,10 +5582,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5587,7 +5593,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5599,10 +5605,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5611,10 +5617,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5622,22 +5628,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5649,7 +5655,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5657,22 +5663,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5684,7 +5690,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5692,22 +5698,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5716,10 +5722,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5727,22 +5733,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5751,10 +5757,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5762,22 +5768,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5786,10 +5792,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5797,22 +5803,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5824,7 +5830,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5832,22 +5838,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5859,7 +5865,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5867,22 +5873,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5891,10 +5897,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5902,22 +5908,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5926,10 +5932,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5937,10 +5943,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5949,10 +5955,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5961,10 +5967,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6004,12 +6010,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6023,19 +6029,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6058,10 +6064,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6084,10 +6090,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6110,10 +6116,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6136,7 +6142,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6160,7 +6166,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6184,10 +6190,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6210,7 +6216,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6234,7 +6240,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6258,10 +6264,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6284,7 +6290,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6308,7 +6314,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6332,7 +6338,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6356,7 +6362,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6380,15 +6386,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6396,7 +6402,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6404,7 +6410,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6433,7 +6439,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6450,10 +6456,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6461,7 +6467,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6470,10 +6476,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6481,7 +6487,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6493,7 +6499,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6501,7 +6507,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6510,10 +6516,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6521,7 +6527,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6530,10 +6536,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6547,18 +6553,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6567,53 +6573,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
   </sheetData>
@@ -6638,26 +6644,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6665,13 +6671,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6679,13 +6685,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6693,13 +6699,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6707,13 +6713,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6721,13 +6727,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6735,13 +6741,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6749,13 +6755,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6763,13 +6769,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6777,13 +6783,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6791,13 +6797,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6805,21 +6811,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6855,7 +6861,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6863,7 +6869,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6875,167 +6881,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
@@ -7067,7 +7073,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7087,47 +7093,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7138,16 +7144,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7155,19 +7161,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7175,19 +7181,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7195,19 +7201,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="594">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -927,6 +927,9 @@
   </si>
   <si>
     <t>Every published version is chunked and embedded</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-25: 0011_article_chunks + chunkAndPublish/backfillChunks + fetch provider adapter (DEC-3 OpenAI text-embedding-3-small); db:test 152, npm test 293)</t>
   </si>
   <si>
     <t>S04-03</t>
@@ -4328,12 +4331,12 @@
         <v>301</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>151</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4345,10 +4348,10 @@
         <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4360,7 +4363,7 @@
         <v>298</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>151</v>
@@ -4368,7 +4371,7 @@
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4380,10 +4383,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4392,10 +4395,10 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4403,7 +4406,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4415,10 +4418,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4427,10 +4430,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4438,7 +4441,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4450,10 +4453,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4462,10 +4465,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4473,7 +4476,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4482,13 +4485,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4497,10 +4500,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4508,7 +4511,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4517,13 +4520,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4532,10 +4535,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4543,7 +4546,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4555,10 +4558,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4567,10 +4570,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4578,7 +4581,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4587,13 +4590,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4602,10 +4605,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4613,7 +4616,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4622,13 +4625,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4637,10 +4640,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4648,7 +4651,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4657,13 +4660,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4672,10 +4675,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4683,7 +4686,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4692,13 +4695,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4707,10 +4710,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4718,7 +4721,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4727,13 +4730,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4742,10 +4745,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4753,7 +4756,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4765,10 +4768,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4777,10 +4780,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4788,7 +4791,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4797,13 +4800,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4812,10 +4815,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4823,7 +4826,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4832,13 +4835,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4847,10 +4850,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4858,7 +4861,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4867,13 +4870,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4882,10 +4885,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4893,7 +4896,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4902,13 +4905,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4917,10 +4920,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4928,7 +4931,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4937,13 +4940,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4952,10 +4955,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4963,7 +4966,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4972,13 +4975,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4987,10 +4990,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -4998,7 +5001,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5007,13 +5010,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5022,10 +5025,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5033,7 +5036,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5042,13 +5045,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5057,10 +5060,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5068,7 +5071,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5077,13 +5080,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5092,10 +5095,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5103,7 +5106,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5115,10 +5118,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5130,7 +5133,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5138,7 +5141,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5150,10 +5153,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5162,10 +5165,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5173,7 +5176,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5185,10 +5188,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5197,10 +5200,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5208,7 +5211,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5217,13 +5220,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5232,10 +5235,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5243,7 +5246,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5252,13 +5255,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5267,10 +5270,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5278,7 +5281,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5287,13 +5290,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5302,10 +5305,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5313,7 +5316,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5322,13 +5325,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5337,10 +5340,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5348,7 +5351,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5360,10 +5363,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5375,7 +5378,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5383,7 +5386,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5392,13 +5395,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5407,10 +5410,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5418,7 +5421,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5427,13 +5430,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5442,10 +5445,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5453,7 +5456,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5462,13 +5465,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5477,10 +5480,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5488,7 +5491,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5500,10 +5503,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5512,10 +5515,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5523,7 +5526,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5535,10 +5538,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5547,10 +5550,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5558,7 +5561,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5570,10 +5573,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5582,10 +5585,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5593,7 +5596,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5605,10 +5608,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5617,10 +5620,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5628,22 +5631,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5655,7 +5658,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5663,22 +5666,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5690,7 +5693,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5698,22 +5701,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5722,10 +5725,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5733,22 +5736,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5757,10 +5760,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5768,22 +5771,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5792,10 +5795,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5803,22 +5806,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5830,7 +5833,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5838,22 +5841,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5865,7 +5868,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5873,22 +5876,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5897,10 +5900,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5908,22 +5911,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5932,10 +5935,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5943,10 +5946,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5955,10 +5958,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5967,10 +5970,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6010,12 +6013,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6029,19 +6032,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6064,10 +6067,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6090,10 +6093,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6116,10 +6119,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>508</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>507</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6142,7 +6145,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6166,7 +6169,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6190,10 +6193,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>508</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>507</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6216,7 +6219,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6240,7 +6243,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6264,10 +6267,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>508</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>507</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6290,7 +6293,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6314,7 +6317,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6338,7 +6341,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6362,7 +6365,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6386,15 +6389,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6402,7 +6405,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6410,7 +6413,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6439,7 +6442,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6456,10 +6459,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6467,7 +6470,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6476,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6487,7 +6490,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6499,7 +6502,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6507,7 +6510,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6516,10 +6519,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6527,7 +6530,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6536,10 +6539,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6553,18 +6556,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6573,53 +6576,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -6644,26 +6647,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6671,13 +6674,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6685,13 +6688,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6699,13 +6702,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6713,13 +6716,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6727,13 +6730,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6741,13 +6744,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6755,13 +6758,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6769,13 +6772,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6783,13 +6786,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6797,13 +6800,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6811,21 +6814,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6861,7 +6864,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6869,7 +6872,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6881,167 +6884,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -7073,7 +7076,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7093,47 +7096,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7144,16 +7147,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7161,19 +7164,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7181,19 +7184,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7201,19 +7204,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="595">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -942,6 +942,9 @@
   </si>
   <si>
     <t>Recall ≥90% on the golden set's target articles</t>
+  </si>
+  <si>
+    <t>🚧 AC-1/AC-2 done; AC-3 blocked on golden v2 (G1)</t>
   </si>
   <si>
     <t>S05-01</t>
@@ -4366,12 +4369,12 @@
         <v>306</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>151</v>
+        <v>307</v>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4383,10 +4386,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4398,7 +4401,7 @@
         <v>303</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>151</v>
@@ -4406,7 +4409,7 @@
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4418,10 +4421,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4430,10 +4433,10 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4441,7 +4444,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4453,10 +4456,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4465,10 +4468,10 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4476,7 +4479,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4485,13 +4488,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4500,10 +4503,10 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4511,7 +4514,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4520,13 +4523,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4535,10 +4538,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4546,7 +4549,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4558,10 +4561,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4570,10 +4573,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4581,7 +4584,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4590,13 +4593,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4605,10 +4608,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4616,7 +4619,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4625,13 +4628,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4640,10 +4643,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4651,7 +4654,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4660,13 +4663,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4675,10 +4678,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4686,7 +4689,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4695,13 +4698,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4710,10 +4713,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4721,7 +4724,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4730,13 +4733,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4745,10 +4748,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4756,7 +4759,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4768,10 +4771,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4780,10 +4783,10 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4791,7 +4794,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4800,13 +4803,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4815,10 +4818,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4826,7 +4829,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4835,13 +4838,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4850,10 +4853,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4861,7 +4864,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4870,13 +4873,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4885,10 +4888,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4896,7 +4899,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4905,13 +4908,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4920,10 +4923,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4931,7 +4934,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4940,13 +4943,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4955,10 +4958,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4966,7 +4969,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4975,13 +4978,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4990,10 +4993,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5001,7 +5004,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5010,13 +5013,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5025,10 +5028,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5036,7 +5039,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5045,13 +5048,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5060,10 +5063,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5071,7 +5074,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5080,13 +5083,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5095,10 +5098,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5106,7 +5109,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5118,10 +5121,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5133,7 +5136,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5141,7 +5144,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5153,10 +5156,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5165,10 +5168,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5176,7 +5179,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5188,10 +5191,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5200,10 +5203,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5211,7 +5214,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5220,13 +5223,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5235,10 +5238,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5255,13 +5258,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5270,10 +5273,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5281,7 +5284,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5290,13 +5293,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5305,10 +5308,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5316,7 +5319,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5325,13 +5328,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5340,10 +5343,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5351,7 +5354,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5363,10 +5366,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5378,7 +5381,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5386,7 +5389,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5395,13 +5398,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5410,10 +5413,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5421,7 +5424,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5430,13 +5433,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5445,10 +5448,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5456,7 +5459,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5465,13 +5468,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5480,10 +5483,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5491,7 +5494,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5503,10 +5506,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5515,10 +5518,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5538,10 +5541,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5550,10 +5553,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5561,7 +5564,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5573,10 +5576,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5585,10 +5588,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5596,7 +5599,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5608,10 +5611,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5620,10 +5623,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5631,22 +5634,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5658,7 +5661,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5666,22 +5669,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5693,7 +5696,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5701,22 +5704,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5725,10 +5728,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5736,22 +5739,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5760,10 +5763,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5771,22 +5774,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5795,10 +5798,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5806,22 +5809,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5833,7 +5836,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5841,22 +5844,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5868,7 +5871,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5876,22 +5879,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5900,10 +5903,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5911,22 +5914,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5935,10 +5938,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5946,10 +5949,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5958,10 +5961,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5970,10 +5973,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6013,12 +6016,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6032,19 +6035,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6067,10 +6070,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6093,10 +6096,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6119,10 +6122,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>508</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6145,7 +6148,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6169,7 +6172,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6193,10 +6196,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>508</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6219,7 +6222,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6243,7 +6246,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6267,10 +6270,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>509</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>508</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6293,7 +6296,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6317,7 +6320,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6341,7 +6344,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6365,7 +6368,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6389,15 +6392,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6405,7 +6408,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6413,7 +6416,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6442,7 +6445,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6459,10 +6462,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6470,7 +6473,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6479,10 +6482,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6490,7 +6493,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6502,7 +6505,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6510,7 +6513,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6519,10 +6522,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6530,7 +6533,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6539,10 +6542,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6556,18 +6559,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6576,53 +6579,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
   </sheetData>
@@ -6647,26 +6650,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6674,13 +6677,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6688,13 +6691,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6702,13 +6705,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6716,13 +6719,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6730,13 +6733,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6744,13 +6747,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6758,13 +6761,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6772,13 +6775,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6786,13 +6789,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6800,13 +6803,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6814,21 +6817,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6864,7 +6867,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6872,7 +6875,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6884,167 +6887,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -7076,7 +7079,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7096,47 +7099,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7147,16 +7150,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7164,19 +7167,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7184,19 +7187,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7204,19 +7207,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="596">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -957,6 +957,9 @@
   </si>
   <si>
     <t>Malformed output rejected server-side, never sent</t>
+  </si>
+  <si>
+    <t>✅ Done (333 unit + 174 db; DEC-2 Gemini)</t>
   </si>
   <si>
     <t>S05-02</t>
@@ -4404,12 +4407,12 @@
         <v>311</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>151</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4421,10 +4424,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4436,7 +4439,7 @@
         <v>308</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>151</v>
@@ -4444,7 +4447,7 @@
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4456,10 +4459,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4471,7 +4474,7 @@
         <v>308</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>151</v>
@@ -4479,7 +4482,7 @@
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4488,13 +4491,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4506,7 +4509,7 @@
         <v>308</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4514,7 +4517,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4523,13 +4526,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4538,10 +4541,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4549,7 +4552,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4561,10 +4564,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4573,10 +4576,10 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4584,7 +4587,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4593,13 +4596,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4608,10 +4611,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4619,7 +4622,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4628,13 +4631,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4643,10 +4646,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4654,7 +4657,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4663,13 +4666,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4678,10 +4681,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4689,7 +4692,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4698,13 +4701,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4713,10 +4716,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4724,7 +4727,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4733,13 +4736,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4748,10 +4751,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4759,7 +4762,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4771,10 +4774,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4786,7 +4789,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4794,7 +4797,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4803,13 +4806,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4818,10 +4821,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4829,7 +4832,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4838,13 +4841,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4853,10 +4856,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4873,13 +4876,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4888,10 +4891,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4899,7 +4902,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4908,13 +4911,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4923,10 +4926,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4934,7 +4937,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4943,13 +4946,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4958,10 +4961,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4969,7 +4972,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4978,13 +4981,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4993,10 +4996,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5004,7 +5007,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5013,13 +5016,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5028,10 +5031,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5039,7 +5042,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5048,13 +5051,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5063,10 +5066,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5074,7 +5077,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5083,13 +5086,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5098,10 +5101,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5109,7 +5112,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5121,10 +5124,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5136,7 +5139,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5144,7 +5147,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5156,10 +5159,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5168,10 +5171,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5179,7 +5182,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5191,10 +5194,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5203,10 +5206,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5214,7 +5217,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5223,13 +5226,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5238,10 +5241,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5249,7 +5252,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5258,13 +5261,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5273,10 +5276,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5284,7 +5287,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5293,13 +5296,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5308,10 +5311,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5319,7 +5322,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5328,13 +5331,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5343,10 +5346,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5354,7 +5357,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5366,10 +5369,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5381,7 +5384,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5389,7 +5392,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5398,13 +5401,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5413,10 +5416,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5424,7 +5427,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5433,13 +5436,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5448,10 +5451,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5459,7 +5462,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5468,13 +5471,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5483,10 +5486,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5494,7 +5497,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5506,10 +5509,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5518,10 +5521,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5529,7 +5532,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5541,10 +5544,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5553,10 +5556,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5564,7 +5567,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5576,10 +5579,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5588,10 +5591,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5599,7 +5602,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5611,10 +5614,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5623,10 +5626,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5634,22 +5637,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5661,7 +5664,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5669,22 +5672,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5696,7 +5699,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5704,22 +5707,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5728,10 +5731,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5739,22 +5742,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5763,10 +5766,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5774,22 +5777,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5798,10 +5801,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5809,22 +5812,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5836,7 +5839,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5844,22 +5847,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5871,7 +5874,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5879,22 +5882,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5903,10 +5906,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5914,22 +5917,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5938,10 +5941,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5949,10 +5952,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5961,10 +5964,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5973,10 +5976,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6016,12 +6019,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6035,19 +6038,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6070,10 +6073,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6096,10 +6099,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6122,10 +6125,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>509</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6148,7 +6151,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6172,7 +6175,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6196,10 +6199,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>509</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6222,7 +6225,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6246,7 +6249,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6270,10 +6273,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>509</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6296,7 +6299,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6320,7 +6323,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6344,7 +6347,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6368,7 +6371,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6392,15 +6395,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6408,7 +6411,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6416,7 +6419,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6445,7 +6448,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6462,10 +6465,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6473,7 +6476,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6482,10 +6485,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6493,7 +6496,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6505,7 +6508,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6513,7 +6516,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6522,10 +6525,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6533,7 +6536,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6542,10 +6545,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6559,18 +6562,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6579,53 +6582,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
   </sheetData>
@@ -6650,26 +6653,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6677,13 +6680,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6691,13 +6694,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6705,13 +6708,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6719,13 +6722,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6733,13 +6736,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6747,13 +6750,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6761,13 +6764,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6775,13 +6778,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6789,13 +6792,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6803,13 +6806,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6817,21 +6820,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6867,7 +6870,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6875,7 +6878,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6887,167 +6890,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -7079,7 +7082,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7099,47 +7102,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7150,16 +7153,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7167,19 +7170,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7187,19 +7190,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7207,19 +7210,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="597">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -984,6 +984,9 @@
   </si>
   <si>
     <t>Any historical answer reconstructable from the database</t>
+  </si>
+  <si>
+    <t>✅ Done (180 db + 333 unit; reconstructAnswer)</t>
   </si>
   <si>
     <t>S06-01</t>
@@ -4477,12 +4480,12 @@
         <v>320</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>151</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4491,13 +4494,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4509,7 +4512,7 @@
         <v>308</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4517,7 +4520,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4526,13 +4529,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4541,10 +4544,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4552,7 +4555,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4564,10 +4567,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4579,7 +4582,7 @@
         <v>313</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4587,7 +4590,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4596,13 +4599,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4611,10 +4614,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4622,7 +4625,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4631,13 +4634,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4646,10 +4649,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4666,13 +4669,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4681,10 +4684,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4692,7 +4695,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4701,13 +4704,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4716,10 +4719,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4727,7 +4730,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4736,13 +4739,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4751,10 +4754,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4762,7 +4765,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4774,10 +4777,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4789,7 +4792,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4797,7 +4800,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4806,13 +4809,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4821,10 +4824,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4832,7 +4835,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4841,13 +4844,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4856,10 +4859,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4867,7 +4870,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4876,13 +4879,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4891,10 +4894,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4902,7 +4905,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4911,13 +4914,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4926,10 +4929,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4937,7 +4940,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4946,13 +4949,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4961,10 +4964,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4972,7 +4975,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4981,13 +4984,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -4999,7 +5002,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5007,7 +5010,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5016,13 +5019,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5031,10 +5034,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5042,7 +5045,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5051,13 +5054,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5066,10 +5069,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5077,7 +5080,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5086,13 +5089,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5101,10 +5104,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5112,7 +5115,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5124,10 +5127,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5139,7 +5142,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5147,7 +5150,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5159,10 +5162,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5171,10 +5174,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5182,7 +5185,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5194,10 +5197,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5206,10 +5209,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5217,7 +5220,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5226,13 +5229,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5241,10 +5244,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5252,7 +5255,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5261,13 +5264,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5276,10 +5279,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5287,7 +5290,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5296,13 +5299,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5311,10 +5314,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5322,7 +5325,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5331,13 +5334,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5346,10 +5349,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5357,7 +5360,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5369,10 +5372,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5384,7 +5387,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5392,7 +5395,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5401,13 +5404,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5416,10 +5419,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5427,7 +5430,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5436,13 +5439,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5451,10 +5454,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5462,7 +5465,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5471,13 +5474,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5486,10 +5489,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5497,7 +5500,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5509,10 +5512,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5521,10 +5524,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5532,7 +5535,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5544,10 +5547,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5556,10 +5559,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5567,7 +5570,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5579,10 +5582,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5591,10 +5594,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5602,7 +5605,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5614,10 +5617,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5626,10 +5629,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5637,22 +5640,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5664,7 +5667,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5672,22 +5675,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5699,7 +5702,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5707,22 +5710,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5731,10 +5734,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5742,22 +5745,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5766,10 +5769,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5777,22 +5780,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5804,7 +5807,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5812,22 +5815,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5839,7 +5842,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5847,22 +5850,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5874,7 +5877,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5882,22 +5885,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5906,10 +5909,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5917,22 +5920,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5941,10 +5944,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5952,10 +5955,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5964,10 +5967,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5976,10 +5979,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6019,12 +6022,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6038,19 +6041,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6073,10 +6076,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6099,10 +6102,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6125,10 +6128,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>511</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6151,7 +6154,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6175,7 +6178,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6199,10 +6202,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>511</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6225,7 +6228,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6249,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6273,10 +6276,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>511</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6299,7 +6302,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6323,7 +6326,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6347,7 +6350,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6371,7 +6374,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6395,15 +6398,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6411,7 +6414,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6419,7 +6422,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6448,7 +6451,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6465,10 +6468,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6476,7 +6479,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6485,10 +6488,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6496,7 +6499,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6508,7 +6511,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6516,7 +6519,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6525,10 +6528,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6536,7 +6539,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6545,10 +6548,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6562,18 +6565,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6582,53 +6585,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -6653,26 +6656,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6680,13 +6683,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6694,13 +6697,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6708,13 +6711,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6722,13 +6725,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6736,13 +6739,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6750,13 +6753,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6764,13 +6767,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6778,13 +6781,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6792,13 +6795,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6806,13 +6809,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6820,21 +6823,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6870,7 +6873,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6878,7 +6881,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6890,167 +6893,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -7082,7 +7085,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7102,47 +7105,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7153,16 +7156,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7170,19 +7173,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7190,19 +7193,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7210,19 +7213,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="598">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -972,6 +972,9 @@
   </si>
   <si>
     <t>No false answer survives the gate on the golden set</t>
+  </si>
+  <si>
+    <t>🚧 AC-1/AC-2 done (citation+quote verification, banned content, sensitive/policy gate, reason codes; 356 unit + 184 db green). AC-3 (G2 ≤2% false answers) UNPROVEN — needs G1 golden set v2 + S06-03 harness.</t>
   </si>
   <si>
     <t>S05-03</t>
@@ -4445,12 +4448,12 @@
         <v>316</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>151</v>
+        <v>317</v>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4462,10 +4465,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4477,15 +4480,15 @@
         <v>308</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4494,13 +4497,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4512,7 +4515,7 @@
         <v>308</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>151</v>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4529,13 +4532,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4544,10 +4547,10 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4555,7 +4558,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4567,10 +4570,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4582,7 +4585,7 @@
         <v>313</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4590,7 +4593,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4599,13 +4602,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4614,10 +4617,10 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4625,7 +4628,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4634,13 +4637,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4649,10 +4652,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4660,7 +4663,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4669,13 +4672,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4684,10 +4687,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4695,7 +4698,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4704,13 +4707,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4719,10 +4722,10 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4730,7 +4733,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4739,13 +4742,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4754,10 +4757,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4765,7 +4768,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4777,10 +4780,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4792,7 +4795,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4800,7 +4803,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4809,13 +4812,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4824,10 +4827,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4835,7 +4838,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4844,13 +4847,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4859,10 +4862,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4870,7 +4873,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4879,13 +4882,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4894,10 +4897,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4905,7 +4908,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4914,13 +4917,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4929,10 +4932,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4940,7 +4943,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4949,13 +4952,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4964,10 +4967,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4975,7 +4978,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4984,13 +4987,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5002,7 +5005,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5010,7 +5013,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5019,13 +5022,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5034,10 +5037,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5045,7 +5048,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5054,13 +5057,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5069,10 +5072,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5080,7 +5083,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5089,13 +5092,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5104,10 +5107,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5115,7 +5118,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5127,10 +5130,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5142,7 +5145,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5150,7 +5153,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5162,10 +5165,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5174,10 +5177,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5185,7 +5188,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5197,10 +5200,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5209,10 +5212,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5220,7 +5223,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5229,13 +5232,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5244,10 +5247,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5255,7 +5258,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5264,13 +5267,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5279,10 +5282,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5290,7 +5293,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5299,13 +5302,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5314,10 +5317,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5325,7 +5328,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5334,13 +5337,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5349,10 +5352,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5360,7 +5363,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5372,10 +5375,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5387,7 +5390,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5395,7 +5398,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5404,13 +5407,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5419,10 +5422,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5430,7 +5433,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5439,13 +5442,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5454,10 +5457,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5465,7 +5468,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5474,13 +5477,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5489,10 +5492,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5500,7 +5503,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5512,10 +5515,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5524,10 +5527,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5535,7 +5538,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5547,10 +5550,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5559,10 +5562,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5570,7 +5573,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5582,10 +5585,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5594,10 +5597,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5605,7 +5608,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5617,10 +5620,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5629,10 +5632,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5640,22 +5643,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5667,7 +5670,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5675,22 +5678,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5702,7 +5705,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5710,22 +5713,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5734,10 +5737,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5745,22 +5748,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5769,10 +5772,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5780,22 +5783,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5807,7 +5810,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5815,22 +5818,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5842,7 +5845,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5850,22 +5853,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5877,7 +5880,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5885,22 +5888,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5909,10 +5912,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5920,22 +5923,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5944,10 +5947,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5955,10 +5958,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5967,10 +5970,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5979,10 +5982,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6022,12 +6025,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6041,19 +6044,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6076,10 +6079,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6102,10 +6105,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6128,10 +6131,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>511</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6154,7 +6157,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6178,7 +6181,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6202,10 +6205,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>511</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6228,7 +6231,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6252,7 +6255,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6276,10 +6279,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>512</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>511</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6302,7 +6305,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6326,7 +6329,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6350,7 +6353,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6374,7 +6377,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6398,15 +6401,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6414,7 +6417,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6422,7 +6425,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6451,7 +6454,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6468,10 +6471,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6479,7 +6482,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6488,10 +6491,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6499,7 +6502,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6511,7 +6514,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6519,7 +6522,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6528,10 +6531,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6539,7 +6542,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6548,10 +6551,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6565,18 +6568,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6585,53 +6588,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -6656,26 +6659,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6683,13 +6686,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6697,13 +6700,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6711,13 +6714,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6725,13 +6728,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6739,13 +6742,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6753,13 +6756,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6767,13 +6770,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6781,13 +6784,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6795,13 +6798,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6809,13 +6812,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6823,21 +6826,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6873,7 +6876,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6881,7 +6884,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6893,167 +6896,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -7085,7 +7088,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7105,47 +7108,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7156,16 +7159,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7173,19 +7176,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7193,19 +7196,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7213,19 +7216,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="599">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1005,6 +1005,9 @@
   </si>
   <si>
     <t>A stranger holds a full conversation on staging</t>
+  </si>
+  <si>
+    <t>🚧 AC-1/AC-2/AC-3 met as a working surface (real HTTP round trip, signed cookie, slug-only tenant, disclosure + handoff-as-message; 374 unit + 195 db green, web:build green). AC-1's 'on staging' half UNVERIFIED here — deploy is the operator step.</t>
   </si>
   <si>
     <t>S06-02</t>
@@ -4518,12 +4521,12 @@
         <v>327</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>151</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4535,10 +4538,10 @@
         <v>324</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4550,7 +4553,7 @@
         <v>323</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>151</v>
@@ -4558,7 +4561,7 @@
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4570,10 +4573,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4585,7 +4588,7 @@
         <v>313</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4593,7 +4596,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4605,10 +4608,10 @@
         <v>324</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4620,7 +4623,7 @@
         <v>323</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4628,7 +4631,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4640,10 +4643,10 @@
         <v>324</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4652,10 +4655,10 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4663,7 +4666,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4675,10 +4678,10 @@
         <v>324</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4687,10 +4690,10 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4698,7 +4701,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4710,10 +4713,10 @@
         <v>324</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4725,7 +4728,7 @@
         <v>323</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4733,7 +4736,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4745,10 +4748,10 @@
         <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4757,10 +4760,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4768,7 +4771,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4780,10 +4783,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4795,7 +4798,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4803,7 +4806,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4812,13 +4815,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4827,10 +4830,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4838,7 +4841,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4847,13 +4850,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4862,10 +4865,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4873,7 +4876,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4882,13 +4885,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4897,10 +4900,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4908,7 +4911,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4917,13 +4920,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4932,10 +4935,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4943,7 +4946,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4952,13 +4955,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4967,10 +4970,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4978,7 +4981,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4987,13 +4990,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5005,7 +5008,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5013,7 +5016,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5022,13 +5025,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5037,10 +5040,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5048,7 +5051,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5057,13 +5060,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5072,10 +5075,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5083,7 +5086,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5092,13 +5095,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5107,10 +5110,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5118,7 +5121,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5130,10 +5133,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5145,7 +5148,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5153,7 +5156,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5165,10 +5168,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5177,10 +5180,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5188,7 +5191,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5200,10 +5203,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5212,10 +5215,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5223,7 +5226,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5232,13 +5235,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5250,7 +5253,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5258,7 +5261,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5267,13 +5270,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5285,7 +5288,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5293,7 +5296,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5302,13 +5305,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5317,10 +5320,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5328,7 +5331,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5337,13 +5340,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5352,10 +5355,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5363,7 +5366,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5375,10 +5378,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5390,7 +5393,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5398,7 +5401,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5407,13 +5410,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5422,10 +5425,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5433,7 +5436,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5442,13 +5445,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5457,10 +5460,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5468,7 +5471,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5477,13 +5480,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5492,10 +5495,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5503,7 +5506,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5515,10 +5518,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5527,10 +5530,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5538,7 +5541,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5550,10 +5553,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5562,10 +5565,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5573,7 +5576,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5585,10 +5588,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5597,10 +5600,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5608,7 +5611,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5620,10 +5623,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5632,10 +5635,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5643,22 +5646,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5670,7 +5673,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5678,22 +5681,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5705,7 +5708,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5713,22 +5716,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5737,10 +5740,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5748,22 +5751,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5772,10 +5775,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5783,22 +5786,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5810,7 +5813,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5818,22 +5821,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5845,7 +5848,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5853,22 +5856,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5880,7 +5883,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5888,22 +5891,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5912,10 +5915,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5923,22 +5926,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5947,10 +5950,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5958,10 +5961,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5970,10 +5973,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5982,10 +5985,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6025,12 +6028,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6044,19 +6047,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6079,10 +6082,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6105,10 +6108,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6131,10 +6134,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>512</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6157,7 +6160,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6181,7 +6184,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6205,10 +6208,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>512</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6231,7 +6234,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6255,7 +6258,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6279,10 +6282,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>513</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>512</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6305,7 +6308,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6329,7 +6332,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6353,7 +6356,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6377,7 +6380,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6401,15 +6404,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6417,7 +6420,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6425,7 +6428,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6454,7 +6457,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6471,10 +6474,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6482,7 +6485,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6491,10 +6494,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6502,7 +6505,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6514,7 +6517,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6522,7 +6525,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6531,10 +6534,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6542,7 +6545,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6551,10 +6554,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6568,18 +6571,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6588,53 +6591,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>
@@ -6659,26 +6662,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6686,13 +6689,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6700,13 +6703,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6714,13 +6717,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6728,13 +6731,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6742,13 +6745,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6756,13 +6759,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6770,13 +6773,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6784,13 +6787,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6798,13 +6801,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6812,13 +6815,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6826,21 +6829,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6876,7 +6879,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6884,7 +6887,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6896,167 +6899,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -7088,7 +7091,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7108,47 +7111,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7159,16 +7162,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7176,19 +7179,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7196,19 +7199,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7216,19 +7219,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="600">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1020,6 +1020,9 @@
   </si>
   <si>
     <t>Illegal transitions impossible at the database level</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-25) — 0016 trigger guard (full 4x4 matrix proven through raw SQL) + atomic takeover on the conversation row lock; model provably silent after takeover; 381 unit / 204 db green.</t>
   </si>
   <si>
     <t>S06-03</t>
@@ -4556,12 +4559,12 @@
         <v>332</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>151</v>
+        <v>333</v>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4573,10 +4576,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4588,7 +4591,7 @@
         <v>313</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>151</v>
@@ -4596,7 +4599,7 @@
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4608,10 +4611,10 @@
         <v>324</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4623,7 +4626,7 @@
         <v>323</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4631,7 +4634,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4643,10 +4646,10 @@
         <v>324</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4658,7 +4661,7 @@
         <v>329</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4666,7 +4669,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4678,10 +4681,10 @@
         <v>324</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4693,7 +4696,7 @@
         <v>329</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4701,7 +4704,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4713,10 +4716,10 @@
         <v>324</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4728,7 +4731,7 @@
         <v>323</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4736,7 +4739,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4748,10 +4751,10 @@
         <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4760,10 +4763,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4771,7 +4774,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4783,10 +4786,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4798,7 +4801,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4806,7 +4809,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4815,13 +4818,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4833,7 +4836,7 @@
         <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4841,7 +4844,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4850,13 +4853,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4865,10 +4868,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4876,7 +4879,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4885,13 +4888,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4900,10 +4903,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4911,7 +4914,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4920,13 +4923,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4935,10 +4938,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4946,7 +4949,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4955,13 +4958,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4970,10 +4973,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4981,7 +4984,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4990,13 +4993,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5008,7 +5011,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5016,7 +5019,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5025,13 +5028,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5040,10 +5043,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5051,7 +5054,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5060,13 +5063,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5075,10 +5078,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5086,7 +5089,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5095,13 +5098,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5110,10 +5113,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5121,7 +5124,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5133,10 +5136,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5148,7 +5151,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5156,7 +5159,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5168,10 +5171,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5180,10 +5183,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5191,7 +5194,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5203,10 +5206,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5215,10 +5218,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5226,7 +5229,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5235,13 +5238,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5253,7 +5256,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5261,7 +5264,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5270,13 +5273,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5288,7 +5291,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5296,7 +5299,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5305,13 +5308,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5320,10 +5323,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5340,13 +5343,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5355,10 +5358,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5366,7 +5369,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5378,10 +5381,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5393,7 +5396,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5401,7 +5404,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5410,13 +5413,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5425,10 +5428,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5436,7 +5439,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5445,13 +5448,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5460,10 +5463,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5471,7 +5474,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5480,13 +5483,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5495,10 +5498,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5506,7 +5509,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5518,10 +5521,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5530,10 +5533,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5541,7 +5544,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5553,10 +5556,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5565,10 +5568,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5576,7 +5579,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5588,10 +5591,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5600,10 +5603,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5611,7 +5614,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5623,10 +5626,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5635,10 +5638,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5646,22 +5649,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5673,7 +5676,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5681,22 +5684,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5708,7 +5711,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5716,22 +5719,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5740,10 +5743,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5751,22 +5754,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5775,10 +5778,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5786,22 +5789,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5813,7 +5816,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5821,22 +5824,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5848,7 +5851,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5856,22 +5859,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5883,7 +5886,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5891,22 +5894,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5915,10 +5918,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5926,22 +5929,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5950,10 +5953,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5961,10 +5964,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5973,10 +5976,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5985,10 +5988,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6028,12 +6031,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6047,19 +6050,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6082,10 +6085,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6108,10 +6111,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6134,10 +6137,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>513</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6160,7 +6163,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6184,7 +6187,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6208,10 +6211,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>513</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6234,7 +6237,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6258,7 +6261,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6282,10 +6285,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>513</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6308,7 +6311,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6332,7 +6335,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6356,7 +6359,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6380,7 +6383,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6404,15 +6407,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6420,7 +6423,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6428,7 +6431,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6457,7 +6460,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6474,10 +6477,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6485,7 +6488,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6494,10 +6497,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6505,7 +6508,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6517,7 +6520,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6525,7 +6528,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6534,10 +6537,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6545,7 +6548,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6554,10 +6557,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6571,18 +6574,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6591,53 +6594,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
@@ -6662,26 +6665,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6689,13 +6692,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6703,13 +6706,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6717,13 +6720,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6731,13 +6734,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6745,13 +6748,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6759,13 +6762,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6773,13 +6776,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6787,13 +6790,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6801,13 +6804,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6815,13 +6818,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6829,21 +6832,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6879,7 +6882,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6887,7 +6890,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6899,167 +6902,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -7091,7 +7094,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7111,47 +7114,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7162,16 +7165,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7179,19 +7182,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7199,19 +7202,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7219,19 +7222,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="601">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1035,6 +1035,9 @@
   </si>
   <si>
     <t>G2 passes on the fixture property; runs on every prompt change</t>
+  </si>
+  <si>
+    <t>🚧 Harness + CI done (2026-10-25) — npm run eval scores four ways on golden v1 through the real pipeline; regression gate armed on a recorded baseline; canary job in eval.yml. G2 itself is RED (25% false answers on the demo fixture) and stays red until G1: 1/13 answerable questions have their target topic in the corpus.</t>
   </si>
   <si>
     <t>S07-01</t>
@@ -4594,12 +4597,12 @@
         <v>337</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>151</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4611,10 +4614,10 @@
         <v>324</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4626,7 +4629,7 @@
         <v>323</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>151</v>
@@ -4634,7 +4637,7 @@
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4646,10 +4649,10 @@
         <v>324</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4661,7 +4664,7 @@
         <v>329</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>151</v>
@@ -4669,7 +4672,7 @@
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4681,10 +4684,10 @@
         <v>324</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4696,7 +4699,7 @@
         <v>329</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4716,10 +4719,10 @@
         <v>324</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4731,7 +4734,7 @@
         <v>323</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4739,7 +4742,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4751,10 +4754,10 @@
         <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4763,10 +4766,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4774,7 +4777,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4786,10 +4789,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4801,7 +4804,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4809,7 +4812,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4818,13 +4821,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4836,7 +4839,7 @@
         <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4844,7 +4847,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4853,13 +4856,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4868,10 +4871,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4879,7 +4882,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4888,13 +4891,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4903,10 +4906,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4914,7 +4917,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4923,13 +4926,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4938,10 +4941,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4949,7 +4952,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4958,13 +4961,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4973,10 +4976,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4984,7 +4987,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4993,13 +4996,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5011,7 +5014,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5019,7 +5022,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5028,13 +5031,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5043,10 +5046,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5054,7 +5057,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5063,13 +5066,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5078,10 +5081,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5089,7 +5092,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5098,13 +5101,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5113,10 +5116,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5124,7 +5127,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5136,10 +5139,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5151,7 +5154,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5159,7 +5162,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5171,10 +5174,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5183,10 +5186,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5194,7 +5197,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5206,10 +5209,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5218,10 +5221,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5229,7 +5232,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5238,13 +5241,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5256,7 +5259,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5264,7 +5267,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5273,13 +5276,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5291,7 +5294,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5299,7 +5302,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5308,13 +5311,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5323,10 +5326,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5334,7 +5337,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5343,13 +5346,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5358,10 +5361,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5369,7 +5372,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5381,10 +5384,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5396,7 +5399,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5404,7 +5407,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5413,13 +5416,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5428,10 +5431,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5439,7 +5442,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5448,13 +5451,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5463,10 +5466,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5474,7 +5477,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5483,13 +5486,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5498,10 +5501,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5509,7 +5512,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5521,10 +5524,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5533,10 +5536,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5544,7 +5547,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5556,10 +5559,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5568,10 +5571,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5579,7 +5582,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5591,10 +5594,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5603,10 +5606,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5626,10 +5629,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5638,10 +5641,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5649,22 +5652,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5676,7 +5679,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5684,22 +5687,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5711,7 +5714,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5719,22 +5722,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5743,10 +5746,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5754,22 +5757,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5778,10 +5781,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5789,22 +5792,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5816,7 +5819,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5824,22 +5827,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5851,7 +5854,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5859,22 +5862,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5886,7 +5889,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5894,22 +5897,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5918,10 +5921,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5929,22 +5932,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5953,10 +5956,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5964,10 +5967,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5976,10 +5979,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5988,10 +5991,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6031,12 +6034,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6050,19 +6053,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6085,10 +6088,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6111,10 +6114,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6137,10 +6140,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>514</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6163,7 +6166,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6187,7 +6190,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6211,10 +6214,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>514</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6237,7 +6240,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6261,7 +6264,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6285,10 +6288,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>515</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>514</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6311,7 +6314,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6335,7 +6338,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6359,7 +6362,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6383,7 +6386,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6407,15 +6410,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6423,7 +6426,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6431,7 +6434,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6460,7 +6463,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6477,10 +6480,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6488,7 +6491,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6497,10 +6500,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6508,7 +6511,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6520,7 +6523,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6528,7 +6531,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6537,10 +6540,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6548,7 +6551,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6557,10 +6560,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6574,18 +6577,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6594,53 +6597,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
@@ -6665,26 +6668,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6692,13 +6695,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6706,13 +6709,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6720,13 +6723,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6734,13 +6737,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6748,13 +6751,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6762,13 +6765,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6776,13 +6779,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6790,13 +6793,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6804,13 +6807,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6818,13 +6821,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6832,21 +6835,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6882,7 +6885,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6890,7 +6893,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6902,167 +6905,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
   </sheetData>
@@ -7094,7 +7097,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7114,47 +7117,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7165,16 +7168,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7182,19 +7185,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7202,19 +7205,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7222,19 +7225,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="602">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1062,6 +1062,9 @@
   </si>
   <si>
     <t>A human is reachable in one tap from any state</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-25) — POST /api/chat/handoff reaches awaiting_staff from idle/awaiting_ai/awaiting_staff/resolved and from no-conversation-yet, provably without a provider call; 0017 widens resolved-&gt;awaiting_staff; disclosure in the first reply ES+EN, once; one open service_request per conversation. 403 unit / 212 db green.</t>
   </si>
   <si>
     <t>S07-03</t>
@@ -4667,12 +4670,12 @@
         <v>346</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>151</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4684,10 +4687,10 @@
         <v>324</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4699,7 +4702,7 @@
         <v>329</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>151</v>
@@ -4707,7 +4710,7 @@
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4719,10 +4722,10 @@
         <v>324</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4734,7 +4737,7 @@
         <v>323</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4742,7 +4745,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4754,10 +4757,10 @@
         <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4766,10 +4769,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4777,7 +4780,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4789,10 +4792,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4804,7 +4807,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4812,7 +4815,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4821,13 +4824,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4839,7 +4842,7 @@
         <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4847,7 +4850,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4856,13 +4859,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4871,10 +4874,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4882,7 +4885,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4891,13 +4894,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4906,10 +4909,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4917,7 +4920,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4926,13 +4929,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4941,10 +4944,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4952,7 +4955,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4961,13 +4964,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4976,10 +4979,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4987,7 +4990,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4996,13 +4999,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5014,7 +5017,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5022,7 +5025,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5031,13 +5034,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5046,10 +5049,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5057,7 +5060,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5066,13 +5069,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5081,10 +5084,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5092,7 +5095,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5101,13 +5104,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5116,10 +5119,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5127,7 +5130,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5139,10 +5142,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5154,7 +5157,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5162,7 +5165,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5174,10 +5177,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5186,10 +5189,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5197,7 +5200,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5209,10 +5212,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5221,10 +5224,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5232,7 +5235,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5241,13 +5244,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5259,7 +5262,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5267,7 +5270,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5276,13 +5279,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5294,7 +5297,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5302,7 +5305,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5311,13 +5314,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5326,10 +5329,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5337,7 +5340,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5346,13 +5349,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5361,10 +5364,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5372,7 +5375,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5384,10 +5387,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5399,7 +5402,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5407,7 +5410,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5416,13 +5419,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5431,10 +5434,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5442,7 +5445,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5451,13 +5454,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5466,10 +5469,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5477,7 +5480,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5486,13 +5489,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5501,10 +5504,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5512,7 +5515,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5524,10 +5527,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5536,10 +5539,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5547,7 +5550,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5559,10 +5562,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5571,10 +5574,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5582,7 +5585,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5594,10 +5597,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5606,10 +5609,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5617,7 +5620,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5629,10 +5632,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5641,10 +5644,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5652,22 +5655,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5679,7 +5682,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5687,22 +5690,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5714,7 +5717,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5722,22 +5725,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5746,10 +5749,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5757,22 +5760,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5781,10 +5784,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5792,22 +5795,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5819,7 +5822,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5827,22 +5830,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5854,7 +5857,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5862,22 +5865,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5889,7 +5892,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5897,22 +5900,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5921,10 +5924,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5932,22 +5935,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5956,10 +5959,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5967,10 +5970,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5979,10 +5982,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5991,10 +5994,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6034,12 +6037,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6053,19 +6056,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6088,10 +6091,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6114,10 +6117,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6140,10 +6143,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>515</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6166,7 +6169,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6190,7 +6193,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6214,10 +6217,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>515</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6240,7 +6243,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6264,7 +6267,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6288,10 +6291,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>516</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>515</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6314,7 +6317,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6338,7 +6341,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6362,7 +6365,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6386,7 +6389,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6410,15 +6413,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6426,7 +6429,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6434,7 +6437,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6463,7 +6466,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6480,10 +6483,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6491,7 +6494,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6500,10 +6503,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6511,7 +6514,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6523,7 +6526,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6531,7 +6534,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6540,10 +6543,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6551,7 +6554,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6560,10 +6563,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,18 +6580,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6597,53 +6600,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>
@@ -6668,26 +6671,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6695,13 +6698,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6709,13 +6712,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6723,13 +6726,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6737,13 +6740,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6751,13 +6754,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6765,13 +6768,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6779,13 +6782,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6793,13 +6796,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6807,13 +6810,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6821,13 +6824,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6835,21 +6838,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6885,7 +6888,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6893,7 +6896,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6905,167 +6908,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -7097,7 +7100,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7117,47 +7120,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7168,16 +7171,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7185,19 +7188,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7205,19 +7208,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7225,19 +7228,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="603">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1077,6 +1077,9 @@
   </si>
   <si>
     <t>No code path can claim a request is fulfilled</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-25) — captureRequest writes service_requests (+ knowledge_gaps for no-answer) before the acknowledgement, in the guest turn's transaction; rollback leaves no orphan; one open request per conversation; honesty sweep over every guest.* string in ES+EN, plus a vacuity check. 408 unit / 221 db green.</t>
   </si>
   <si>
     <t>S07-04</t>
@@ -4705,12 +4708,12 @@
         <v>351</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>151</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4722,10 +4725,10 @@
         <v>324</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4737,7 +4740,7 @@
         <v>323</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>151</v>
@@ -4745,7 +4748,7 @@
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4757,10 +4760,10 @@
         <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4769,10 +4772,10 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4780,7 +4783,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4792,10 +4795,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4807,7 +4810,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4815,7 +4818,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4824,13 +4827,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4842,7 +4845,7 @@
         <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4850,7 +4853,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4859,13 +4862,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4874,10 +4877,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4885,7 +4888,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4894,13 +4897,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4909,10 +4912,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4920,7 +4923,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4929,13 +4932,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4944,10 +4947,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4955,7 +4958,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4964,13 +4967,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4982,7 +4985,7 @@
         <v>348</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4990,7 +4993,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -4999,13 +5002,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5017,7 +5020,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5025,7 +5028,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5034,13 +5037,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5049,10 +5052,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5060,7 +5063,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5069,13 +5072,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5084,10 +5087,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5095,7 +5098,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5104,13 +5107,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5119,10 +5122,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5130,7 +5133,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5142,10 +5145,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5157,7 +5160,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5165,7 +5168,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5177,10 +5180,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5189,10 +5192,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5200,7 +5203,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5212,10 +5215,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5224,10 +5227,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5235,7 +5238,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5244,13 +5247,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5262,7 +5265,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5270,7 +5273,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5279,13 +5282,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5297,7 +5300,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5305,7 +5308,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5314,13 +5317,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5329,10 +5332,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5340,7 +5343,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5349,13 +5352,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5364,10 +5367,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5375,7 +5378,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5387,10 +5390,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5402,7 +5405,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5410,7 +5413,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5419,13 +5422,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5434,10 +5437,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5445,7 +5448,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5454,13 +5457,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5469,10 +5472,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5480,7 +5483,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5489,13 +5492,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5504,10 +5507,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5515,7 +5518,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5527,10 +5530,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5539,10 +5542,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5550,7 +5553,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5562,10 +5565,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5574,10 +5577,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5585,7 +5588,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5597,10 +5600,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5609,10 +5612,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5620,7 +5623,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5632,10 +5635,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5644,10 +5647,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5655,22 +5658,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5682,7 +5685,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5690,22 +5693,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5717,7 +5720,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5725,22 +5728,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5749,10 +5752,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5760,22 +5763,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5784,10 +5787,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5795,22 +5798,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5822,7 +5825,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5830,22 +5833,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5857,7 +5860,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5865,22 +5868,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5892,7 +5895,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5900,22 +5903,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5924,10 +5927,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5935,22 +5938,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5959,10 +5962,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5970,10 +5973,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5982,10 +5985,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5994,10 +5997,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6037,12 +6040,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6056,19 +6059,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6091,10 +6094,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6117,10 +6120,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6143,10 +6146,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>516</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6169,7 +6172,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6193,7 +6196,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6217,10 +6220,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>516</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6243,7 +6246,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6267,7 +6270,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6291,10 +6294,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>517</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>516</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6317,7 +6320,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6341,7 +6344,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6365,7 +6368,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6389,7 +6392,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6413,15 +6416,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6429,7 +6432,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6437,7 +6440,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6466,7 +6469,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6483,10 +6486,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6494,7 +6497,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6503,10 +6506,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6514,7 +6517,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6526,7 +6529,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6534,7 +6537,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6543,10 +6546,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6554,7 +6557,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6563,10 +6566,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6580,18 +6583,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6600,53 +6603,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
@@ -6671,26 +6674,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6698,13 +6701,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6712,13 +6715,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6726,13 +6729,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6740,13 +6743,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6754,13 +6757,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6768,13 +6771,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6782,13 +6785,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6796,13 +6799,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6810,13 +6813,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6824,13 +6827,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6838,21 +6841,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6888,7 +6891,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6896,7 +6899,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6908,167 +6911,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -7100,7 +7103,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7120,47 +7123,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7171,16 +7174,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7188,19 +7191,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7208,19 +7211,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7228,19 +7231,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="604">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1092,6 +1092,9 @@
   </si>
   <si>
     <t>Cap trip degrades to 'a team member will reply' without an error</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-25) — 3 fixed-window buckets (hashed IP / conversation / property) + Turnstile port (enforced outside local) + spend counters in Postgres feeding policyGate; cap trip = guest.request_ack + captured request, 429/403 never 5xx; 442 unit / 232 db / 19 migrations</t>
   </si>
   <si>
     <t>S07-05</t>
@@ -4743,12 +4746,12 @@
         <v>356</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>151</v>
+        <v>357</v>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4760,10 +4763,10 @@
         <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4775,7 +4778,7 @@
         <v>353</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>151</v>
@@ -4783,7 +4786,7 @@
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4795,10 +4798,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4810,7 +4813,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4818,7 +4821,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4827,13 +4830,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4845,7 +4848,7 @@
         <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4853,7 +4856,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4862,13 +4865,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4877,10 +4880,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4888,7 +4891,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4897,13 +4900,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4912,10 +4915,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4923,7 +4926,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4932,13 +4935,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4947,10 +4950,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4958,7 +4961,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4967,13 +4970,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4985,7 +4988,7 @@
         <v>348</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4993,7 +4996,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5002,13 +5005,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5020,7 +5023,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5028,7 +5031,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5037,13 +5040,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5052,10 +5055,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5063,7 +5066,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5072,13 +5075,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5087,10 +5090,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5098,7 +5101,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5107,13 +5110,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5122,10 +5125,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5133,7 +5136,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5145,10 +5148,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5160,7 +5163,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5168,7 +5171,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5180,10 +5183,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5192,10 +5195,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5203,7 +5206,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5215,10 +5218,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5227,10 +5230,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5238,7 +5241,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5247,13 +5250,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5265,7 +5268,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5273,7 +5276,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5282,13 +5285,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5300,7 +5303,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5308,7 +5311,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5317,13 +5320,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5332,10 +5335,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5343,7 +5346,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5352,13 +5355,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5367,10 +5370,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5378,7 +5381,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5390,10 +5393,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5405,7 +5408,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5413,7 +5416,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5422,13 +5425,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5437,10 +5440,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5448,7 +5451,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5457,13 +5460,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5472,10 +5475,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5483,7 +5486,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5492,13 +5495,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5507,10 +5510,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5518,7 +5521,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5530,10 +5533,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5542,10 +5545,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5553,7 +5556,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5565,10 +5568,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5577,10 +5580,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5588,7 +5591,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5600,10 +5603,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5612,10 +5615,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5623,7 +5626,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5635,10 +5638,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5647,10 +5650,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5658,22 +5661,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5685,7 +5688,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5693,22 +5696,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5720,7 +5723,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5728,22 +5731,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5752,10 +5755,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5763,22 +5766,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5787,10 +5790,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5798,22 +5801,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5825,7 +5828,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5833,22 +5836,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5860,7 +5863,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5868,22 +5871,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5895,7 +5898,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5903,22 +5906,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5927,10 +5930,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5938,22 +5941,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5962,10 +5965,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5973,10 +5976,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5985,10 +5988,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -5997,10 +6000,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6040,12 +6043,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6059,19 +6062,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6094,10 +6097,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6120,10 +6123,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6146,10 +6149,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>517</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6172,7 +6175,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6196,7 +6199,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6220,10 +6223,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>517</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6246,7 +6249,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6270,7 +6273,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6294,10 +6297,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>517</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6320,7 +6323,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6344,7 +6347,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6368,7 +6371,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6392,7 +6395,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6416,15 +6419,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6432,7 +6435,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6440,7 +6443,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6469,7 +6472,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6486,10 +6489,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6497,7 +6500,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6506,10 +6509,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6517,7 +6520,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6529,7 +6532,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6537,7 +6540,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6546,10 +6549,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6557,7 +6560,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6566,10 +6569,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6583,18 +6586,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6603,53 +6606,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -6674,26 +6677,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6701,13 +6704,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6715,13 +6718,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6729,13 +6732,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6743,13 +6746,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6757,13 +6760,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,13 +6774,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6785,13 +6788,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6799,13 +6802,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6813,13 +6816,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6827,13 +6830,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6841,21 +6844,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6891,7 +6894,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6899,7 +6902,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6911,167 +6914,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -7103,7 +7106,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7123,47 +7126,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7174,16 +7177,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7191,19 +7194,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7211,19 +7214,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7231,19 +7234,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="605">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1107,6 +1107,9 @@
   </si>
   <si>
     <t>Kill the AI mid-conversation; guest still gets an honest message</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-25) — outage records ai_runs(provider_unavailable, model_id=none) + message_failed in the turn transaction; guest gets guest.unavailable + a captured service_request, never a 5xx; AI_FAIL_MODE=once|always chaos hook (refused in prod); 457 unit / 237 db, no migration</t>
   </si>
   <si>
     <t>S07-06</t>
@@ -4781,12 +4784,12 @@
         <v>361</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>151</v>
+        <v>362</v>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4798,10 +4801,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4813,7 +4816,7 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>151</v>
@@ -4821,7 +4824,7 @@
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4830,13 +4833,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4848,7 +4851,7 @@
         <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4856,7 +4859,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4865,13 +4868,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4880,10 +4883,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4891,7 +4894,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4900,13 +4903,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4915,10 +4918,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4926,7 +4929,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4935,13 +4938,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4950,10 +4953,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4961,7 +4964,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4970,13 +4973,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4988,7 +4991,7 @@
         <v>348</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4996,7 +4999,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5005,13 +5008,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5023,7 +5026,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5031,7 +5034,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5040,13 +5043,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5055,10 +5058,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5066,7 +5069,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5075,13 +5078,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5090,10 +5093,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5101,7 +5104,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5110,13 +5113,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5125,10 +5128,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5136,7 +5139,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5148,10 +5151,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5163,7 +5166,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5171,7 +5174,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5183,10 +5186,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5195,10 +5198,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5206,7 +5209,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5218,10 +5221,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5230,10 +5233,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5241,7 +5244,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5250,13 +5253,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5268,7 +5271,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5276,7 +5279,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5285,13 +5288,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5303,7 +5306,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5311,7 +5314,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5320,13 +5323,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5335,10 +5338,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5346,7 +5349,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5355,13 +5358,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5370,10 +5373,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5381,7 +5384,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5393,10 +5396,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5408,7 +5411,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5416,7 +5419,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5425,13 +5428,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5440,10 +5443,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5451,7 +5454,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5460,13 +5463,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5475,10 +5478,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5486,7 +5489,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5495,13 +5498,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5510,10 +5513,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5521,7 +5524,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5533,10 +5536,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5545,10 +5548,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5556,7 +5559,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5568,10 +5571,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5580,10 +5583,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5591,7 +5594,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5603,10 +5606,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5615,10 +5618,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5626,7 +5629,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5638,10 +5641,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5650,10 +5653,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5661,22 +5664,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5688,7 +5691,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5696,22 +5699,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5723,7 +5726,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5731,22 +5734,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5755,10 +5758,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5766,22 +5769,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5790,10 +5793,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5801,22 +5804,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5828,7 +5831,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5836,22 +5839,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5863,7 +5866,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5871,22 +5874,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5898,7 +5901,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5906,22 +5909,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5930,10 +5933,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5941,22 +5944,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5965,10 +5968,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5976,10 +5979,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5988,10 +5991,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6000,10 +6003,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6043,12 +6046,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6062,19 +6065,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6097,10 +6100,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6123,10 +6126,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6149,10 +6152,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>519</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>518</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6175,7 +6178,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6199,7 +6202,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6223,10 +6226,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>519</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>518</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6249,7 +6252,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6273,7 +6276,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6297,10 +6300,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>519</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>518</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6323,7 +6326,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6347,7 +6350,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6371,7 +6374,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6395,7 +6398,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6419,15 +6422,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6435,7 +6438,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6443,7 +6446,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6472,7 +6475,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6489,10 +6492,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6500,7 +6503,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6509,10 +6512,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6520,7 +6523,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6532,7 +6535,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6540,7 +6543,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6549,10 +6552,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6560,7 +6563,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6569,10 +6572,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6586,18 +6589,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6606,53 +6609,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
   </sheetData>
@@ -6677,26 +6680,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6704,13 +6707,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6718,13 +6721,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6732,13 +6735,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6746,13 +6749,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6760,13 +6763,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6774,13 +6777,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6788,13 +6791,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6802,13 +6805,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6816,13 +6819,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6830,13 +6833,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6844,21 +6847,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6894,7 +6897,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6902,7 +6905,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6914,167 +6917,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -7106,7 +7109,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7126,47 +7129,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,16 +7180,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7194,19 +7197,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7214,19 +7217,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7234,19 +7237,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="607">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1052,6 +1052,9 @@
     <t>QR resolves to the right property on a real phone</t>
   </si>
   <si>
+    <t>✅ Done (QR + embed, 0020; phone scan owed)</t>
+  </si>
+  <si>
     <t>S07-02</t>
   </si>
   <si>
@@ -1122,6 +1125,9 @@
   </si>
   <si>
     <t>Both providers killed; product degrades honestly</t>
+  </si>
+  <si>
+    <t>✅ Done (498 tests; metrics counters wired; no migration)</t>
   </si>
   <si>
     <t>S08-01</t>
@@ -4644,12 +4650,12 @@
         <v>342</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>151</v>
+        <v>343</v>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4661,10 +4667,10 @@
         <v>324</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4676,15 +4682,15 @@
         <v>329</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4696,10 +4702,10 @@
         <v>324</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4711,15 +4717,15 @@
         <v>329</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4731,10 +4737,10 @@
         <v>324</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4746,15 +4752,15 @@
         <v>323</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4766,10 +4772,10 @@
         <v>324</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4778,18 +4784,18 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4801,10 +4807,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4816,15 +4822,15 @@
         <v>308</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>151</v>
+        <v>368</v>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4833,13 +4839,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4851,7 +4857,7 @@
         <v>329</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4859,7 +4865,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4868,13 +4874,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4883,10 +4889,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4894,7 +4900,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4903,13 +4909,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4918,10 +4924,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4929,7 +4935,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4938,13 +4944,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4953,10 +4959,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4964,7 +4970,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4973,13 +4979,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4988,10 +4994,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -4999,7 +5005,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5008,13 +5014,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5026,7 +5032,7 @@
         <v>313</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5034,7 +5040,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5043,13 +5049,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5058,10 +5064,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5069,7 +5075,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5078,13 +5084,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5093,10 +5099,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5104,7 +5110,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5113,13 +5119,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5128,10 +5134,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5139,7 +5145,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5151,10 +5157,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5166,7 +5172,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5174,7 +5180,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5186,10 +5192,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5198,10 +5204,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5209,7 +5215,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5221,10 +5227,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5233,10 +5239,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5244,7 +5250,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5253,13 +5259,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5271,7 +5277,7 @@
         <v>323</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5279,7 +5285,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5288,13 +5294,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5306,7 +5312,7 @@
         <v>323</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5314,7 +5320,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5323,13 +5329,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5338,10 +5344,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5349,7 +5355,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5358,13 +5364,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5373,10 +5379,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5384,7 +5390,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5396,10 +5402,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5411,7 +5417,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5419,7 +5425,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5428,13 +5434,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5443,10 +5449,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5454,7 +5460,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5463,13 +5469,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5478,10 +5484,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5489,7 +5495,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5498,13 +5504,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5513,10 +5519,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5524,7 +5530,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5536,10 +5542,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5548,10 +5554,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5559,7 +5565,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5571,10 +5577,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5583,10 +5589,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5594,7 +5600,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5606,10 +5612,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5618,10 +5624,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5629,7 +5635,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5641,10 +5647,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5653,10 +5659,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5664,22 +5670,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5691,7 +5697,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5699,22 +5705,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5726,7 +5732,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5734,22 +5740,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5758,10 +5764,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5769,22 +5775,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5793,10 +5799,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5804,22 +5810,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5831,7 +5837,7 @@
         <v>313</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5839,22 +5845,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5866,7 +5872,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5874,22 +5880,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5901,7 +5907,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5909,22 +5915,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5933,10 +5939,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5944,22 +5950,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5968,10 +5974,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5979,10 +5985,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5991,10 +5997,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6003,10 +6009,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6046,12 +6052,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6065,19 +6071,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6100,10 +6106,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6126,10 +6132,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6152,10 +6158,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6178,7 +6184,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6202,7 +6208,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6226,10 +6232,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6252,7 +6258,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6276,7 +6282,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6300,10 +6306,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6326,7 +6332,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6350,7 +6356,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6374,7 +6380,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6398,7 +6404,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6422,15 +6428,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6438,7 +6444,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6446,7 +6452,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6475,7 +6481,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6492,10 +6498,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6503,7 +6509,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6512,10 +6518,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6523,7 +6529,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6535,7 +6541,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6543,7 +6549,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6552,10 +6558,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6563,7 +6569,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6572,10 +6578,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6589,18 +6595,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6609,53 +6615,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -6680,26 +6686,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6707,13 +6713,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6721,13 +6727,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6735,13 +6741,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6749,13 +6755,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6763,13 +6769,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6777,13 +6783,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6791,13 +6797,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6805,13 +6811,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6819,13 +6825,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6833,13 +6839,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6847,21 +6853,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6897,7 +6903,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6905,7 +6911,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6917,167 +6923,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
@@ -7109,7 +7115,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7129,47 +7135,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7180,16 +7186,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7197,19 +7203,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7217,19 +7223,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7237,19 +7243,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="608">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -900,6 +900,9 @@
   </si>
   <si>
     <t>Pool hours answered by lookup, not generation</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: re-verified on main — 243 db / 500 unit, 0009 + fact service; tick was missed after PR #32)</t>
   </si>
   <si>
     <t>S04-01</t>
@@ -4300,12 +4303,12 @@
         <v>292</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>151</v>
+        <v>293</v>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4317,10 +4320,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4332,15 +4335,15 @@
         <v>279</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4352,10 +4355,10 @@
         <v>214</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4367,15 +4370,15 @@
         <v>279</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4387,10 +4390,10 @@
         <v>214</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4399,18 +4402,18 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4422,10 +4425,10 @@
         <v>214</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4434,18 +4437,18 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4457,10 +4460,10 @@
         <v>214</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4469,18 +4472,18 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4492,10 +4495,10 @@
         <v>214</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4504,18 +4507,18 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4524,13 +4527,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4539,18 +4542,18 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4559,13 +4562,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4574,18 +4577,18 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4597,10 +4600,10 @@
         <v>214</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4609,18 +4612,18 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4629,13 +4632,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4644,18 +4647,18 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K45" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="46" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>90</v>
@@ -4664,13 +4667,13 @@
         <v>195</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G46" s="12">
         <v>0.5</v>
@@ -4679,18 +4682,18 @@
         <v>149</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J46" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K46" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="47" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>90</v>
@@ -4699,13 +4702,13 @@
         <v>195</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G47" s="12">
         <v>1</v>
@@ -4714,18 +4717,18 @@
         <v>149</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J47" s="11" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K47" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="48" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>90</v>
@@ -4734,13 +4737,13 @@
         <v>195</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G48" s="12">
         <v>1</v>
@@ -4749,18 +4752,18 @@
         <v>149</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J48" s="11" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K48" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>90</v>
@@ -4769,13 +4772,13 @@
         <v>195</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G49" s="12">
         <v>0.5</v>
@@ -4784,18 +4787,18 @@
         <v>149</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J49" s="11" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="K49" s="11" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>90</v>
@@ -4807,10 +4810,10 @@
         <v>214</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G50" s="12">
         <v>0.5</v>
@@ -4819,18 +4822,18 @@
         <v>149</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J50" s="11" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="K50" s="11" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="51" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>95</v>
@@ -4839,13 +4842,13 @@
         <v>195</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G51" s="12">
         <v>2</v>
@@ -4854,10 +4857,10 @@
         <v>149</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="J51" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>151</v>
@@ -4865,7 +4868,7 @@
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4874,13 +4877,13 @@
         <v>195</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4889,10 +4892,10 @@
         <v>149</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4900,7 +4903,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4909,13 +4912,13 @@
         <v>195</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4924,10 +4927,10 @@
         <v>149</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4935,7 +4938,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4944,13 +4947,13 @@
         <v>195</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4959,10 +4962,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4970,7 +4973,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4979,13 +4982,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -4994,10 +4997,10 @@
         <v>149</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -5005,7 +5008,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5014,13 +5017,13 @@
         <v>195</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5029,10 +5032,10 @@
         <v>149</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5040,7 +5043,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5049,13 +5052,13 @@
         <v>195</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5064,10 +5067,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5075,7 +5078,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5084,13 +5087,13 @@
         <v>195</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5099,10 +5102,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5110,7 +5113,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5119,13 +5122,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5134,10 +5137,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5145,7 +5148,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5157,10 +5160,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5172,7 +5175,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5180,7 +5183,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5192,10 +5195,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5204,10 +5207,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5215,7 +5218,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5227,10 +5230,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5239,10 +5242,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5250,7 +5253,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5259,13 +5262,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5274,10 +5277,10 @@
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5285,7 +5288,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5294,13 +5297,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5309,10 +5312,10 @@
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5320,7 +5323,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5329,13 +5332,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5344,10 +5347,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5355,7 +5358,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5364,13 +5367,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5379,10 +5382,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5390,7 +5393,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5402,10 +5405,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5417,7 +5420,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5425,7 +5428,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5434,13 +5437,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5449,10 +5452,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5460,7 +5463,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5469,13 +5472,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5484,10 +5487,10 @@
         <v>170</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5495,7 +5498,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5504,13 +5507,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5519,10 +5522,10 @@
         <v>170</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5530,7 +5533,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5542,10 +5545,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5554,10 +5557,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5565,7 +5568,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5577,10 +5580,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5589,10 +5592,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5612,10 +5615,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5624,10 +5627,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5635,7 +5638,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5647,10 +5650,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5659,10 +5662,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5670,22 +5673,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5697,7 +5700,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5705,22 +5708,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5732,7 +5735,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5740,22 +5743,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5764,10 +5767,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5775,22 +5778,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5799,10 +5802,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5810,22 +5813,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5834,10 +5837,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5845,22 +5848,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5872,7 +5875,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5880,22 +5883,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5907,7 +5910,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5915,22 +5918,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5939,10 +5942,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5950,22 +5953,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5974,10 +5977,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5985,10 +5988,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -5997,10 +6000,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6009,10 +6012,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6052,12 +6055,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6071,19 +6074,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6106,10 +6109,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6132,10 +6135,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6158,10 +6161,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6184,7 +6187,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6208,7 +6211,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6232,10 +6235,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6258,7 +6261,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6282,7 +6285,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6306,10 +6309,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>522</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6332,7 +6335,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6356,7 +6359,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6380,7 +6383,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6404,7 +6407,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6428,15 +6431,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6444,7 +6447,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6452,7 +6455,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6481,7 +6484,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6498,10 +6501,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6509,7 +6512,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6518,10 +6521,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6529,7 +6532,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6541,7 +6544,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6549,7 +6552,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6558,10 +6561,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6569,7 +6572,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6578,10 +6581,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6595,18 +6598,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6615,53 +6618,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -6686,26 +6689,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6713,13 +6716,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6727,13 +6730,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6741,13 +6744,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6755,13 +6758,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6769,13 +6772,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6783,13 +6786,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6797,13 +6800,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6811,13 +6814,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6825,13 +6828,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6839,13 +6842,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6853,21 +6856,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6903,7 +6906,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6911,7 +6914,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6923,167 +6926,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>
@@ -7115,7 +7118,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7135,47 +7138,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7186,16 +7189,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7203,19 +7206,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7223,19 +7226,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7243,19 +7246,19 @@
         <v>61</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="609">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1146,6 +1146,9 @@
   </si>
   <si>
     <t>An agent triages a queue on a phone in under 60 seconds</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: /api/inbox + /inbox, 0021 indexes, 253 db / 514 unit; phone stopwatch owed)</t>
   </si>
   <si>
     <t>S08-02</t>
@@ -4863,12 +4866,12 @@
         <v>374</v>
       </c>
       <c r="K51" s="11" t="s">
-        <v>151</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>95</v>
@@ -4880,10 +4883,10 @@
         <v>371</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G52" s="12">
         <v>1</v>
@@ -4895,7 +4898,7 @@
         <v>370</v>
       </c>
       <c r="J52" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>151</v>
@@ -4903,7 +4906,7 @@
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4915,10 +4918,10 @@
         <v>371</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4930,7 +4933,7 @@
         <v>370</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4938,7 +4941,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4950,10 +4953,10 @@
         <v>371</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4962,10 +4965,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4973,7 +4976,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4982,13 +4985,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -5000,7 +5003,7 @@
         <v>350</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -5008,7 +5011,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5020,10 +5023,10 @@
         <v>371</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5035,7 +5038,7 @@
         <v>314</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5043,7 +5046,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5055,10 +5058,10 @@
         <v>371</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5067,10 +5070,10 @@
         <v>149</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5078,7 +5081,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5090,10 +5093,10 @@
         <v>371</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5102,10 +5105,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5113,7 +5116,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5122,13 +5125,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5137,10 +5140,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5148,7 +5151,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5160,10 +5163,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5175,7 +5178,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5183,7 +5186,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5195,10 +5198,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5207,10 +5210,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5218,7 +5221,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5230,10 +5233,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5242,10 +5245,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5253,7 +5256,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5262,13 +5265,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5280,7 +5283,7 @@
         <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5288,7 +5291,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5297,13 +5300,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5315,7 +5318,7 @@
         <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5323,7 +5326,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5332,13 +5335,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5347,10 +5350,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5358,7 +5361,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5367,13 +5370,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5382,10 +5385,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5393,7 +5396,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5405,10 +5408,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5420,7 +5423,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5428,7 +5431,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5437,13 +5440,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5452,10 +5455,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5463,7 +5466,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5472,13 +5475,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5490,7 +5493,7 @@
         <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5498,7 +5501,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5507,13 +5510,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5525,7 +5528,7 @@
         <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5533,7 +5536,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5545,10 +5548,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5557,10 +5560,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5568,7 +5571,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5580,10 +5583,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5592,10 +5595,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5603,7 +5606,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5615,10 +5618,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5627,10 +5630,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5638,7 +5641,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5650,10 +5653,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5662,10 +5665,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5673,22 +5676,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5700,7 +5703,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5708,22 +5711,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5735,7 +5738,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5743,22 +5746,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5767,10 +5770,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5778,22 +5781,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5802,10 +5805,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5813,22 +5816,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5840,7 +5843,7 @@
         <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5848,22 +5851,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5875,7 +5878,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5883,22 +5886,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5910,7 +5913,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5918,22 +5921,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5942,10 +5945,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5953,22 +5956,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5977,10 +5980,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5988,10 +5991,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -6000,10 +6003,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6012,10 +6015,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6055,12 +6058,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6074,19 +6077,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6109,10 +6112,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6135,10 +6138,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6161,10 +6164,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>522</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6187,7 +6190,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6211,7 +6214,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6235,10 +6238,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>522</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6261,7 +6264,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6285,7 +6288,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6309,10 +6312,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>523</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>522</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6335,7 +6338,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6359,7 +6362,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6383,7 +6386,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6407,7 +6410,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6431,15 +6434,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6447,7 +6450,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6455,7 +6458,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6484,7 +6487,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6501,10 +6504,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6512,7 +6515,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6521,10 +6524,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6532,7 +6535,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6544,7 +6547,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6552,7 +6555,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6561,10 +6564,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6572,7 +6575,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6581,10 +6584,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6598,18 +6601,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6618,53 +6621,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
   </sheetData>
@@ -6689,26 +6692,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6716,13 +6719,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6730,13 +6733,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6744,13 +6747,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6758,13 +6761,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6772,13 +6775,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6786,13 +6789,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6800,13 +6803,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6814,13 +6817,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6834,7 +6837,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6842,13 +6845,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6856,21 +6859,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6906,7 +6909,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6914,7 +6917,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6926,167 +6929,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>
@@ -7118,7 +7121,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7138,47 +7141,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7189,16 +7192,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7206,19 +7209,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7226,19 +7229,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7249,16 +7252,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="610">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1161,6 +1161,9 @@
   </si>
   <si>
     <t>Staff can see the cited text verbatim</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: /api/inbox/conversations/:id + /inbox/[id], 0022 citations.quote, 261 db / 518 unit; sources screenshot owed)</t>
   </si>
   <si>
     <t>S08-03</t>
@@ -4901,12 +4904,12 @@
         <v>379</v>
       </c>
       <c r="K52" s="11" t="s">
-        <v>151</v>
+        <v>380</v>
       </c>
     </row>
     <row r="53" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>95</v>
@@ -4918,10 +4921,10 @@
         <v>371</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="G53" s="12">
         <v>1.5</v>
@@ -4933,7 +4936,7 @@
         <v>370</v>
       </c>
       <c r="J53" s="11" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>151</v>
@@ -4941,7 +4944,7 @@
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4953,10 +4956,10 @@
         <v>371</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4965,10 +4968,10 @@
         <v>149</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4976,7 +4979,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4985,13 +4988,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -5003,7 +5006,7 @@
         <v>350</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -5011,7 +5014,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5023,10 +5026,10 @@
         <v>371</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5038,7 +5041,7 @@
         <v>314</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5046,7 +5049,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5058,10 +5061,10 @@
         <v>371</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5073,7 +5076,7 @@
         <v>376</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5081,7 +5084,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5093,10 +5096,10 @@
         <v>371</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5105,10 +5108,10 @@
         <v>149</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5116,7 +5119,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5125,13 +5128,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5140,10 +5143,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5151,7 +5154,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5163,10 +5166,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5178,7 +5181,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5186,7 +5189,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5198,10 +5201,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5210,10 +5213,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5221,7 +5224,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5233,10 +5236,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5245,10 +5248,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5256,7 +5259,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5265,13 +5268,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5283,7 +5286,7 @@
         <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5291,7 +5294,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5300,13 +5303,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5318,7 +5321,7 @@
         <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5326,7 +5329,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5335,13 +5338,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5350,10 +5353,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5361,7 +5364,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5370,13 +5373,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5385,10 +5388,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5396,7 +5399,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5408,10 +5411,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5423,7 +5426,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5431,7 +5434,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5440,13 +5443,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5455,10 +5458,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5466,7 +5469,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5475,13 +5478,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5493,7 +5496,7 @@
         <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5501,7 +5504,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5510,13 +5513,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5528,7 +5531,7 @@
         <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5536,7 +5539,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5548,10 +5551,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5560,10 +5563,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5571,7 +5574,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5583,10 +5586,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5595,10 +5598,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5606,7 +5609,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5618,10 +5621,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5630,10 +5633,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5641,7 +5644,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5653,10 +5656,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5665,10 +5668,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5676,22 +5679,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5703,7 +5706,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5711,22 +5714,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5738,7 +5741,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5746,22 +5749,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5770,10 +5773,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5781,22 +5784,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5805,10 +5808,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5816,22 +5819,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5843,7 +5846,7 @@
         <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5851,22 +5854,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5878,7 +5881,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5886,22 +5889,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5913,7 +5916,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5921,22 +5924,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5945,10 +5948,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5956,22 +5959,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5980,10 +5983,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5991,10 +5994,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -6003,10 +6006,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6015,10 +6018,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6058,12 +6061,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6077,19 +6080,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6112,10 +6115,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6138,10 +6141,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6164,10 +6167,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>523</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6190,7 +6193,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6214,7 +6217,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6238,10 +6241,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>523</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6264,7 +6267,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6288,7 +6291,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6312,10 +6315,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>523</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6338,7 +6341,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6362,7 +6365,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6386,7 +6389,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6410,7 +6413,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6434,15 +6437,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6450,7 +6453,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6458,7 +6461,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6487,7 +6490,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6504,10 +6507,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6515,7 +6518,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6524,10 +6527,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6535,7 +6538,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6547,7 +6550,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6555,7 +6558,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6564,10 +6567,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6575,7 +6578,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6584,10 +6587,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6601,18 +6604,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6621,53 +6624,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -6692,26 +6695,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6719,13 +6722,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6733,13 +6736,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6747,13 +6750,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6761,13 +6764,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6775,13 +6778,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6789,13 +6792,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6803,13 +6806,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6817,13 +6820,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6837,7 +6840,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6845,13 +6848,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6859,21 +6862,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6909,7 +6912,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6917,7 +6920,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6929,167 +6932,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -7121,7 +7124,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7141,47 +7144,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7192,16 +7195,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7209,19 +7212,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7229,19 +7232,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7252,16 +7255,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="611">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1176,6 +1176,9 @@
   </si>
   <si>
     <t>No race where AI replies after a takeover</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: 4 staff actions + lock-strength split (FOR NO KEY UPDATE vs FOR UPDATE), 0023, race test 2 conns, 272 db / 523 unit)</t>
   </si>
   <si>
     <t>S08-04</t>
@@ -4939,12 +4942,12 @@
         <v>384</v>
       </c>
       <c r="K53" s="11" t="s">
-        <v>151</v>
+        <v>385</v>
       </c>
     </row>
     <row r="54" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>95</v>
@@ -4956,10 +4959,10 @@
         <v>371</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G54" s="12">
         <v>1</v>
@@ -4971,7 +4974,7 @@
         <v>381</v>
       </c>
       <c r="J54" s="11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>151</v>
@@ -4979,7 +4982,7 @@
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4988,13 +4991,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -5006,7 +5009,7 @@
         <v>350</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -5014,7 +5017,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5026,10 +5029,10 @@
         <v>371</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5041,7 +5044,7 @@
         <v>314</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5049,7 +5052,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5061,10 +5064,10 @@
         <v>371</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5076,7 +5079,7 @@
         <v>376</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5084,7 +5087,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5096,10 +5099,10 @@
         <v>371</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5111,7 +5114,7 @@
         <v>381</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5119,7 +5122,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5128,13 +5131,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5143,10 +5146,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5154,7 +5157,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5166,10 +5169,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5181,7 +5184,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5189,7 +5192,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5201,10 +5204,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5213,10 +5216,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5224,7 +5227,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5236,10 +5239,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5248,10 +5251,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5268,13 +5271,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5286,7 +5289,7 @@
         <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5294,7 +5297,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5303,13 +5306,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5321,7 +5324,7 @@
         <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5329,7 +5332,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5338,13 +5341,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5353,10 +5356,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5364,7 +5367,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5373,13 +5376,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5388,10 +5391,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5399,7 +5402,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5411,10 +5414,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5426,7 +5429,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5434,7 +5437,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5443,13 +5446,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5458,10 +5461,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5469,7 +5472,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5478,13 +5481,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5496,7 +5499,7 @@
         <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5504,7 +5507,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5513,13 +5516,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5531,7 +5534,7 @@
         <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5539,7 +5542,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5551,10 +5554,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5563,10 +5566,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5574,7 +5577,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5586,10 +5589,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5598,10 +5601,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5609,7 +5612,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5621,10 +5624,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5633,10 +5636,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5656,10 +5659,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5668,10 +5671,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5679,22 +5682,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5706,7 +5709,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5714,22 +5717,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5741,7 +5744,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5749,22 +5752,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5773,10 +5776,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5784,22 +5787,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5808,10 +5811,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5819,22 +5822,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5846,7 +5849,7 @@
         <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5854,22 +5857,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5881,7 +5884,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5889,22 +5892,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5916,7 +5919,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5924,22 +5927,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5948,10 +5951,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5959,22 +5962,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5983,10 +5986,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5994,10 +5997,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -6006,10 +6009,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6018,10 +6021,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6061,12 +6064,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6080,19 +6083,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6115,10 +6118,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6141,10 +6144,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6167,10 +6170,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>525</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>524</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6193,7 +6196,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6217,7 +6220,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6241,10 +6244,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>525</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>524</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6267,7 +6270,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6291,7 +6294,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6315,10 +6318,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>525</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>524</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6341,7 +6344,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6365,7 +6368,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6389,7 +6392,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6413,7 +6416,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6437,15 +6440,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6453,7 +6456,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6461,7 +6464,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6490,7 +6493,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6507,10 +6510,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6518,7 +6521,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6527,10 +6530,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6538,7 +6541,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6550,7 +6553,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6558,7 +6561,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6567,10 +6570,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6578,7 +6581,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6587,10 +6590,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6604,18 +6607,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6624,53 +6627,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>
@@ -6695,26 +6698,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6722,13 +6725,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6736,13 +6739,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6750,13 +6753,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6764,13 +6767,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6778,13 +6781,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6792,13 +6795,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6806,13 +6809,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6820,13 +6823,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6840,7 +6843,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6848,13 +6851,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6862,21 +6865,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6912,7 +6915,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6920,7 +6923,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6932,167 +6935,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -7124,7 +7127,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7144,47 +7147,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7195,16 +7198,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7212,19 +7215,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7232,19 +7235,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7255,16 +7258,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="612">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1191,6 +1191,9 @@
   </si>
   <si>
     <t>Mode change applies to the next message, no deploy</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: /api/settings/ai-mode + /settings, next-message proof + DST, runtime strip-types guard, 279 db / 530 unit)</t>
   </si>
   <si>
     <t>S09-01</t>
@@ -4977,12 +4980,12 @@
         <v>389</v>
       </c>
       <c r="K54" s="11" t="s">
-        <v>151</v>
+        <v>390</v>
       </c>
     </row>
     <row r="55" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>100</v>
@@ -4991,13 +4994,13 @@
         <v>195</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G55" s="12">
         <v>2</v>
@@ -5009,7 +5012,7 @@
         <v>350</v>
       </c>
       <c r="J55" s="11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>151</v>
@@ -5017,7 +5020,7 @@
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5029,10 +5032,10 @@
         <v>371</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5044,7 +5047,7 @@
         <v>314</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>151</v>
@@ -5052,7 +5055,7 @@
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5064,10 +5067,10 @@
         <v>371</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5079,7 +5082,7 @@
         <v>376</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>151</v>
@@ -5087,7 +5090,7 @@
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5099,10 +5102,10 @@
         <v>371</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5114,7 +5117,7 @@
         <v>381</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>151</v>
@@ -5122,7 +5125,7 @@
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5131,13 +5134,13 @@
         <v>195</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5146,10 +5149,10 @@
         <v>149</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>151</v>
@@ -5157,7 +5160,7 @@
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5169,10 +5172,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5184,7 +5187,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5192,7 +5195,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5204,10 +5207,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5216,10 +5219,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5227,7 +5230,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5239,10 +5242,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5251,10 +5254,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5262,7 +5265,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5271,13 +5274,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5289,7 +5292,7 @@
         <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5297,7 +5300,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5306,13 +5309,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5324,7 +5327,7 @@
         <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5332,7 +5335,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5341,13 +5344,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5356,10 +5359,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5367,7 +5370,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5376,13 +5379,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5391,10 +5394,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5402,7 +5405,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5414,10 +5417,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5429,7 +5432,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5437,7 +5440,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5446,13 +5449,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5461,10 +5464,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5472,7 +5475,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5481,13 +5484,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5499,7 +5502,7 @@
         <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5507,7 +5510,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5516,13 +5519,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5534,7 +5537,7 @@
         <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5542,7 +5545,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5554,10 +5557,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5566,10 +5569,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5577,7 +5580,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5589,10 +5592,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5601,10 +5604,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5612,7 +5615,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5624,10 +5627,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5636,10 +5639,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5647,7 +5650,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5659,10 +5662,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5671,10 +5674,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5682,22 +5685,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5709,7 +5712,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5717,22 +5720,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5744,7 +5747,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5752,22 +5755,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5776,10 +5779,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5787,22 +5790,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5811,10 +5814,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5822,22 +5825,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5849,7 +5852,7 @@
         <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5857,22 +5860,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5884,7 +5887,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5892,22 +5895,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5919,7 +5922,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5927,22 +5930,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5951,10 +5954,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5962,22 +5965,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5986,10 +5989,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -5997,10 +6000,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -6009,10 +6012,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6021,10 +6024,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6064,12 +6067,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6083,19 +6086,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6118,10 +6121,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6144,10 +6147,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6170,10 +6173,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>525</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6196,7 +6199,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6220,7 +6223,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6244,10 +6247,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>525</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6270,7 +6273,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6294,7 +6297,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6318,10 +6321,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>526</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>525</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6344,7 +6347,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6368,7 +6371,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6392,7 +6395,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6416,7 +6419,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6440,15 +6443,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6456,7 +6459,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6464,7 +6467,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6493,7 +6496,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6510,10 +6513,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6521,7 +6524,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6530,10 +6533,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6541,7 +6544,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6553,7 +6556,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6561,7 +6564,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6570,10 +6573,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6581,7 +6584,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6590,10 +6593,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6607,18 +6610,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6627,53 +6630,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
   </sheetData>
@@ -6698,26 +6701,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6725,13 +6728,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6739,13 +6742,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6753,13 +6756,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6767,13 +6770,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6781,13 +6784,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6795,13 +6798,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6809,13 +6812,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6823,13 +6826,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6843,7 +6846,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6851,13 +6854,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6865,21 +6868,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6915,7 +6918,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6923,7 +6926,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6935,167 +6938,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -7127,7 +7130,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7147,47 +7150,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7198,16 +7201,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7215,19 +7218,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7235,19 +7238,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7258,16 +7261,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="612">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="617">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1211,6 +1211,9 @@
     <t>request_acknowledged is set by a real staff action</t>
   </si>
   <si>
+    <t>✅ Done (2026-10-26: request_transition_guard trigger — transition matrix + actor GUC + membership role, per-edge evidence, immutable (org,property,request); 4 endpoints + Acknowledge/Cancel UI, 0024, 315 db / 562 unit)</t>
+  </si>
+  <si>
     <t>S09-02</t>
   </si>
   <si>
@@ -1223,6 +1226,9 @@
     <t>Every no_answer lands in the queue automatically</t>
   </si>
   <si>
+    <t>✅ Done (2026-10-26: one gap writer (recordGap) upserting per property+question_key with hits, close event + median open age, /api/gaps + /gaps screen, 0025, 336 db / 567 unit)</t>
+  </si>
+  <si>
     <t>S09-03</t>
   </si>
   <si>
@@ -1235,6 +1241,9 @@
     <t>A flag is attributable to an ai_run</t>
   </si>
   <si>
+    <t>✅ Done (2026-10-26: answer_flags append-only with composite FK to ai_runs, one flag per (run, actor), actor/time/note, indicator on the answer + event, 0026, 352 db / 570 unit)</t>
+  </si>
+  <si>
     <t>S09-04</t>
   </si>
   <si>
@@ -1247,6 +1256,9 @@
     <t>Flagging an answer does not delay the guest reply</t>
   </si>
   <si>
+    <t>✅ Done (2026-10-26: review work off the guest's path via outbox kind='review' — first outbox consumer; NOLOGIN concierge_worker definer claim, 0027, 368 db / 576 unit; worker unscheduled, S11-01)</t>
+  </si>
+  <si>
     <t>S09-05</t>
   </si>
   <si>
@@ -1257,6 +1269,9 @@
   </si>
   <si>
     <t>A request with no staff view still reaches a human by email</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: escalation email queued in the request's own transaction; Resend over plain fetch, settings contacts + redacted deployment fallback, claim_outbox generalised, 0028, 395 db / 610 unit; real delivery email owed)</t>
   </si>
   <si>
     <t>S10-01</t>
@@ -5015,12 +5030,12 @@
         <v>395</v>
       </c>
       <c r="K55" s="11" t="s">
-        <v>151</v>
+        <v>396</v>
       </c>
     </row>
     <row r="56" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>100</v>
@@ -5032,10 +5047,10 @@
         <v>371</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G56" s="12">
         <v>0.5</v>
@@ -5047,15 +5062,15 @@
         <v>314</v>
       </c>
       <c r="J56" s="11" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="K56" s="11" t="s">
-        <v>151</v>
+        <v>401</v>
       </c>
     </row>
     <row r="57" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>100</v>
@@ -5067,10 +5082,10 @@
         <v>371</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="G57" s="12">
         <v>0.5</v>
@@ -5082,15 +5097,15 @@
         <v>376</v>
       </c>
       <c r="J57" s="11" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K57" s="11" t="s">
-        <v>151</v>
+        <v>406</v>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>100</v>
@@ -5102,10 +5117,10 @@
         <v>371</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="G58" s="12">
         <v>0.5</v>
@@ -5117,15 +5132,15 @@
         <v>381</v>
       </c>
       <c r="J58" s="11" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="K58" s="11" t="s">
-        <v>151</v>
+        <v>411</v>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>100</v>
@@ -5137,10 +5152,10 @@
         <v>392</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="G59" s="12">
         <v>1</v>
@@ -5152,15 +5167,15 @@
         <v>391</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K59" s="11" t="s">
-        <v>151</v>
+        <v>416</v>
       </c>
     </row>
     <row r="60" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>105</v>
@@ -5172,10 +5187,10 @@
         <v>107</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="G60" s="12">
         <v>1.5</v>
@@ -5187,7 +5202,7 @@
         <v>231</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>151</v>
@@ -5195,7 +5210,7 @@
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5207,10 +5222,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5219,10 +5234,10 @@
         <v>149</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5230,7 +5245,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5242,10 +5257,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5254,10 +5269,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5265,7 +5280,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5274,13 +5289,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5292,7 +5307,7 @@
         <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5300,7 +5315,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5309,13 +5324,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5327,7 +5342,7 @@
         <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5335,7 +5350,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5344,13 +5359,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5359,10 +5374,10 @@
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5370,7 +5385,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5379,13 +5394,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5394,10 +5409,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5405,7 +5420,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5417,10 +5432,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5432,7 +5447,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5440,7 +5455,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5449,13 +5464,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5464,10 +5479,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5475,7 +5490,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5484,13 +5499,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5502,7 +5517,7 @@
         <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5510,7 +5525,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5519,13 +5534,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5537,7 +5552,7 @@
         <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5545,7 +5560,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5557,10 +5572,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5569,10 +5584,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5580,7 +5595,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5592,10 +5607,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5604,10 +5619,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5615,7 +5630,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5627,10 +5642,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5639,10 +5654,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5650,7 +5665,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5662,10 +5677,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5674,10 +5689,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5685,22 +5700,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5712,7 +5727,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5720,22 +5735,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="B76" s="23" t="s">
         <v>479</v>
-      </c>
-      <c r="B76" s="23" t="s">
-        <v>474</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5747,7 +5762,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5755,22 +5770,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5779,10 +5794,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5790,22 +5805,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5814,10 +5829,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5825,22 +5840,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5852,7 +5867,7 @@
         <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5860,22 +5875,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5887,7 +5902,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5895,22 +5910,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5922,7 +5937,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5930,22 +5945,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5954,10 +5969,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5965,10 +5980,10 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
@@ -5977,10 +5992,10 @@
         <v>392</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -5989,10 +6004,10 @@
         <v>170</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -6000,10 +6015,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -6012,10 +6027,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6024,10 +6039,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="26" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6067,12 +6082,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6086,19 +6101,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6121,10 +6136,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>522</v>
+        <v>527</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6147,10 +6162,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6173,10 +6188,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6199,7 +6214,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6223,7 +6238,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6247,10 +6262,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6273,7 +6288,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6297,7 +6312,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6321,10 +6336,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6347,7 +6362,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6371,7 +6386,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6395,7 +6410,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6419,7 +6434,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6443,15 +6458,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6459,7 +6474,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6467,7 +6482,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>531</v>
+        <v>536</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6496,7 +6511,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>532</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6513,10 +6528,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>534</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6524,7 +6539,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6533,10 +6548,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>537</v>
+        <v>542</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6544,7 +6559,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>538</v>
+        <v>543</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6556,7 +6571,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>539</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6564,7 +6579,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6573,10 +6588,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6584,7 +6599,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6593,10 +6608,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6610,18 +6625,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6630,53 +6645,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>555</v>
+        <v>560</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>559</v>
+        <v>564</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>560</v>
+        <v>565</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -6701,26 +6716,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>562</v>
+        <v>567</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>563</v>
+        <v>568</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>566</v>
+        <v>571</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6728,13 +6743,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6742,13 +6757,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6756,13 +6771,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6770,13 +6785,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6784,13 +6799,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6798,13 +6813,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6812,13 +6827,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6826,13 +6841,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6846,7 +6861,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6854,13 +6869,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>586</v>
+        <v>591</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6868,21 +6883,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6918,7 +6933,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>591</v>
+        <v>596</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6926,7 +6941,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6938,167 +6953,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>593</v>
+        <v>598</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
   </sheetData>
@@ -7130,7 +7145,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>596</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7150,47 +7165,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>597</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7201,16 +7216,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>599</v>
+        <v>604</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>600</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7218,19 +7233,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>602</v>
+        <v>607</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>603</v>
+        <v>608</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7238,19 +7253,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>605</v>
+        <v>610</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>608</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7261,16 +7276,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -677,7 +677,7 @@
     <t>File format agreed; 20 questions in the repo</t>
   </si>
   <si>
-    <t>🚧 Local evidence verified — pending founder sign-off that the format is agreed</t>
+    <t>✅ Done (owner sign-off on the golden-set v1 format given in the Arena conversation 2026-10-26; format + 20 starter questions verified locally against the real pipeline via npm run eval)</t>
   </si>
   <si>
     <t>W00-16</t>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="618">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1284,6 +1284,9 @@
   </si>
   <si>
     <t>Dashboard numbers reconcile exactly to raw events</t>
+  </si>
+  <si>
+    <t>🚧 AC-2 and AC-3 met and verified (0029 hardening; reconcile() over 8 pairs, deltas 0; 100 actions -&gt; exactly 100 events; 39 db files / 415 + 48 unit / 629 green). AC-1 is 16 of 18: booking_link_clicked and outbound_webhook_delivered have no producer — they belong to DF-02 and DF-01, both deferred to MVP-1.5. Owner deferred on 2026-10-26; both names stay reserved in the taxonomy and a test fails if either gains a producer before the charter is updated.</t>
   </si>
   <si>
     <t>S10-02</t>
@@ -5205,12 +5208,12 @@
         <v>420</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>151</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5222,10 +5225,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5237,7 +5240,7 @@
         <v>417</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5245,7 +5248,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5257,10 +5260,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5269,10 +5272,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5280,7 +5283,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5289,13 +5292,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5307,7 +5310,7 @@
         <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5315,7 +5318,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5324,13 +5327,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5342,7 +5345,7 @@
         <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5350,7 +5353,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5359,13 +5362,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5377,7 +5380,7 @@
         <v>417</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5385,7 +5388,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5394,13 +5397,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5409,10 +5412,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5420,7 +5423,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5432,10 +5435,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5447,7 +5450,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5455,7 +5458,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5464,13 +5467,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5479,10 +5482,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5490,7 +5493,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5499,13 +5502,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5517,7 +5520,7 @@
         <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5525,7 +5528,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5534,13 +5537,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5552,7 +5555,7 @@
         <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5560,7 +5563,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5572,10 +5575,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5584,10 +5587,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5595,7 +5598,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5607,10 +5610,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5619,10 +5622,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5630,7 +5633,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5642,10 +5645,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5654,10 +5657,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5665,7 +5668,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5677,10 +5680,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5689,10 +5692,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5700,22 +5703,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5727,7 +5730,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5735,22 +5738,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5762,7 +5765,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5770,22 +5773,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5794,10 +5797,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5805,22 +5808,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5829,10 +5832,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5840,22 +5843,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5867,7 +5870,7 @@
         <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5875,22 +5878,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5902,7 +5905,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5910,22 +5913,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5937,7 +5940,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5945,22 +5948,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5969,10 +5972,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5980,10 +5983,10 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
@@ -5992,10 +5995,10 @@
         <v>392</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -6007,7 +6010,7 @@
         <v>412</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -6015,10 +6018,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -6027,10 +6030,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6042,7 +6045,7 @@
         <v>417</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6082,12 +6085,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6101,19 +6104,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6136,10 +6139,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6162,10 +6165,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6188,10 +6191,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>531</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6214,7 +6217,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6238,7 +6241,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6262,10 +6265,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>531</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6288,7 +6291,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6312,7 +6315,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6336,10 +6339,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>531</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6362,7 +6365,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6386,7 +6389,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6410,7 +6413,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6434,7 +6437,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6458,15 +6461,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6474,7 +6477,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6482,7 +6485,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6511,7 +6514,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6528,10 +6531,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6539,7 +6542,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6548,10 +6551,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6559,7 +6562,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6571,7 +6574,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6579,7 +6582,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6588,10 +6591,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6599,7 +6602,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6608,10 +6611,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6625,18 +6628,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6645,53 +6648,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -6716,26 +6719,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6743,13 +6746,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6757,13 +6760,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,13 +6774,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6785,13 +6788,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6799,13 +6802,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6813,13 +6816,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6827,13 +6830,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6841,13 +6844,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6861,7 +6864,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6869,13 +6872,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6883,21 +6886,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6941,7 +6944,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6953,167 +6956,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -7145,7 +7148,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7165,47 +7168,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7216,16 +7219,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7233,19 +7236,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7253,19 +7256,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7276,16 +7279,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="618">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -677,7 +677,7 @@
     <t>File format agreed; 20 questions in the repo</t>
   </si>
   <si>
-    <t>🚧 Local evidence verified — pending founder sign-off that the format is agreed</t>
+    <t>✅ Done (owner sign-off on the golden-set v1 format given in the Arena conversation 2026-10-26; format + 20 starter questions verified locally against the real pipeline via npm run eval)</t>
   </si>
   <si>
     <t>W00-16</t>
@@ -1284,6 +1284,9 @@
   </si>
   <si>
     <t>Dashboard numbers reconcile exactly to raw events</t>
+  </si>
+  <si>
+    <t>🚧 AC-2 and AC-3 met and verified (0029 hardening; reconcile() over 8 pairs, deltas 0; 100 actions -&gt; exactly 100 events; 39 db files / 415 + 48 unit / 629 green). AC-1 is 16 of 18: booking_link_clicked and outbound_webhook_delivered have no producer — they belong to DF-02 and DF-01, both deferred to MVP-1.5. Owner deferred on 2026-10-26; both names stay reserved in the taxonomy and a test fails if either gains a producer before the charter is updated.</t>
   </si>
   <si>
     <t>S10-02</t>
@@ -5205,12 +5208,12 @@
         <v>420</v>
       </c>
       <c r="K60" s="11" t="s">
-        <v>151</v>
+        <v>421</v>
       </c>
     </row>
     <row r="61" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>105</v>
@@ -5222,10 +5225,10 @@
         <v>107</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G61" s="12">
         <v>1</v>
@@ -5237,7 +5240,7 @@
         <v>417</v>
       </c>
       <c r="J61" s="11" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>151</v>
@@ -5245,7 +5248,7 @@
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5257,10 +5260,10 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G62" s="12">
         <v>2</v>
@@ -5269,10 +5272,10 @@
         <v>149</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>151</v>
@@ -5280,7 +5283,7 @@
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>110</v>
@@ -5289,13 +5292,13 @@
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G63" s="12">
         <v>1.5</v>
@@ -5307,7 +5310,7 @@
         <v>324</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5315,7 +5318,7 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>110</v>
@@ -5324,13 +5327,13 @@
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G64" s="12">
         <v>1</v>
@@ -5342,7 +5345,7 @@
         <v>324</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5350,7 +5353,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5359,13 +5362,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G65" s="12">
         <v>1</v>
@@ -5377,7 +5380,7 @@
         <v>417</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5385,7 +5388,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5394,13 +5397,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5409,10 +5412,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5420,7 +5423,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5432,10 +5435,10 @@
         <v>214</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G67" s="12">
         <v>0.5</v>
@@ -5447,7 +5450,7 @@
         <v>275</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5455,7 +5458,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>115</v>
@@ -5464,13 +5467,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5479,10 +5482,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5490,7 +5493,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>115</v>
@@ -5499,13 +5502,13 @@
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G69" s="12">
         <v>1</v>
@@ -5517,7 +5520,7 @@
         <v>370</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5525,7 +5528,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5534,13 +5537,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5552,7 +5555,7 @@
         <v>370</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5560,7 +5563,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5572,10 +5575,10 @@
         <v>190</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G71" s="12">
         <v>1.5</v>
@@ -5584,10 +5587,10 @@
         <v>149</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5595,7 +5598,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>121</v>
@@ -5607,10 +5610,10 @@
         <v>190</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5619,10 +5622,10 @@
         <v>149</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5630,7 +5633,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>121</v>
@@ -5642,10 +5645,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G73" s="12">
         <v>0.5</v>
@@ -5654,10 +5657,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5665,7 +5668,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5677,10 +5680,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G74" s="12">
         <v>0.5</v>
@@ -5689,10 +5692,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5700,22 +5703,22 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C75" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G75" s="24">
         <v>0.25</v>
@@ -5727,7 +5730,7 @@
         <v>181</v>
       </c>
       <c r="J75" s="23" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K75" s="23" t="s">
         <v>151</v>
@@ -5735,22 +5738,22 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C76" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G76" s="24">
         <v>1.5</v>
@@ -5762,7 +5765,7 @@
         <v>185</v>
       </c>
       <c r="J76" s="23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K76" s="23" t="s">
         <v>151</v>
@@ -5770,22 +5773,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G77" s="24">
         <v>1.5</v>
@@ -5794,10 +5797,10 @@
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5805,22 +5808,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G78" s="24">
         <v>1</v>
@@ -5829,10 +5832,10 @@
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5840,22 +5843,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G79" s="24">
         <v>1</v>
@@ -5867,7 +5870,7 @@
         <v>314</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5875,22 +5878,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5902,7 +5905,7 @@
         <v>185</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5910,22 +5913,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G81" s="24">
         <v>0.5</v>
@@ -5937,7 +5940,7 @@
         <v>162</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5945,22 +5948,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -5969,10 +5972,10 @@
         <v>170</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -5980,10 +5983,10 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="25" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
@@ -5992,10 +5995,10 @@
         <v>392</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G83" s="27">
         <v>1</v>
@@ -6007,7 +6010,7 @@
         <v>412</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>151</v>
@@ -6015,10 +6018,10 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="25" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
@@ -6027,10 +6030,10 @@
         <v>107</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G84" s="27">
         <v>0.5</v>
@@ -6042,7 +6045,7 @@
         <v>417</v>
       </c>
       <c r="J84" s="26" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K84" s="26" t="s">
         <v>151</v>
@@ -6082,12 +6085,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6101,19 +6104,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6136,10 +6139,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6162,10 +6165,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6188,10 +6191,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>531</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6214,7 +6217,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6238,7 +6241,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6262,10 +6265,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>531</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6288,7 +6291,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6312,7 +6315,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6336,10 +6339,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>532</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>531</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6362,7 +6365,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6386,7 +6389,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6410,7 +6413,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6434,7 +6437,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6458,15 +6461,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6474,7 +6477,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6482,7 +6485,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6511,7 +6514,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6528,10 +6531,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6539,7 +6542,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6548,10 +6551,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6559,7 +6562,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6571,7 +6574,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6579,7 +6582,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6588,10 +6591,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6599,7 +6602,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6608,10 +6611,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6625,18 +6628,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6645,53 +6648,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
   </sheetData>
@@ -6716,26 +6719,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6743,13 +6746,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6757,13 +6760,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6771,13 +6774,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6785,13 +6788,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6799,13 +6802,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6813,13 +6816,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6827,13 +6830,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6841,13 +6844,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6861,7 +6864,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6869,13 +6872,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6883,21 +6886,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6933,7 +6936,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6941,7 +6944,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6953,167 +6956,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>
@@ -7145,7 +7148,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7165,47 +7168,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7216,16 +7219,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7233,19 +7236,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7253,19 +7256,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7276,16 +7279,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="628">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1287,6 +1287,36 @@
   </si>
   <si>
     <t>🚧 AC-2 and AC-3 met and verified (0029 hardening; reconcile() over 8 pairs, deltas 0; 100 actions -&gt; exactly 100 events; 39 db files / 415 + 48 unit / 629 green). AC-1 is 16 of 18: booking_link_clicked and outbound_webhook_delivered have no producer — they belong to DF-02 and DF-01, both deferred to MVP-1.5. Owner deferred on 2026-10-26; both names stay reserved in the taxonomy and a test fails if either gains a producer before the charter is updated.</t>
+  </si>
+  <si>
+    <t>S10-01-1</t>
+  </si>
+  <si>
+    <t>One clock for events and their business rows</t>
+  </si>
+  <si>
+    <t>Producers stamp each event from their own row's created_at (INSERT ... RETURNING), so a windowed reconcile can never split a pair. Found in the S10-01 review; owner chose option 3.</t>
+  </si>
+  <si>
+    <t>Every reconciled pair agrees on created_at exactly, and no window reports a delta that is not real drift</t>
+  </si>
+  <si>
+    <t>🚧 Implemented and verified locally (clock-agreement: 12 tests over all 8 metrics; db 40 files / 427, unit 49 / 638) — pending merge, then ✅</t>
+  </si>
+  <si>
+    <t>S10-01-2</t>
+  </si>
+  <si>
+    <t>AC-1 emission scan via the TypeScript AST</t>
+  </si>
+  <si>
+    <t>The coverage scan parses source instead of matching text, so commented-out and in-string emitEvent calls no longer count as producers. Found in the S10-01 review; option 3 of the issue.</t>
+  </si>
+  <si>
+    <t>A commented-out emit cannot satisfy AC-1, and an aliased import is still recognised</t>
+  </si>
+  <si>
+    <t>✅ Done (merged in PR #146 — tests/events/emission-coverage.test.ts, 8 tests; finds the same 16 of 18 names the regex did)</t>
   </si>
   <si>
     <t>S10-02</t>
@@ -3191,7 +3221,7 @@
     <tabColor rgb="00A9D08E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K86"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5231,7 +5261,7 @@
         <v>424</v>
       </c>
       <c r="G61" s="12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H61" s="11" t="s">
         <v>149</v>
@@ -5243,12 +5273,12 @@
         <v>425</v>
       </c>
       <c r="K61" s="11" t="s">
-        <v>151</v>
+        <v>426</v>
       </c>
     </row>
     <row r="62" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>105</v>
@@ -5260,57 +5290,57 @@
         <v>107</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="G62" s="12">
-        <v>2</v>
+        <v>0.25</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K62" s="11" t="s">
-        <v>151</v>
+        <v>431</v>
       </c>
     </row>
     <row r="63" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C63" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G63" s="12">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H63" s="11" t="s">
         <v>149</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>324</v>
+        <v>417</v>
       </c>
       <c r="J63" s="11" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>151</v>
@@ -5318,34 +5348,34 @@
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C64" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>431</v>
+        <v>107</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="G64" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>149</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>324</v>
+        <v>432</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5353,7 +5383,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5362,25 +5392,25 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G65" s="12">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H65" s="11" t="s">
         <v>149</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>417</v>
+        <v>324</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5388,7 +5418,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5397,13 +5427,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5412,10 +5442,10 @@
         <v>149</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>430</v>
+        <v>324</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5423,7 +5453,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5432,25 +5462,25 @@
         <v>195</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>214</v>
+        <v>441</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="G67" s="12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H67" s="11" t="s">
         <v>149</v>
       </c>
       <c r="I67" s="11" t="s">
-        <v>275</v>
+        <v>417</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5458,22 +5488,22 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C68" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5482,10 +5512,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5493,34 +5523,34 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C69" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>431</v>
+        <v>214</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G69" s="12">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="I69" s="11" t="s">
-        <v>370</v>
+        <v>275</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5528,7 +5558,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5537,25 +5567,25 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>370</v>
+        <v>453</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5563,34 +5593,34 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="C71" s="21" t="s">
-        <v>237</v>
+      <c r="C71" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>190</v>
+        <v>441</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G71" s="12">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I71" s="11" t="s">
-        <v>451</v>
+        <v>370</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5598,34 +5628,34 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="C72" s="19" t="s">
-        <v>145</v>
+        <v>115</v>
+      </c>
+      <c r="C72" s="20" t="s">
+        <v>195</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>190</v>
+        <v>441</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="I72" s="11" t="s">
-        <v>463</v>
+        <v>370</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5633,10 +5663,10 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C73" s="21" t="s">
         <v>237</v>
@@ -5645,22 +5675,22 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="G73" s="12">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="H73" s="11" t="s">
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5668,7 +5698,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5680,94 +5710,94 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="G74" s="12">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H74" s="11" t="s">
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A75" s="22" t="s">
-        <v>479</v>
-      </c>
-      <c r="B75" s="23" t="s">
-        <v>480</v>
-      </c>
-      <c r="C75" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D75" s="23" t="s">
+      <c r="A75" s="10" t="s">
         <v>481</v>
       </c>
-      <c r="E75" s="23" t="s">
+      <c r="B75" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E75" s="11" t="s">
         <v>482</v>
       </c>
-      <c r="F75" s="23" t="s">
+      <c r="F75" s="11" t="s">
         <v>483</v>
       </c>
-      <c r="G75" s="24">
-        <v>0.25</v>
-      </c>
-      <c r="H75" s="23" t="s">
+      <c r="G75" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="I75" s="23" t="s">
-        <v>181</v>
-      </c>
-      <c r="J75" s="23" t="s">
+      <c r="I75" s="11" t="s">
+        <v>473</v>
+      </c>
+      <c r="J75" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="K75" s="23" t="s">
+      <c r="K75" s="11" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A76" s="22" t="s">
+      <c r="A76" s="10" t="s">
         <v>485</v>
       </c>
-      <c r="B76" s="23" t="s">
-        <v>480</v>
-      </c>
-      <c r="C76" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>481</v>
-      </c>
-      <c r="E76" s="23" t="s">
+      <c r="B76" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E76" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="F76" s="23" t="s">
+      <c r="F76" s="11" t="s">
         <v>487</v>
       </c>
-      <c r="G76" s="24">
-        <v>1.5</v>
-      </c>
-      <c r="H76" s="23" t="s">
+      <c r="G76" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="H76" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="I76" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="J76" s="23" t="s">
+      <c r="I76" s="11" t="s">
+        <v>477</v>
+      </c>
+      <c r="J76" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="K76" s="23" t="s">
+      <c r="K76" s="11" t="s">
         <v>151</v>
       </c>
     </row>
@@ -5776,31 +5806,31 @@
         <v>489</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="G77" s="24">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="H77" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I77" s="23" t="s">
-        <v>485</v>
+        <v>181</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5808,34 +5838,34 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G78" s="24">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H78" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I78" s="23" t="s">
-        <v>489</v>
+        <v>185</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5843,34 +5873,34 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G79" s="24">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H79" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>314</v>
+        <v>495</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5878,22 +5908,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5902,10 +5932,10 @@
         <v>149</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>185</v>
+        <v>499</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5913,34 +5943,34 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G81" s="24">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H81" s="23" t="s">
         <v>149</v>
       </c>
       <c r="I81" s="23" t="s">
-        <v>162</v>
+        <v>314</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5948,106 +5978,176 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="I82" s="23" t="s">
-        <v>489</v>
+        <v>185</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83" s="25" t="s">
-        <v>513</v>
-      </c>
-      <c r="B83" s="26" t="s">
-        <v>514</v>
+      <c r="A83" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="B83" s="23" t="s">
+        <v>490</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="D83" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="E83" s="26" t="s">
-        <v>515</v>
-      </c>
-      <c r="F83" s="26" t="s">
+      <c r="D83" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="E83" s="23" t="s">
         <v>516</v>
       </c>
-      <c r="G83" s="27">
-        <v>1</v>
-      </c>
-      <c r="H83" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="I83" s="26" t="s">
-        <v>412</v>
-      </c>
-      <c r="J83" s="26" t="s">
+      <c r="F83" s="23" t="s">
         <v>517</v>
       </c>
-      <c r="K83" s="26" t="s">
+      <c r="G83" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="H83" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="I83" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="J83" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="K83" s="23" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="25" t="s">
-        <v>518</v>
-      </c>
-      <c r="B84" s="26" t="s">
-        <v>514</v>
+      <c r="A84" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="B84" s="23" t="s">
+        <v>490</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="D84" s="26" t="s">
+      <c r="D84" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="E84" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="F84" s="23" t="s">
+        <v>521</v>
+      </c>
+      <c r="G84" s="24">
+        <v>1</v>
+      </c>
+      <c r="H84" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="I84" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="J84" s="23" t="s">
+        <v>522</v>
+      </c>
+      <c r="K84" s="23" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="85" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="25" t="s">
+        <v>523</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="C85" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D85" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="E85" s="26" t="s">
+        <v>525</v>
+      </c>
+      <c r="F85" s="26" t="s">
+        <v>526</v>
+      </c>
+      <c r="G85" s="27">
+        <v>1</v>
+      </c>
+      <c r="H85" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="I85" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="J85" s="26" t="s">
+        <v>527</v>
+      </c>
+      <c r="K85" s="26" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="86" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>524</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D86" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="E84" s="26" t="s">
-        <v>519</v>
-      </c>
-      <c r="F84" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="G84" s="27">
+      <c r="E86" s="26" t="s">
+        <v>529</v>
+      </c>
+      <c r="F86" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="G86" s="27">
         <v>0.5</v>
       </c>
-      <c r="H84" s="26" t="s">
+      <c r="H86" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="I84" s="26" t="s">
+      <c r="I86" s="26" t="s">
         <v>417</v>
       </c>
-      <c r="J84" s="26" t="s">
-        <v>521</v>
-      </c>
-      <c r="K84" s="26" t="s">
+      <c r="J86" s="26" t="s">
+        <v>531</v>
+      </c>
+      <c r="K86" s="26" t="s">
         <v>151</v>
       </c>
     </row>
@@ -6085,12 +6185,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>522</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>523</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6104,19 +6204,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>524</v>
+        <v>534</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>525</v>
+        <v>535</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>526</v>
+        <v>536</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>527</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6139,10 +6239,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>529</v>
+        <v>539</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6165,10 +6265,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6191,10 +6291,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6217,7 +6317,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6241,7 +6341,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6265,10 +6365,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6291,7 +6391,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6315,7 +6415,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6339,10 +6439,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>532</v>
+        <v>542</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6365,7 +6465,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6389,7 +6489,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6413,7 +6513,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6437,7 +6537,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6461,15 +6561,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>534</v>
+        <v>544</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>535</v>
+        <v>545</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6477,7 +6577,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>536</v>
+        <v>546</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6485,7 +6585,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6514,7 +6614,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>538</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6531,10 +6631,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>539</v>
+        <v>549</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>540</v>
+        <v>550</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6542,7 +6642,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>541</v>
+        <v>551</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6551,10 +6651,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>542</v>
+        <v>552</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>543</v>
+        <v>553</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6562,7 +6662,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6574,7 +6674,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>545</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6582,7 +6682,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>546</v>
+        <v>556</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6591,10 +6691,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>547</v>
+        <v>557</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>548</v>
+        <v>558</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6602,7 +6702,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6611,10 +6711,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>550</v>
+        <v>560</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>551</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6628,18 +6728,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>553</v>
+        <v>563</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>554</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>555</v>
+        <v>565</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6648,53 +6748,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -6719,26 +6819,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6746,13 +6846,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>573</v>
+        <v>583</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>575</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6760,13 +6860,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6774,13 +6874,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>579</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6788,13 +6888,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>580</v>
+        <v>590</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6802,13 +6902,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6816,13 +6916,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>584</v>
+        <v>594</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>585</v>
+        <v>595</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6830,13 +6930,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>586</v>
+        <v>596</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>587</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6844,13 +6944,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>589</v>
+        <v>599</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6864,7 +6964,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>590</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6872,13 +6972,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>592</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6886,21 +6986,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>593</v>
+        <v>603</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>594</v>
+        <v>604</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>596</v>
+        <v>606</v>
       </c>
       <c r="D17"/>
     </row>
@@ -6936,7 +7036,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>597</v>
+        <v>607</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6944,7 +7044,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>598</v>
+        <v>608</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -6956,167 +7056,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>599</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>493</v>
+        <v>503</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>494</v>
+        <v>504</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>496</v>
+        <v>506</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>497</v>
+        <v>507</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>600</v>
+        <v>610</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>498</v>
+        <v>508</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>504</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>505</v>
+        <v>515</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>508</v>
+        <v>518</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>601</v>
+        <v>611</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>512</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -7148,7 +7248,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>602</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7168,47 +7268,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>603</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>521</v>
+        <v>531</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7219,16 +7319,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>604</v>
+        <v>614</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>605</v>
+        <v>615</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>606</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7236,19 +7336,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>607</v>
+        <v>617</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>608</v>
+        <v>618</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>609</v>
+        <v>619</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>610</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7256,19 +7356,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>612</v>
+        <v>622</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>613</v>
+        <v>623</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>614</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7279,16 +7379,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>615</v>
+        <v>625</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>616</v>
+        <v>626</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>617</v>
+        <v>627</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -1286,7 +1286,7 @@
     <t>Dashboard numbers reconcile exactly to raw events</t>
   </si>
   <si>
-    <t>🚧 AC-2 and AC-3 met and verified (0029 hardening; reconcile() over 8 pairs, deltas 0; 100 actions -&gt; exactly 100 events; 39 db files / 415 + 48 unit / 629 green). AC-1 is 16 of 18: booking_link_clicked and outbound_webhook_delivered have no producer — they belong to DF-02 and DF-01, both deferred to MVP-1.5. Owner deferred on 2026-10-26; both names stay reserved in the taxonomy and a test fails if either gains a producer before the charter is updated.</t>
+    <t>✅ Done (merged in PR #146 as 12ebab0. AC-2 and AC-3 met and verified: 0029 append-only hardening, reconcile() over 8 business/event pairs with deltas 0, 100 actions produce exactly 100 events. AC-1 accepted at 16 of 18 — booking_link_clicked and outbound_webhook_delivered have no producer; they belong to DF-02 and DF-01, both deferred to MVP-1.5 by the owner on 2026-10-26. Both names stay reserved in the taxonomy and a test fails if either gains a producer before the charter is updated. Follow-ups: S10-01-2 merged in #146, S10-01-1 merged in #149.)</t>
   </si>
   <si>
     <t>S10-01-1</t>
@@ -1301,7 +1301,7 @@
     <t>Every reconciled pair agrees on created_at exactly, and no window reports a delta that is not real drift</t>
   </si>
   <si>
-    <t>🚧 Implemented and verified locally (clock-agreement: 12 tests over all 8 metrics; db 40 files / 427, unit 49 / 638) — pending merge, then ✅</t>
+    <t>✅ Done (merged in PR #149 as 44b31f0 — src/events/clock.ts; every producer reads created_at back from its own INSERT and hands that exact value to emitEvent, so a business row and its event carry one identical stamp and no reconcile window boundary can fall between them. tests/db/clock-agreement.db.test.ts: 12 tests drive the real producers for all 8 metrics and compare e.created_at &lt;&gt; b.created_at in SQL. Also fixed the ai_runs window metric, which counted answer_flagged_wrong as a run and so reported phantom drift; AI_RUN_TERMINAL_EVENT_TYPES now classifies it. db 40 files / 427, unit 49 files / 638, CI 8/8.)</t>
   </si>
   <si>
     <t>S10-01-2</t>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="629">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1329,6 +1329,9 @@
   </si>
   <si>
     <t>A historical date can be recomputed without drift</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: 12 metrics in src/analytics/rollups.ts over events/conversations/messages/service_requests, days in the property's own time zone; idempotent re-run proven in the db test AND at the CLI (diff IDENTICAL); AC-2 asserted per metric against a direct count(*) FROM events. No migration needed — rollups/UNIQUE/RLS/index already existed, migrations stay at 29. Nightly scheduling deferred by the owner (DEC-1) to S11-01/W00-13; script is manual + CI-exercised. 41 db / 437 · 50 unit / 647.)</t>
   </si>
   <si>
     <t>S10-03</t>
@@ -5343,12 +5346,12 @@
         <v>435</v>
       </c>
       <c r="K63" s="11" t="s">
-        <v>151</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>105</v>
@@ -5360,10 +5363,10 @@
         <v>107</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="G64" s="12">
         <v>2</v>
@@ -5375,7 +5378,7 @@
         <v>432</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>151</v>
@@ -5383,7 +5386,7 @@
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5392,13 +5395,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G65" s="12">
         <v>1.5</v>
@@ -5410,7 +5413,7 @@
         <v>324</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5418,7 +5421,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5427,13 +5430,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5445,7 +5448,7 @@
         <v>324</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5453,7 +5456,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5462,13 +5465,13 @@
         <v>195</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G67" s="12">
         <v>1</v>
@@ -5480,7 +5483,7 @@
         <v>417</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5488,7 +5491,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>110</v>
@@ -5497,13 +5500,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5512,10 +5515,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5523,7 +5526,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>110</v>
@@ -5535,10 +5538,10 @@
         <v>214</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G69" s="12">
         <v>0.5</v>
@@ -5550,7 +5553,7 @@
         <v>275</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5558,7 +5561,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5567,13 +5570,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5582,10 +5585,10 @@
         <v>149</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5593,7 +5596,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5602,13 +5605,13 @@
         <v>195</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G71" s="12">
         <v>1</v>
@@ -5620,7 +5623,7 @@
         <v>370</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5628,7 +5631,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>115</v>
@@ -5637,13 +5640,13 @@
         <v>195</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5655,7 +5658,7 @@
         <v>370</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5663,7 +5666,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>115</v>
@@ -5675,10 +5678,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G73" s="12">
         <v>1.5</v>
@@ -5687,10 +5690,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5698,7 +5701,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5710,10 +5713,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G74" s="12">
         <v>1</v>
@@ -5722,10 +5725,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5733,7 +5736,7 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>121</v>
@@ -5745,10 +5748,10 @@
         <v>190</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G75" s="12">
         <v>0.5</v>
@@ -5757,10 +5760,10 @@
         <v>149</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>151</v>
@@ -5768,7 +5771,7 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>121</v>
@@ -5780,10 +5783,10 @@
         <v>190</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G76" s="12">
         <v>0.5</v>
@@ -5792,10 +5795,10 @@
         <v>149</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>151</v>
@@ -5803,22 +5806,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="G77" s="24">
         <v>0.25</v>
@@ -5830,7 +5833,7 @@
         <v>181</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5838,22 +5841,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G78" s="24">
         <v>1.5</v>
@@ -5865,7 +5868,7 @@
         <v>185</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5873,22 +5876,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G79" s="24">
         <v>1.5</v>
@@ -5897,10 +5900,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5908,22 +5911,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5932,10 +5935,10 @@
         <v>149</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5943,22 +5946,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G81" s="24">
         <v>1</v>
@@ -5970,7 +5973,7 @@
         <v>314</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5978,22 +5981,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -6005,7 +6008,7 @@
         <v>185</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -6013,22 +6016,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G83" s="24">
         <v>0.5</v>
@@ -6040,7 +6043,7 @@
         <v>162</v>
       </c>
       <c r="J83" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K83" s="23" t="s">
         <v>151</v>
@@ -6048,22 +6051,22 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F84" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="G84" s="24">
         <v>1</v>
@@ -6072,10 +6075,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="J84" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K84" s="23" t="s">
         <v>151</v>
@@ -6083,10 +6086,10 @@
     </row>
     <row r="85" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="25" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C85" s="20" t="s">
         <v>195</v>
@@ -6095,10 +6098,10 @@
         <v>392</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="G85" s="27">
         <v>1</v>
@@ -6110,7 +6113,7 @@
         <v>412</v>
       </c>
       <c r="J85" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K85" s="26" t="s">
         <v>151</v>
@@ -6118,10 +6121,10 @@
     </row>
     <row r="86" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="25" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C86" s="20" t="s">
         <v>195</v>
@@ -6130,10 +6133,10 @@
         <v>107</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G86" s="27">
         <v>0.5</v>
@@ -6145,7 +6148,7 @@
         <v>417</v>
       </c>
       <c r="J86" s="26" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K86" s="26" t="s">
         <v>151</v>
@@ -6185,12 +6188,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6204,19 +6207,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6239,10 +6242,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6265,10 +6268,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6291,10 +6294,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>543</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6317,7 +6320,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6341,7 +6344,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6365,10 +6368,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>543</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6391,7 +6394,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6415,7 +6418,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6439,10 +6442,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>543</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>542</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6465,7 +6468,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6489,7 +6492,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6513,7 +6516,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6537,7 +6540,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6561,15 +6564,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6577,7 +6580,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6585,7 +6588,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6614,7 +6617,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6631,10 +6634,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6642,7 +6645,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6651,10 +6654,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6662,7 +6665,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6674,7 +6677,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6682,7 +6685,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6691,10 +6694,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6702,7 +6705,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6711,10 +6714,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6728,18 +6731,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6748,53 +6751,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -6819,26 +6822,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6846,13 +6849,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6860,13 +6863,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6874,13 +6877,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6888,13 +6891,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6902,13 +6905,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6916,13 +6919,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6930,13 +6933,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6944,13 +6947,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6964,7 +6967,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6972,13 +6975,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6986,21 +6989,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D17"/>
     </row>
@@ -7036,7 +7039,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7044,7 +7047,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -7056,167 +7059,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
@@ -7248,7 +7251,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7268,47 +7271,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7319,16 +7322,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7336,19 +7339,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7356,19 +7359,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7379,16 +7382,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="630">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1344,6 +1344,9 @@
   </si>
   <si>
     <t>Every tile traceable to a query a manager can explain</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: GET /api/analytics + /analytics; each tile carries rollups.metric and the identity-checked SQL from S10-02 (toBe, not a copy) in a &lt;details&gt;; values leave Postgres as text and are only formatted, no totals and no zero-filling, so AC-2 is checkable on the card; 24 tile strings + 17 chrome strings in en+es, label map is Record&lt;RollupMetricName,…&gt; so a missing string is a type error. No migration (29). 42 db / 444 · 51 unit / 653 · web:build emits ƒ /analytics. Screenshot owed — no JWKS in this environment.)</t>
   </si>
   <si>
     <t>S11-01</t>
@@ -5381,12 +5384,12 @@
         <v>440</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>151</v>
+        <v>441</v>
       </c>
     </row>
     <row r="65" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>110</v>
@@ -5395,13 +5398,13 @@
         <v>195</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G65" s="12">
         <v>1.5</v>
@@ -5413,7 +5416,7 @@
         <v>324</v>
       </c>
       <c r="J65" s="11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>151</v>
@@ -5421,7 +5424,7 @@
     </row>
     <row r="66" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>110</v>
@@ -5430,13 +5433,13 @@
         <v>195</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G66" s="12">
         <v>1</v>
@@ -5448,7 +5451,7 @@
         <v>324</v>
       </c>
       <c r="J66" s="11" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>151</v>
@@ -5456,7 +5459,7 @@
     </row>
     <row r="67" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>110</v>
@@ -5465,13 +5468,13 @@
         <v>195</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G67" s="12">
         <v>1</v>
@@ -5483,7 +5486,7 @@
         <v>417</v>
       </c>
       <c r="J67" s="11" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>151</v>
@@ -5491,7 +5494,7 @@
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>110</v>
@@ -5500,13 +5503,13 @@
         <v>195</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5515,10 +5518,10 @@
         <v>149</v>
       </c>
       <c r="I68" s="11" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5526,7 +5529,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>110</v>
@@ -5538,10 +5541,10 @@
         <v>214</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G69" s="12">
         <v>0.5</v>
@@ -5553,7 +5556,7 @@
         <v>275</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5561,7 +5564,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5570,13 +5573,13 @@
         <v>195</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5585,10 +5588,10 @@
         <v>149</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5596,7 +5599,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5605,13 +5608,13 @@
         <v>195</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G71" s="12">
         <v>1</v>
@@ -5623,7 +5626,7 @@
         <v>370</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5631,7 +5634,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>115</v>
@@ -5640,13 +5643,13 @@
         <v>195</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5658,7 +5661,7 @@
         <v>370</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5666,7 +5669,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>115</v>
@@ -5678,10 +5681,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G73" s="12">
         <v>1.5</v>
@@ -5690,10 +5693,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5701,7 +5704,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5713,10 +5716,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="G74" s="12">
         <v>1</v>
@@ -5725,10 +5728,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5736,7 +5739,7 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>121</v>
@@ -5748,10 +5751,10 @@
         <v>190</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="G75" s="12">
         <v>0.5</v>
@@ -5760,10 +5763,10 @@
         <v>149</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>151</v>
@@ -5771,7 +5774,7 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>121</v>
@@ -5783,10 +5786,10 @@
         <v>190</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G76" s="12">
         <v>0.5</v>
@@ -5795,10 +5798,10 @@
         <v>149</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>151</v>
@@ -5806,22 +5809,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G77" s="24">
         <v>0.25</v>
@@ -5833,7 +5836,7 @@
         <v>181</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5841,22 +5844,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G78" s="24">
         <v>1.5</v>
@@ -5868,7 +5871,7 @@
         <v>185</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5876,22 +5879,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G79" s="24">
         <v>1.5</v>
@@ -5900,10 +5903,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5911,22 +5914,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5935,10 +5938,10 @@
         <v>149</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5946,22 +5949,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G81" s="24">
         <v>1</v>
@@ -5973,7 +5976,7 @@
         <v>314</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5981,22 +5984,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -6008,7 +6011,7 @@
         <v>185</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -6016,22 +6019,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="G83" s="24">
         <v>0.5</v>
@@ -6043,7 +6046,7 @@
         <v>162</v>
       </c>
       <c r="J83" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K83" s="23" t="s">
         <v>151</v>
@@ -6051,22 +6054,22 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F84" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G84" s="24">
         <v>1</v>
@@ -6075,10 +6078,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J84" s="23" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K84" s="23" t="s">
         <v>151</v>
@@ -6086,10 +6089,10 @@
     </row>
     <row r="85" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="25" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C85" s="20" t="s">
         <v>195</v>
@@ -6098,10 +6101,10 @@
         <v>392</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G85" s="27">
         <v>1</v>
@@ -6113,7 +6116,7 @@
         <v>412</v>
       </c>
       <c r="J85" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="K85" s="26" t="s">
         <v>151</v>
@@ -6121,10 +6124,10 @@
     </row>
     <row r="86" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="25" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C86" s="20" t="s">
         <v>195</v>
@@ -6133,10 +6136,10 @@
         <v>107</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G86" s="27">
         <v>0.5</v>
@@ -6148,7 +6151,7 @@
         <v>417</v>
       </c>
       <c r="J86" s="26" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="K86" s="26" t="s">
         <v>151</v>
@@ -6188,12 +6191,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6207,19 +6210,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6242,10 +6245,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6268,10 +6271,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6294,10 +6297,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>543</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6320,7 +6323,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6344,7 +6347,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6368,10 +6371,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>543</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6394,7 +6397,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6418,7 +6421,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6442,10 +6445,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>544</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>543</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6468,7 +6471,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6492,7 +6495,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6516,7 +6519,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6540,7 +6543,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6564,15 +6567,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6580,7 +6583,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6588,7 +6591,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6617,7 +6620,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6634,10 +6637,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6645,7 +6648,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6654,10 +6657,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6665,7 +6668,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6677,7 +6680,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6685,7 +6688,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6694,10 +6697,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6705,7 +6708,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6714,10 +6717,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6731,18 +6734,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6751,53 +6754,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -6822,26 +6825,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6849,13 +6852,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6863,13 +6866,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6877,13 +6880,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6891,13 +6894,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6905,13 +6908,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6919,13 +6922,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6933,13 +6936,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6947,13 +6950,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6967,7 +6970,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6975,13 +6978,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6989,21 +6992,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="D17"/>
     </row>
@@ -7039,7 +7042,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7047,7 +7050,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -7059,167 +7062,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -7251,7 +7254,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7271,47 +7274,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7322,16 +7325,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7339,19 +7342,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7359,19 +7362,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7382,16 +7385,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="631">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1386,6 +1386,9 @@
   </si>
   <si>
     <t>A synthetic card number never reaches logs</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: AC-1 hard-refuses the turn above withGuestSession — bogus-slug test proves no property read, row counts prove no writes; maskPii redacts cards/emails/phones in a pino logMethod hook + reportError (UUIDs protected after a test caught them being masked). AC-2: 0030 body_redacted_at + partial index, retention dry-run by default with --apply, row survives and text goes; 91d redacted / 89d untouched / other tenant untouched. AC-3 synthetic 4242 card only. S11-03-1 OPEN: blocked turns are a counter (pii_blocked_total), not a taxonomy event — Appendix C verbatim. 30 migrations, 44 db / 455 · 52 unit / 663.)</t>
   </si>
   <si>
     <t>S11-04</t>
@@ -5489,12 +5492,12 @@
         <v>454</v>
       </c>
       <c r="K67" s="11" t="s">
-        <v>151</v>
+        <v>455</v>
       </c>
     </row>
     <row r="68" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>110</v>
@@ -5506,10 +5509,10 @@
         <v>443</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G68" s="12">
         <v>1</v>
@@ -5521,7 +5524,7 @@
         <v>442</v>
       </c>
       <c r="J68" s="11" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>151</v>
@@ -5529,7 +5532,7 @@
     </row>
     <row r="69" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="10" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>110</v>
@@ -5541,10 +5544,10 @@
         <v>214</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G69" s="12">
         <v>0.5</v>
@@ -5556,7 +5559,7 @@
         <v>275</v>
       </c>
       <c r="J69" s="11" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>151</v>
@@ -5564,7 +5567,7 @@
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5576,10 +5579,10 @@
         <v>443</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5588,10 +5591,10 @@
         <v>149</v>
       </c>
       <c r="I70" s="11" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5599,7 +5602,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5611,10 +5614,10 @@
         <v>443</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="G71" s="12">
         <v>1</v>
@@ -5626,7 +5629,7 @@
         <v>370</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5634,7 +5637,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>115</v>
@@ -5646,10 +5649,10 @@
         <v>443</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5661,7 +5664,7 @@
         <v>370</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5669,7 +5672,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>115</v>
@@ -5681,10 +5684,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G73" s="12">
         <v>1.5</v>
@@ -5693,10 +5696,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5704,7 +5707,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5716,10 +5719,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G74" s="12">
         <v>1</v>
@@ -5728,10 +5731,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5739,7 +5742,7 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>121</v>
@@ -5751,10 +5754,10 @@
         <v>190</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G75" s="12">
         <v>0.5</v>
@@ -5763,10 +5766,10 @@
         <v>149</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>151</v>
@@ -5774,7 +5777,7 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>121</v>
@@ -5786,10 +5789,10 @@
         <v>190</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G76" s="12">
         <v>0.5</v>
@@ -5798,10 +5801,10 @@
         <v>149</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>151</v>
@@ -5809,22 +5812,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G77" s="24">
         <v>0.25</v>
@@ -5836,7 +5839,7 @@
         <v>181</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5844,22 +5847,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G78" s="24">
         <v>1.5</v>
@@ -5871,7 +5874,7 @@
         <v>185</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5879,22 +5882,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G79" s="24">
         <v>1.5</v>
@@ -5903,10 +5906,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5914,22 +5917,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5938,10 +5941,10 @@
         <v>149</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5949,22 +5952,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G81" s="24">
         <v>1</v>
@@ -5976,7 +5979,7 @@
         <v>314</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5984,22 +5987,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -6011,7 +6014,7 @@
         <v>185</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -6019,22 +6022,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G83" s="24">
         <v>0.5</v>
@@ -6046,7 +6049,7 @@
         <v>162</v>
       </c>
       <c r="J83" s="23" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="K83" s="23" t="s">
         <v>151</v>
@@ -6054,22 +6057,22 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F84" s="23" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G84" s="24">
         <v>1</v>
@@ -6078,10 +6081,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J84" s="23" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K84" s="23" t="s">
         <v>151</v>
@@ -6089,10 +6092,10 @@
     </row>
     <row r="85" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="25" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C85" s="20" t="s">
         <v>195</v>
@@ -6101,10 +6104,10 @@
         <v>392</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G85" s="27">
         <v>1</v>
@@ -6116,7 +6119,7 @@
         <v>412</v>
       </c>
       <c r="J85" s="26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K85" s="26" t="s">
         <v>151</v>
@@ -6124,10 +6127,10 @@
     </row>
     <row r="86" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C86" s="20" t="s">
         <v>195</v>
@@ -6136,10 +6139,10 @@
         <v>107</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G86" s="27">
         <v>0.5</v>
@@ -6151,7 +6154,7 @@
         <v>417</v>
       </c>
       <c r="J86" s="26" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K86" s="26" t="s">
         <v>151</v>
@@ -6191,12 +6194,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6210,19 +6213,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6245,10 +6248,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6271,10 +6274,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6297,10 +6300,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>544</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6323,7 +6326,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6347,7 +6350,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6371,10 +6374,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>544</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6397,7 +6400,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6421,7 +6424,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6445,10 +6448,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>545</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>544</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6471,7 +6474,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6495,7 +6498,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6519,7 +6522,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6543,7 +6546,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6567,15 +6570,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6583,7 +6586,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6591,7 +6594,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6620,7 +6623,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6637,10 +6640,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6648,7 +6651,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6657,10 +6660,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6668,7 +6671,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6680,7 +6683,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6688,7 +6691,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6697,10 +6700,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6708,7 +6711,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6717,10 +6720,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6734,18 +6737,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6754,53 +6757,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -6825,26 +6828,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6852,13 +6855,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6866,13 +6869,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6880,13 +6883,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6894,13 +6897,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6908,13 +6911,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6922,13 +6925,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6936,13 +6939,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6950,13 +6953,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6970,7 +6973,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6978,13 +6981,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6992,21 +6995,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D17"/>
     </row>
@@ -7042,7 +7045,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7050,7 +7053,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -7062,167 +7065,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
@@ -7254,7 +7257,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7274,47 +7277,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7325,16 +7328,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7342,19 +7345,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7362,19 +7365,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7385,16 +7388,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="632">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -1413,6 +1413,9 @@
   </si>
   <si>
     <t>Job fails loudly on a seeded drift case</t>
+  </si>
+  <si>
+    <t>✅ Done (2026-10-26: AC-1 three invariants in src/knowledge/reconcile.ts — current version has no chunks (article unretrievable), chunk on a demoted version (stale policy; promote_article_version leaves them, so the db test plants it through the real publish path), orphan chunk (FK cascade makes it impossible today, so the test lifts the constraint to prove the query works). AC-2 seeded drift → exit 1 naming invariant + chunk + version, never repairs; exit 2 for usage so a scheduler can tell 'found drift' from 'could not run'. embedding_drift_total emitted with tenant labels — NO CONSUMER YET (S11-04 blocked behind S11-01 ← S06-01), stated in the runbook. jobs-smoke.yml is workflow_dispatch ONLY (no cron; charter's reconcile-nightly.yml deliberately not created per DECISION 1a) and is a smoke test, not real reconciliation.)</t>
   </si>
   <si>
     <t>S12-01</t>
@@ -5562,12 +5565,12 @@
         <v>463</v>
       </c>
       <c r="K69" s="11" t="s">
-        <v>151</v>
+        <v>464</v>
       </c>
     </row>
     <row r="70" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>115</v>
@@ -5579,10 +5582,10 @@
         <v>443</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G70" s="12">
         <v>1</v>
@@ -5594,7 +5597,7 @@
         <v>456</v>
       </c>
       <c r="J70" s="11" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>151</v>
@@ -5602,7 +5605,7 @@
     </row>
     <row r="71" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>115</v>
@@ -5614,10 +5617,10 @@
         <v>443</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G71" s="12">
         <v>1</v>
@@ -5629,7 +5632,7 @@
         <v>370</v>
       </c>
       <c r="J71" s="11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>151</v>
@@ -5637,7 +5640,7 @@
     </row>
     <row r="72" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>115</v>
@@ -5649,10 +5652,10 @@
         <v>443</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G72" s="12">
         <v>1</v>
@@ -5664,7 +5667,7 @@
         <v>370</v>
       </c>
       <c r="J72" s="11" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>151</v>
@@ -5672,7 +5675,7 @@
     </row>
     <row r="73" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>115</v>
@@ -5684,10 +5687,10 @@
         <v>190</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="G73" s="12">
         <v>1.5</v>
@@ -5696,10 +5699,10 @@
         <v>149</v>
       </c>
       <c r="I73" s="11" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J73" s="11" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>151</v>
@@ -5707,7 +5710,7 @@
     </row>
     <row r="74" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>121</v>
@@ -5719,10 +5722,10 @@
         <v>190</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="G74" s="12">
         <v>1</v>
@@ -5731,10 +5734,10 @@
         <v>149</v>
       </c>
       <c r="I74" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J74" s="11" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>151</v>
@@ -5742,7 +5745,7 @@
     </row>
     <row r="75" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>121</v>
@@ -5754,10 +5757,10 @@
         <v>190</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G75" s="12">
         <v>0.5</v>
@@ -5766,10 +5769,10 @@
         <v>149</v>
       </c>
       <c r="I75" s="11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J75" s="11" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>151</v>
@@ -5777,7 +5780,7 @@
     </row>
     <row r="76" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>121</v>
@@ -5789,10 +5792,10 @@
         <v>190</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G76" s="12">
         <v>0.5</v>
@@ -5801,10 +5804,10 @@
         <v>149</v>
       </c>
       <c r="I76" s="11" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J76" s="11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>151</v>
@@ -5812,22 +5815,22 @@
     </row>
     <row r="77" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C77" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G77" s="24">
         <v>0.25</v>
@@ -5839,7 +5842,7 @@
         <v>181</v>
       </c>
       <c r="J77" s="23" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="K77" s="23" t="s">
         <v>151</v>
@@ -5847,22 +5850,22 @@
     </row>
     <row r="78" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C78" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G78" s="24">
         <v>1.5</v>
@@ -5874,7 +5877,7 @@
         <v>185</v>
       </c>
       <c r="J78" s="23" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="K78" s="23" t="s">
         <v>151</v>
@@ -5882,22 +5885,22 @@
     </row>
     <row r="79" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C79" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E79" s="23" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="G79" s="24">
         <v>1.5</v>
@@ -5906,10 +5909,10 @@
         <v>149</v>
       </c>
       <c r="I79" s="23" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="J79" s="23" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="K79" s="23" t="s">
         <v>151</v>
@@ -5917,22 +5920,22 @@
     </row>
     <row r="80" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="22" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C80" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G80" s="24">
         <v>1</v>
@@ -5941,10 +5944,10 @@
         <v>149</v>
       </c>
       <c r="I80" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J80" s="23" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="K80" s="23" t="s">
         <v>151</v>
@@ -5952,22 +5955,22 @@
     </row>
     <row r="81" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="22" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C81" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G81" s="24">
         <v>1</v>
@@ -5979,7 +5982,7 @@
         <v>314</v>
       </c>
       <c r="J81" s="23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K81" s="23" t="s">
         <v>151</v>
@@ -5987,22 +5990,22 @@
     </row>
     <row r="82" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="22" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C82" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="G82" s="24">
         <v>1</v>
@@ -6014,7 +6017,7 @@
         <v>185</v>
       </c>
       <c r="J82" s="23" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="K82" s="23" t="s">
         <v>151</v>
@@ -6022,22 +6025,22 @@
     </row>
     <row r="83" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="22" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C83" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G83" s="24">
         <v>0.5</v>
@@ -6049,7 +6052,7 @@
         <v>162</v>
       </c>
       <c r="J83" s="23" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="K83" s="23" t="s">
         <v>151</v>
@@ -6057,22 +6060,22 @@
     </row>
     <row r="84" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="22" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C84" s="20" t="s">
         <v>195</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F84" s="23" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G84" s="24">
         <v>1</v>
@@ -6081,10 +6084,10 @@
         <v>170</v>
       </c>
       <c r="I84" s="23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J84" s="23" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="K84" s="23" t="s">
         <v>151</v>
@@ -6092,10 +6095,10 @@
     </row>
     <row r="85" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="25" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C85" s="20" t="s">
         <v>195</v>
@@ -6104,10 +6107,10 @@
         <v>392</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G85" s="27">
         <v>1</v>
@@ -6119,7 +6122,7 @@
         <v>412</v>
       </c>
       <c r="J85" s="26" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="K85" s="26" t="s">
         <v>151</v>
@@ -6127,10 +6130,10 @@
     </row>
     <row r="86" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="25" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C86" s="20" t="s">
         <v>195</v>
@@ -6139,10 +6142,10 @@
         <v>107</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G86" s="27">
         <v>0.5</v>
@@ -6154,7 +6157,7 @@
         <v>417</v>
       </c>
       <c r="J86" s="26" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K86" s="26" t="s">
         <v>151</v>
@@ -6194,12 +6197,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6213,19 +6216,19 @@
         <v>43</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>143</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6248,10 +6251,10 @@
         <v>8</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6274,10 +6277,10 @@
         <v>5.75</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6300,10 +6303,10 @@
         <v>5.5</v>
       </c>
       <c r="G7" s="28" t="s">
+        <v>546</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>545</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6326,7 +6329,7 @@
         <v>5</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H8" s="11"/>
     </row>
@@ -6350,7 +6353,7 @@
         <v>5</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H9" s="11"/>
     </row>
@@ -6374,10 +6377,10 @@
         <v>5.5</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>546</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>545</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6400,7 +6403,7 @@
         <v>5</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H11" s="11"/>
     </row>
@@ -6424,7 +6427,7 @@
         <v>4</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H12" s="11"/>
     </row>
@@ -6448,10 +6451,10 @@
         <v>5.5</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>546</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>545</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -6474,7 +6477,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H14" s="11"/>
     </row>
@@ -6498,7 +6501,7 @@
         <v>4.5</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H15" s="11"/>
     </row>
@@ -6522,7 +6525,7 @@
         <v>5</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H16" s="11"/>
     </row>
@@ -6546,7 +6549,7 @@
         <v>4.5</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H17" s="11"/>
     </row>
@@ -6570,15 +6573,15 @@
         <v>2</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="20" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C20" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="F20" s="30">
         <v>69.75</v>
@@ -6586,7 +6589,7 @@
     </row>
     <row r="21" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C21" s="18" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F21" s="18">
         <v>70</v>
@@ -6594,7 +6597,7 @@
     </row>
     <row r="22" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="F22" s="31">
         <v>0.25</v>
@@ -6623,7 +6626,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6640,10 +6643,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6651,7 +6654,7 @@
         <v>55</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>51</v>
@@ -6660,10 +6663,10 @@
         <v>52</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="5" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6671,7 +6674,7 @@
         <v>72</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>68</v>
@@ -6683,7 +6686,7 @@
         <v>73</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="6" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6691,7 +6694,7 @@
         <v>83</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>79</v>
@@ -6700,10 +6703,10 @@
         <v>80</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6711,7 +6714,7 @@
         <v>119</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>115</v>
@@ -6720,10 +6723,10 @@
         <v>116</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6737,18 +6740,18 @@
         <v>121</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>129</v>
@@ -6757,53 +6760,53 @@
         <v>61</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>131</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -6828,26 +6831,26 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6855,13 +6858,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6869,13 +6872,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6883,13 +6886,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6897,13 +6900,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6911,13 +6914,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>74</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6925,13 +6928,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>79</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6939,13 +6942,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="12" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6953,13 +6956,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="13" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6973,7 +6976,7 @@
         <v>95</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6981,13 +6984,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -6995,21 +6998,21 @@
         <v>11</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>115</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D17"/>
     </row>
@@ -7045,7 +7048,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7053,7 +7056,7 @@
         <v>135</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>137</v>
@@ -7065,167 +7068,167 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E5" s="12">
         <v>0.25</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E6" s="12">
         <v>1.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E7" s="12">
         <v>1.5</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E8" s="12">
         <v>1</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E9" s="12">
         <v>1</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B10" s="11" t="s">
         <v>75</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E10" s="12">
         <v>1</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E11" s="12">
         <v>0.5</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E12" s="12">
         <v>1</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
@@ -7257,7 +7260,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7277,47 +7280,47 @@
         <v>140</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>392</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E5" s="12">
         <v>1</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>107</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="E6" s="12">
         <v>0.5</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7328,16 +7331,16 @@
         <v>70</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E7" s="12">
         <v>0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7345,19 +7348,19 @@
         <v>61</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E8" s="12">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7365,19 +7368,19 @@
         <v>61</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="E9" s="12">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7388,16 +7391,16 @@
         <v>371</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="E10" s="12">
         <v>0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/docs/07-master-backlog.xlsx
+++ b/docs/07-master-backlog.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1233" uniqueCount="633">
   <si>
     <t>Master Sprint Backlog v2</t>
   </si>
@@ -648,6 +648,9 @@
   </si>
   <si>
     <t>Staging and prod point at different databases</t>
+  </si>
+  <si>
+    <t>🚧 Engineering done (2026-10-26) — AC's 'three separate databases' still needs two cloud DBs, which only the owner can create. Built: src/config/manifest.ts (31 vars: envs, secrecy, home), preflight through the real loaders, scripts/check-readiness.ts (--file .env, every gap in one pass, secrets masked), check-secrets.ts (GitHub/Vercel/local), resolveBootMode (staging+prod REFUSE to boot half-configured; prod refuses ALLOW_DEGRADED_BOOT), hashed cluster fingerprint on /healthz/postgres (Neon names every branch neondb, so names cannot prove separation), scripts/smoke.ts (--target staging=… --target prod=…), deploy.yml (readiness → check:env → MIGRATE → deploy → smoke) and a CI env-check job that proves the gate rejects shared and accepts distinct. Local: strict staging boot exits 1 naming 13 gaps; local boots tolerant; smoke passes. 56 files/710 · 45/462. PENDING (owner): two Neon projects + STAGING/PROD_DATABASE_URL secrets, then npm run check:env. No host yet for src/server.ts — see docs/environments.md.</t>
   </si>
   <si>
     <t>W00-14</t>
@@ -3745,12 +3748,12 @@
         <v>208</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B18" s="11" t="s">
         <v>51</v>
@@ -3762,10 +3765,10 @@
         <v>146</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G18" s="12">
         <v>0.5</v>
@@ -3777,7 +3780,7 @@
         <v>205</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>151</v>
@@ -3785,7 +3788,7 @@
     </row>
     <row r="19" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B19" s="11" t="s">
         <v>51</v>
@@ -3794,13 +3797,13 @@
         <v>195</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G19" s="12">
         <v>0.5</v>
@@ -3812,15 +3815,15 @@
         <v>61</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K19" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>51</v>
@@ -3832,10 +3835,10 @@
         <v>190</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G20" s="12">
         <v>0.25</v>
@@ -3847,7 +3850,7 @@
         <v>189</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>151</v>
@@ -3855,7 +3858,7 @@
     </row>
     <row r="21" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B21" s="11" t="s">
         <v>51</v>
@@ -3867,10 +3870,10 @@
         <v>70</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G21" s="12">
         <v>0.5</v>
@@ -3882,7 +3885,7 @@
         <v>205</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>151</v>
@@ -3890,7 +3893,7 @@
     </row>
     <row r="22" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>51</v>
@@ -3902,10 +3905,10 @@
         <v>177</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G22" s="12">
         <v>0.25</v>
@@ -3917,7 +3920,7 @@
         <v>61</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>151</v>
@@ -3925,7 +3928,7 @@
     </row>
     <row r="23" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" s="11" t="s">
         <v>51</v>
@@ -3937,10 +3940,10 @@
         <v>107</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G23" s="12">
         <v>0.5</v>
@@ -3952,30 +3955,30 @@
         <v>61</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>51</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>146</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G24" s="12">
         <v>0.25</v>
@@ -3984,10 +3987,10 @@
         <v>149</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>151</v>
@@ -3995,7 +3998,7 @@
     </row>
     <row r="25" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B25" s="11" t="s">
         <v>57</v>
@@ -4007,10 +4010,10 @@
         <v>146</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G25" s="12">
         <v>3</v>
@@ -4022,15 +4025,15 @@
         <v>144</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K25" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>57</v>
@@ -4042,10 +4045,10 @@
         <v>146</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G26" s="12">
         <v>2</v>
@@ -4054,18 +4057,18 @@
         <v>149</v>
       </c>
       <c r="I26" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K26" s="11" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="27" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B27" s="11" t="s">
         <v>57</v>
@@ -4077,10 +4080,10 @@
         <v>146</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G27" s="12">
         <v>0.75</v>
@@ -4089,18 +4092,18 @@
         <v>149</v>
       </c>
       <c r="I27" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K27" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>63</v>
@@ -4112,10 +4115,10 @@
         <v>146</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G28" s="12">
         <v>2</v>
@@ -4124,18 +4127,18 @@
         <v>149</v>
       </c>
       <c r="I28" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K28" s="11" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>63</v>
@@ -4147,10 +4150,10 @@
         <v>146</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G29" s="12">
         <v>1</v>
@@ -4159,18 +4162,18 @@
         <v>149</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K29" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>63</v>
@@ -4182,10 +4185,10 @@
         <v>146</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G30" s="12">
         <v>1</v>
@@ -4194,18 +4197,18 @@
         <v>149</v>
       </c>
       <c r="I30" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K30" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>63</v>
@@ -4217,10 +4220,10 @@
         <v>146</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G31" s="12">
         <v>1</v>
@@ -4229,18 +4232,18 @@
         <v>149</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K31" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>63</v>
@@ -4252,10 +4255,10 @@
         <v>70</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G32" s="12">
         <v>0.5</v>
@@ -4264,18 +4267,18 @@
         <v>149</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K32" s="11" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B33" s="11" t="s">
         <v>68</v>
@@ -4287,10 +4290,10 @@
         <v>70</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G33" s="12">
         <v>2</v>
@@ -4299,18 +4302,18 @@
         <v>149</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>68</v>
@@ -4322,10 +4325,10 @@
         <v>70</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G34" s="12">
         <v>1</v>
@@ -4334,18 +4337,18 @@
         <v>149</v>
       </c>
       <c r="I34" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="35" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B35" s="11" t="s">
         <v>68</v>
@@ -4357,10 +4360,10 @@
         <v>70</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G35" s="12">
         <v>2</v>
@@ -4369,18 +4372,18 @@
         <v>149</v>
       </c>
       <c r="I35" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>74</v>
@@ -4392,10 +4395,10 @@
         <v>70</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G36" s="12">
         <v>2</v>
@@ -4404,18 +4407,18 @@
         <v>149</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K36" s="11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>74</v>
@@ -4424,13 +4427,13 @@
         <v>195</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G37" s="12">
         <v>1</v>
@@ -4439,18 +4442,18 @@
         <v>149</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>74</v>
@@ -4459,13 +4462,13 @@
         <v>195</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G38" s="12">
         <v>2</v>
@@ -4474,18 +4477,18 @@
         <v>149</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K38" s="11" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>79</v>
@@ -4494,13 +4497,13 @@
         <v>195</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="G39" s="12">
         <v>2</v>
@@ -4509,18 +4512,18 @@
         <v>149</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="40" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>79</v>
@@ -4529,13 +4532,13 @@
         <v>195</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G40" s="12">
         <v>2.5</v>
@@ -4544,18 +4547,18 @@
         <v>149</v>
       </c>
       <c r="I40" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J40" s="11" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K40" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="41" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B41" s="11" t="s">
         <v>79</v>
@@ -4564,13 +4567,13 @@
         <v>195</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G41" s="12">
         <v>1</v>
@@ -4579,18 +4582,18 @@
         <v>149</v>
       </c>
       <c r="I41" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K41" s="11" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="42" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B42" s="11" t="s">
         <v>85</v>
@@ -4599,13 +4602,13 @@
         <v>195</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G42" s="12">
         <v>2</v>
@@ -4614,18 +4617,18 @@
         <v>149</v>
       </c>
       <c r="I42" s="11" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K42" s="11" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="43" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B43" s="11" t="s">
         <v>85</v>
@@ -4634,13 +4637,13 @@
         <v>195</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G43" s="12">
         <v>1.5</v>
@@ -4649,18 +4652,18 @@
         <v>149</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J43" s="11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K43" s="11" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="44" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B44" s="11" t="s">
         <v>85</v>
@@ -4669,13 +4672,13 @@
         <v>195</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G44" s="12">
         <v>1.5</v>
@@ -4684,18 +4687,18 @@
         <v>149</v>
       </c>
       <c r="I44" s="11" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="J44" s="11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K44" s="11" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="45" ht="40" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>90</v>
@@ -4704,13 +4707,13 @@
         <v>195</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G45" s="12">
         <v>0.5</v>
@@ -4719,18 +4722,18 @@
         <v>170</v>
       </c>
       <c r="I45" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J45" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
   